--- a/Results/Phase 2/Hydrogen/hydrogen resource use fossils results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen resource use fossils results.xlsx
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="C2" t="n">
         <v>172.9654793090297</v>
       </c>
       <c r="D2" t="n">
-        <v>173.4809417008622</v>
+        <v>173.4809417008623</v>
       </c>
       <c r="E2" t="n">
-        <v>159.9807471804043</v>
+        <v>159.9807471804041</v>
       </c>
       <c r="F2" t="n">
         <v>173.5659476407523</v>
@@ -604,67 +604,67 @@
         <v>174.746397337777</v>
       </c>
       <c r="H2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="I2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="J2" t="n">
-        <v>174.5037582089693</v>
+        <v>174.5037582089694</v>
       </c>
       <c r="K2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="L2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="M2" t="n">
-        <v>175.6536252687476</v>
+        <v>175.6536252687477</v>
       </c>
       <c r="N2" t="n">
-        <v>174.5145460951539</v>
+        <v>174.514546095154</v>
       </c>
       <c r="O2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="P2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="Q2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="R2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="S2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="T2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="U2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="V2" t="n">
         <v>179.0933830253471</v>
       </c>
       <c r="W2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="X2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="Y2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="Z2" t="n">
         <v>174.4058094694586</v>
       </c>
       <c r="AA2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
       <c r="AB2" t="n">
-        <v>174.5241126996421</v>
+        <v>174.5241126996422</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="C3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="D3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="E3" t="n">
-        <v>161.3553208447254</v>
+        <v>161.3553208447252</v>
       </c>
       <c r="F3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="G3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="H3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="I3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="J3" t="n">
-        <v>175.1586661715562</v>
+        <v>175.1586661715563</v>
       </c>
       <c r="K3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="L3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="M3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="N3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="O3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="P3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="Q3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="R3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="S3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="T3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="U3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="V3" t="n">
-        <v>180.2428753642946</v>
+        <v>180.2428753642947</v>
       </c>
       <c r="W3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="X3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="Y3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="Z3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="AA3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
       <c r="AB3" t="n">
-        <v>175.1790230266844</v>
+        <v>175.1790230266843</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>470.2339467857129</v>
+        <v>470.2339467857132</v>
       </c>
       <c r="C4" t="n">
-        <v>155.6394880060551</v>
+        <v>155.6394880060552</v>
       </c>
       <c r="D4" t="n">
-        <v>314.3971760991379</v>
+        <v>314.3971760991365</v>
       </c>
       <c r="E4" t="n">
-        <v>330.260873502309</v>
+        <v>330.2608735023085</v>
       </c>
       <c r="F4" t="n">
-        <v>347.1726648033562</v>
+        <v>347.1726648033546</v>
       </c>
       <c r="G4" t="n">
-        <v>638.3830898698418</v>
+        <v>638.3830898698402</v>
       </c>
       <c r="H4" t="n">
-        <v>613.8290760395395</v>
+        <v>613.82907603954</v>
       </c>
       <c r="I4" t="n">
-        <v>309.8829099056015</v>
+        <v>309.8829099056001</v>
       </c>
       <c r="J4" t="n">
         <v>590.2922198981316</v>
       </c>
       <c r="K4" t="n">
-        <v>524.6143142506825</v>
+        <v>524.614314250682</v>
       </c>
       <c r="L4" t="n">
-        <v>584.0265684584382</v>
+        <v>584.0265684584394</v>
       </c>
       <c r="M4" t="n">
-        <v>984.5672587320614</v>
+        <v>984.5672587320604</v>
       </c>
       <c r="N4" t="n">
-        <v>735.9075717073957</v>
+        <v>735.9075717073943</v>
       </c>
       <c r="O4" t="n">
-        <v>466.6617651643431</v>
+        <v>466.6617651643428</v>
       </c>
       <c r="P4" t="n">
-        <v>671.2113214117386</v>
+        <v>671.2113214117388</v>
       </c>
       <c r="Q4" t="n">
-        <v>470.2827818254003</v>
+        <v>470.2827818253987</v>
       </c>
       <c r="R4" t="n">
-        <v>385.728021193186</v>
+        <v>385.7280211931864</v>
       </c>
       <c r="S4" t="n">
-        <v>547.4513198525457</v>
+        <v>547.4513198525456</v>
       </c>
       <c r="T4" t="n">
-        <v>550.6750700415796</v>
+        <v>550.6750700415797</v>
       </c>
       <c r="U4" t="n">
-        <v>735.9075717073957</v>
+        <v>735.9075717073943</v>
       </c>
       <c r="V4" t="n">
-        <v>452.3863005674569</v>
+        <v>452.3863005674557</v>
       </c>
       <c r="W4" t="n">
-        <v>772.3688652788624</v>
+        <v>772.3688652788629</v>
       </c>
       <c r="X4" t="n">
-        <v>445.9734531886642</v>
+        <v>445.973453188664</v>
       </c>
       <c r="Y4" t="n">
-        <v>844.4312401727839</v>
+        <v>844.4312401727834</v>
       </c>
       <c r="Z4" t="n">
-        <v>543.6339121026186</v>
+        <v>543.6339121026176</v>
       </c>
       <c r="AA4" t="n">
-        <v>484.1414874630052</v>
+        <v>484.1414874630049</v>
       </c>
       <c r="AB4" t="n">
-        <v>818.5071218102105</v>
+        <v>818.5071218102097</v>
       </c>
     </row>
     <row r="5">
@@ -910,7 +910,7 @@
         <v>11.01639813549765</v>
       </c>
       <c r="V5" t="n">
-        <v>11.13548839570435</v>
+        <v>11.13548839570434</v>
       </c>
       <c r="W5" t="n">
         <v>11.12882430742481</v>
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>736.9463036734556</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="C6" t="n">
-        <v>882.5942022251661</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="D6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="E6" t="n">
-        <v>882.5942022251661</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="F6" t="n">
-        <v>736.9463036734556</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="G6" t="n">
-        <v>736.9463036734556</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="H6" t="n">
-        <v>882.5942022251661</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="I6" t="n">
-        <v>882.5942022251661</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="J6" t="n">
-        <v>736.9473137883392</v>
+        <v>882.5952123400502</v>
       </c>
       <c r="K6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="L6" t="n">
-        <v>882.5942022251661</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="M6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="N6" t="n">
-        <v>737.0224336828129</v>
+        <v>737.0224336828127</v>
       </c>
       <c r="O6" t="n">
-        <v>882.999778706775</v>
+        <v>882.9997787067755</v>
       </c>
       <c r="P6" t="n">
-        <v>882.9998582489712</v>
+        <v>882.9998582489716</v>
       </c>
       <c r="Q6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="R6" t="n">
-        <v>882.5942022251661</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="S6" t="n">
-        <v>882.5942022251661</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="T6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="U6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="V6" t="n">
-        <v>882.6008663134464</v>
+        <v>882.6008663134467</v>
       </c>
       <c r="W6" t="n">
-        <v>774.10405100418</v>
+        <v>882.9998283281105</v>
       </c>
       <c r="X6" t="n">
-        <v>882.5942022251661</v>
+        <v>882.5942022251668</v>
       </c>
       <c r="Y6" t="n">
-        <v>768.8688859791242</v>
+        <v>768.8688859791249</v>
       </c>
       <c r="Z6" t="n">
-        <v>736.9463036734556</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="AA6" t="n">
-        <v>882.5942022251661</v>
+        <v>736.9463036734561</v>
       </c>
       <c r="AB6" t="n">
-        <v>737.082392254427</v>
+        <v>737.0823922544268</v>
       </c>
     </row>
     <row r="7">
@@ -1050,7 +1050,7 @@
         <v>19.07192165965788</v>
       </c>
       <c r="J7" t="n">
-        <v>19.07293177454154</v>
+        <v>19.07293177454153</v>
       </c>
       <c r="K7" t="n">
         <v>19.07192165965788</v>
@@ -1083,10 +1083,10 @@
         <v>19.07192165965788</v>
       </c>
       <c r="U7" t="n">
-        <v>19.07114507159222</v>
+        <v>19.07114507159223</v>
       </c>
       <c r="V7" t="n">
-        <v>19.07858574793743</v>
+        <v>19.07858574793742</v>
       </c>
       <c r="W7" t="n">
         <v>19.07192165965788</v>
@@ -1114,82 +1114,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.50194779460936</v>
+        <v>22.50194779460937</v>
       </c>
       <c r="C8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="D8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="E8" t="n">
-        <v>31.18191928492987</v>
+        <v>26.56009051198576</v>
       </c>
       <c r="F8" t="n">
         <v>23.85418590641054</v>
       </c>
       <c r="G8" t="n">
-        <v>31.18191928492987</v>
+        <v>32.98176791731029</v>
       </c>
       <c r="H8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="I8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="J8" t="n">
         <v>31.18292939981349</v>
       </c>
       <c r="K8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="L8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="M8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928493055</v>
       </c>
       <c r="N8" t="n">
-        <v>24.45348924919786</v>
+        <v>24.45348924919785</v>
       </c>
       <c r="O8" t="n">
-        <v>26.30252023860828</v>
+        <v>26.3025202386083</v>
       </c>
       <c r="P8" t="n">
-        <v>25.84927806493225</v>
+        <v>25.84927806493226</v>
       </c>
       <c r="Q8" t="n">
         <v>20.79613528942993</v>
       </c>
       <c r="R8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="S8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="T8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="U8" t="n">
-        <v>25.84021195811427</v>
+        <v>26.94480342356862</v>
       </c>
       <c r="V8" t="n">
-        <v>31.18858337320939</v>
+        <v>28.81562330054541</v>
       </c>
       <c r="W8" t="n">
-        <v>31.18362513572082</v>
+        <v>31.18362513572084</v>
       </c>
       <c r="X8" t="n">
         <v>21.59167191631298</v>
       </c>
       <c r="Y8" t="n">
-        <v>39.81129765421724</v>
+        <v>39.81129765421726</v>
       </c>
       <c r="Z8" t="n">
-        <v>31.18191928492987</v>
+        <v>22.34071286895543</v>
       </c>
       <c r="AA8" t="n">
-        <v>31.18191928492987</v>
+        <v>31.18191928492985</v>
       </c>
       <c r="AB8" t="n">
         <v>40.24887530245915</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.34583001959286</v>
+        <v>44.34583001959284</v>
       </c>
       <c r="C9" t="n">
         <v>54.16485233079803</v>
@@ -1211,13 +1211,13 @@
         <v>54.16485233079803</v>
       </c>
       <c r="E9" t="n">
-        <v>54.16485233079803</v>
+        <v>51.8986640942082</v>
       </c>
       <c r="F9" t="n">
-        <v>54.16485233079803</v>
+        <v>31.52932253937568</v>
       </c>
       <c r="G9" t="n">
-        <v>54.16485233079803</v>
+        <v>54.16485501119638</v>
       </c>
       <c r="H9" t="n">
         <v>54.16485233079803</v>
@@ -1226,7 +1226,7 @@
         <v>54.16485233079803</v>
       </c>
       <c r="J9" t="n">
-        <v>54.16586244568171</v>
+        <v>54.16586244568169</v>
       </c>
       <c r="K9" t="n">
         <v>54.16485233079803</v>
@@ -1241,13 +1241,13 @@
         <v>54.16485233079803</v>
       </c>
       <c r="O9" t="n">
-        <v>57.41886703649789</v>
+        <v>57.41886703649788</v>
       </c>
       <c r="P9" t="n">
-        <v>58.12655882255723</v>
+        <v>58.12655882255722</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.16485501119641</v>
+        <v>54.16485501119638</v>
       </c>
       <c r="R9" t="n">
         <v>54.16485233079803</v>
@@ -1262,7 +1262,7 @@
         <v>54.16485233079803</v>
       </c>
       <c r="V9" t="n">
-        <v>54.17151641907755</v>
+        <v>65.50244900222526</v>
       </c>
       <c r="W9" t="n">
         <v>54.16485233079803</v>
@@ -1274,7 +1274,7 @@
         <v>54.16485233079803</v>
       </c>
       <c r="Z9" t="n">
-        <v>54.16485233079803</v>
+        <v>48.24485608302948</v>
       </c>
       <c r="AA9" t="n">
         <v>54.16485233079803</v>
@@ -1299,19 +1299,19 @@
         <v>169.3305380555623</v>
       </c>
       <c r="E10" t="n">
-        <v>154.8146137546242</v>
+        <v>154.8146137546238</v>
       </c>
       <c r="F10" t="n">
-        <v>168.8635966960652</v>
+        <v>168.8635966960651</v>
       </c>
       <c r="G10" t="n">
-        <v>161.7180652993196</v>
+        <v>161.7180652993195</v>
       </c>
       <c r="H10" t="n">
         <v>164.0775050381583</v>
       </c>
       <c r="I10" t="n">
-        <v>169.4901230554175</v>
+        <v>169.4901230554177</v>
       </c>
       <c r="J10" t="n">
         <v>163.075597076125</v>
@@ -1323,40 +1323,40 @@
         <v>163.4377750015202</v>
       </c>
       <c r="M10" t="n">
-        <v>156.6744779748857</v>
+        <v>156.6744779748858</v>
       </c>
       <c r="N10" t="n">
-        <v>163.2257980078141</v>
+        <v>163.225798007814</v>
       </c>
       <c r="O10" t="n">
         <v>164.8466008032046</v>
       </c>
       <c r="P10" t="n">
-        <v>160.838671377319</v>
+        <v>160.8386713773189</v>
       </c>
       <c r="Q10" t="n">
         <v>166.1197436224561</v>
       </c>
       <c r="R10" t="n">
-        <v>168.1493283557377</v>
+        <v>168.1493283557376</v>
       </c>
       <c r="S10" t="n">
-        <v>163.708552147264</v>
+        <v>163.7085521472639</v>
       </c>
       <c r="T10" t="n">
-        <v>164.8268069383838</v>
+        <v>164.8268069383839</v>
       </c>
       <c r="U10" t="n">
         <v>160.0136002025777</v>
       </c>
       <c r="V10" t="n">
-        <v>170.5776448213948</v>
+        <v>170.5776448213949</v>
       </c>
       <c r="W10" t="n">
-        <v>159.7213981208486</v>
+        <v>159.7213981208485</v>
       </c>
       <c r="X10" t="n">
-        <v>166.6751506316217</v>
+        <v>166.6751506316218</v>
       </c>
       <c r="Y10" t="n">
         <v>158.266792923345</v>
@@ -1365,10 +1365,10 @@
         <v>163.7494713943001</v>
       </c>
       <c r="AA10" t="n">
-        <v>165.6417322661845</v>
+        <v>165.6417322661844</v>
       </c>
       <c r="AB10" t="n">
-        <v>160.3353005926245</v>
+        <v>160.3353005926244</v>
       </c>
     </row>
     <row r="11">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>169.9041390864737</v>
+        <v>169.9041390864738</v>
       </c>
       <c r="C11" t="n">
         <v>171.6767137124413</v>
       </c>
       <c r="D11" t="n">
-        <v>170.819862400986</v>
+        <v>170.8198624009861</v>
       </c>
       <c r="E11" t="n">
-        <v>157.0047046104115</v>
+        <v>157.0047046104113</v>
       </c>
       <c r="F11" t="n">
-        <v>170.6924085342508</v>
+        <v>170.6924085342509</v>
       </c>
       <c r="G11" t="n">
         <v>168.6216186742989</v>
@@ -1405,28 +1405,28 @@
         <v>169.0059232640915</v>
       </c>
       <c r="K11" t="n">
-        <v>169.9811848989193</v>
+        <v>169.9811848989194</v>
       </c>
       <c r="L11" t="n">
         <v>169.1818074310551</v>
       </c>
       <c r="M11" t="n">
-        <v>167.233998299693</v>
+        <v>167.2339982996933</v>
       </c>
       <c r="N11" t="n">
         <v>169.0757906189</v>
       </c>
       <c r="O11" t="n">
-        <v>169.8228276604829</v>
+        <v>169.822827660483</v>
       </c>
       <c r="P11" t="n">
         <v>167.9992069991918</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.4021117005078</v>
+        <v>170.402111700508</v>
       </c>
       <c r="R11" t="n">
-        <v>171.3255792220536</v>
+        <v>171.3255792220538</v>
       </c>
       <c r="S11" t="n">
         <v>169.3050118952841</v>
@@ -1435,7 +1435,7 @@
         <v>169.8138213889102</v>
       </c>
       <c r="U11" t="n">
-        <v>167.6237969853386</v>
+        <v>167.6237969853387</v>
       </c>
       <c r="V11" t="n">
         <v>174.6956723270654</v>
@@ -1444,7 +1444,7 @@
         <v>167.4908441069591</v>
       </c>
       <c r="X11" t="n">
-        <v>170.6548236596552</v>
+        <v>170.6548236596553</v>
       </c>
       <c r="Y11" t="n">
         <v>166.8289941065433</v>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>170.1529177276961</v>
+        <v>170.152917727696</v>
       </c>
       <c r="C2" t="n">
         <v>170.3263269819892</v>
@@ -1631,25 +1631,25 @@
         <v>170.4684347827955</v>
       </c>
       <c r="E2" t="n">
-        <v>157.5754880669707</v>
+        <v>157.5754880669708</v>
       </c>
       <c r="F2" t="n">
-        <v>170.763403707957</v>
+        <v>170.7634037079569</v>
       </c>
       <c r="G2" t="n">
         <v>170.9612425263518</v>
       </c>
       <c r="H2" t="n">
-        <v>170.9099867873522</v>
+        <v>170.9099867873523</v>
       </c>
       <c r="I2" t="n">
         <v>170.4238193037241</v>
       </c>
       <c r="J2" t="n">
-        <v>170.8429265789338</v>
+        <v>170.8429265789339</v>
       </c>
       <c r="K2" t="n">
-        <v>171.0452718896413</v>
+        <v>171.0452718896414</v>
       </c>
       <c r="L2" t="n">
         <v>170.7217224604347</v>
@@ -1658,7 +1658,7 @@
         <v>170.7429162847482</v>
       </c>
       <c r="N2" t="n">
-        <v>171.1276115645856</v>
+        <v>171.1276115645857</v>
       </c>
       <c r="O2" t="n">
         <v>171.1965876157203</v>
@@ -1670,37 +1670,37 @@
         <v>170.452293155679</v>
       </c>
       <c r="R2" t="n">
-        <v>170.3944252846962</v>
+        <v>170.3944252846963</v>
       </c>
       <c r="S2" t="n">
-        <v>171.0071052759087</v>
+        <v>171.0071052759088</v>
       </c>
       <c r="T2" t="n">
         <v>170.9247989515638</v>
       </c>
       <c r="U2" t="n">
-        <v>171.0627363926707</v>
+        <v>171.062736392671</v>
       </c>
       <c r="V2" t="n">
         <v>175.3610944647623</v>
       </c>
       <c r="W2" t="n">
-        <v>171.7459908048309</v>
+        <v>171.7459908048308</v>
       </c>
       <c r="X2" t="n">
-        <v>171.7467313547185</v>
+        <v>171.7467313547186</v>
       </c>
       <c r="Y2" t="n">
-        <v>171.5492443752632</v>
+        <v>171.5492443752633</v>
       </c>
       <c r="Z2" t="n">
-        <v>170.4983087092232</v>
+        <v>170.4983087092233</v>
       </c>
       <c r="AA2" t="n">
         <v>171.4002172447952</v>
       </c>
       <c r="AB2" t="n">
-        <v>170.7568135235297</v>
+        <v>170.7568135235296</v>
       </c>
     </row>
     <row r="3">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="D3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="E3" t="n">
-        <v>159.8720969738152</v>
+        <v>159.8720969738151</v>
       </c>
       <c r="F3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="G3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="H3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="I3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="J3" t="n">
-        <v>172.758039287333</v>
+        <v>172.7580392873332</v>
       </c>
       <c r="K3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="L3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="M3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="N3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="O3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="P3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="Q3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="R3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="S3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="T3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="U3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="V3" t="n">
-        <v>177.597563531338</v>
+        <v>177.5975635313381</v>
       </c>
       <c r="W3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="X3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="Y3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="Z3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="AA3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
       <c r="AB3" t="n">
-        <v>172.7697248532612</v>
+        <v>172.7697248532613</v>
       </c>
     </row>
     <row r="4">
@@ -1798,28 +1798,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.32963321140386</v>
+        <v>19.32963321140395</v>
       </c>
       <c r="C4" t="n">
-        <v>62.82812674125169</v>
+        <v>62.82812674125181</v>
       </c>
       <c r="D4" t="n">
-        <v>98.86953359749961</v>
+        <v>98.8695335974999</v>
       </c>
       <c r="E4" t="n">
-        <v>47.34988585000887</v>
+        <v>47.34988585000917</v>
       </c>
       <c r="F4" t="n">
-        <v>176.1064741364599</v>
+        <v>176.1064741364597</v>
       </c>
       <c r="G4" t="n">
-        <v>198.370976207141</v>
+        <v>198.3709762071408</v>
       </c>
       <c r="H4" t="n">
-        <v>224.8431249036137</v>
+        <v>224.8431249036135</v>
       </c>
       <c r="I4" t="n">
-        <v>91.06301575952449</v>
+        <v>91.06301575952439</v>
       </c>
       <c r="J4" t="n">
         <v>185.6061424407396</v>
@@ -1828,55 +1828,55 @@
         <v>222.8794723759462</v>
       </c>
       <c r="L4" t="n">
-        <v>149.0147851660793</v>
+        <v>149.0147851660792</v>
       </c>
       <c r="M4" t="n">
         <v>169.0529519378394</v>
       </c>
       <c r="N4" t="n">
-        <v>272.8586922990226</v>
+        <v>272.8586922990227</v>
       </c>
       <c r="O4" t="n">
-        <v>251.2699894965881</v>
+        <v>251.2699894965878</v>
       </c>
       <c r="P4" t="n">
-        <v>376.8726289062023</v>
+        <v>376.8726289062018</v>
       </c>
       <c r="Q4" t="n">
-        <v>91.89213213359797</v>
+        <v>91.89213213359812</v>
       </c>
       <c r="R4" t="n">
-        <v>85.69429242058187</v>
+        <v>85.69429242058206</v>
       </c>
       <c r="S4" t="n">
-        <v>211.6003030397175</v>
+        <v>211.6003030397173</v>
       </c>
       <c r="T4" t="n">
-        <v>223.2302604190593</v>
+        <v>223.2302604190598</v>
       </c>
       <c r="U4" t="n">
-        <v>221.9613839702433</v>
+        <v>221.961383970243</v>
       </c>
       <c r="V4" t="n">
-        <v>121.8666940241611</v>
+        <v>121.8666940241612</v>
       </c>
       <c r="W4" t="n">
-        <v>420.9158445173433</v>
+        <v>420.9158445173432</v>
       </c>
       <c r="X4" t="n">
-        <v>408.9496218673463</v>
+        <v>408.9496218673448</v>
       </c>
       <c r="Y4" t="n">
-        <v>378.3928151839618</v>
+        <v>378.3928151839619</v>
       </c>
       <c r="Z4" t="n">
-        <v>93.21257956442281</v>
+        <v>93.21257956442304</v>
       </c>
       <c r="AA4" t="n">
-        <v>338.6974540364027</v>
+        <v>338.6974540364033</v>
       </c>
       <c r="AB4" t="n">
-        <v>184.851025243933</v>
+        <v>184.8510252439337</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
       <c r="C5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="D5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="E5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="F5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
       <c r="G5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="H5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="I5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="J5" t="n">
-        <v>5.480390908999476</v>
+        <v>5.480390908999515</v>
       </c>
       <c r="K5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="L5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="M5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="N5" t="n">
-        <v>272.8586922990226</v>
+        <v>272.8586922990227</v>
       </c>
       <c r="O5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
       <c r="P5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
       <c r="R5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="S5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="T5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="U5" t="n">
-        <v>5.175412190902309</v>
+        <v>5.175412190902219</v>
       </c>
       <c r="V5" t="n">
-        <v>5.49696373228617</v>
+        <v>5.496963732286179</v>
       </c>
       <c r="W5" t="n">
-        <v>5.477326464587089</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="X5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.175412190902309</v>
+        <v>5.17541219090224</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.477326464587053</v>
+        <v>5.477326464587199</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.47732646458705</v>
+        <v>5.477326464587081</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="C6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="D6" t="n">
-        <v>761.8703859429512</v>
+        <v>761.870385942951</v>
       </c>
       <c r="E6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="F6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="G6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="H6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="I6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="J6" t="n">
-        <v>637.2037038739445</v>
+        <v>761.8734503873645</v>
       </c>
       <c r="K6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="L6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="M6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="N6" t="n">
-        <v>272.8586922990226</v>
+        <v>272.8586922990227</v>
       </c>
       <c r="O6" t="n">
-        <v>762.2916006504431</v>
+        <v>762.2916006504427</v>
       </c>
       <c r="P6" t="n">
-        <v>600.6745452854537</v>
+        <v>762.2883170125957</v>
       </c>
       <c r="Q6" t="n">
-        <v>761.8703859429512</v>
+        <v>761.870385942951</v>
       </c>
       <c r="R6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="S6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="T6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="U6" t="n">
-        <v>637.2006394295317</v>
+        <v>761.870385942951</v>
       </c>
       <c r="V6" t="n">
-        <v>637.2202766972316</v>
+        <v>761.8900232106507</v>
       </c>
       <c r="W6" t="n">
-        <v>669.5089131872481</v>
+        <v>669.5089131872489</v>
       </c>
       <c r="X6" t="n">
-        <v>637.2006394295317</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="Y6" t="n">
-        <v>664.9380254361636</v>
+        <v>664.9380254361649</v>
       </c>
       <c r="Z6" t="n">
-        <v>761.8703859429512</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="AA6" t="n">
-        <v>637.2006394295317</v>
+        <v>637.2006394295327</v>
       </c>
       <c r="AB6" t="n">
-        <v>637.242566652573</v>
+        <v>637.2425666525736</v>
       </c>
     </row>
     <row r="7">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="C7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="D7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="E7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="F7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="G7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="H7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="I7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="J7" t="n">
-        <v>10.27022061228165</v>
+        <v>10.2702206122817</v>
       </c>
       <c r="K7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="L7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="M7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="N7" t="n">
-        <v>272.8586922990226</v>
+        <v>272.8586922990227</v>
       </c>
       <c r="O7" t="n">
-        <v>10.26716934860042</v>
+        <v>10.2671693486005</v>
       </c>
       <c r="P7" t="n">
-        <v>10.26716934860042</v>
+        <v>10.2671693486005</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="R7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="S7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="T7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="U7" t="n">
-        <v>10.19568243967406</v>
+        <v>10.19568243967415</v>
       </c>
       <c r="V7" t="n">
         <v>10.28679343556835</v>
       </c>
       <c r="W7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="X7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.26715616786924</v>
+        <v>10.26715616786936</v>
       </c>
     </row>
     <row r="8">
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.68213374393974</v>
+        <v>11.68213374393983</v>
       </c>
       <c r="C8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="D8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="E8" t="n">
-        <v>16.44392807772952</v>
+        <v>13.90841306108357</v>
       </c>
       <c r="F8" t="n">
-        <v>12.42396564780292</v>
+        <v>12.42396564780309</v>
       </c>
       <c r="G8" t="n">
-        <v>16.44392807772952</v>
+        <v>17.4313171522972</v>
       </c>
       <c r="H8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="I8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="J8" t="n">
-        <v>16.44699252214194</v>
+        <v>16.44699252214214</v>
       </c>
       <c r="K8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="L8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="M8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772575</v>
       </c>
       <c r="N8" t="n">
-        <v>272.8586922990226</v>
+        <v>272.8586922990227</v>
       </c>
       <c r="O8" t="n">
-        <v>13.7671111349439</v>
+        <v>13.76711113494401</v>
       </c>
       <c r="P8" t="n">
-        <v>13.51846446451514</v>
+        <v>13.51846446451518</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.74633247733648</v>
+        <v>10.74633247733662</v>
       </c>
       <c r="R8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="S8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="T8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="U8" t="n">
-        <v>13.46174741973289</v>
+        <v>14.06435921313994</v>
       </c>
       <c r="V8" t="n">
-        <v>16.46356534542875</v>
+        <v>15.10098990926571</v>
       </c>
       <c r="W8" t="n">
-        <v>16.44486389719547</v>
+        <v>16.44486389719553</v>
       </c>
       <c r="X8" t="n">
-        <v>11.18276038397075</v>
+        <v>11.18276038397097</v>
       </c>
       <c r="Y8" t="n">
-        <v>21.08369748843219</v>
+        <v>21.08369748843243</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.44392807772952</v>
+        <v>11.59368097035447</v>
       </c>
       <c r="AA8" t="n">
-        <v>16.44392807772952</v>
+        <v>16.44392807772989</v>
       </c>
       <c r="AB8" t="n">
-        <v>21.4180204251351</v>
+        <v>21.41802042513516</v>
       </c>
     </row>
     <row r="9">
@@ -2238,85 +2238,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.71290997926483</v>
+        <v>17.71290997926488</v>
       </c>
       <c r="C9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="D9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="E9" t="n">
-        <v>21.45333721428867</v>
+        <v>20.59006376626086</v>
       </c>
       <c r="F9" t="n">
-        <v>21.45333721428867</v>
+        <v>12.83062835246402</v>
       </c>
       <c r="G9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333968553237</v>
       </c>
       <c r="H9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="I9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="J9" t="n">
-        <v>21.45640165870117</v>
+        <v>21.45640165870109</v>
       </c>
       <c r="K9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="L9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="M9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="N9" t="n">
-        <v>272.8586922990226</v>
+        <v>272.8586922990227</v>
       </c>
       <c r="O9" t="n">
-        <v>22.69291319251439</v>
+        <v>22.69291319251471</v>
       </c>
       <c r="P9" t="n">
-        <v>22.96249916278321</v>
+        <v>22.96249916278371</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.45333968553218</v>
+        <v>21.45333968553237</v>
       </c>
       <c r="R9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="S9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="T9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="U9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="V9" t="n">
-        <v>21.47297448198786</v>
+        <v>25.78934802918047</v>
       </c>
       <c r="W9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="X9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="Y9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.45333721428867</v>
+        <v>19.19819318464019</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
       <c r="AB9" t="n">
-        <v>21.45333721428867</v>
+        <v>21.45333721428882</v>
       </c>
     </row>
     <row r="10">
@@ -2326,37 +2326,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172.4172189803094</v>
+        <v>172.4172189803095</v>
       </c>
       <c r="C10" t="n">
-        <v>171.4053440916955</v>
+        <v>171.4053440916954</v>
       </c>
       <c r="D10" t="n">
-        <v>170.5745255685039</v>
+        <v>170.574525568504</v>
       </c>
       <c r="E10" t="n">
-        <v>158.8191311998353</v>
+        <v>158.8191311998352</v>
       </c>
       <c r="F10" t="n">
-        <v>168.8658878199664</v>
+        <v>168.8658878199667</v>
       </c>
       <c r="G10" t="n">
-        <v>167.6112249494061</v>
+        <v>167.6112249494062</v>
       </c>
       <c r="H10" t="n">
-        <v>168.0203784816419</v>
+        <v>168.0203784816421</v>
       </c>
       <c r="I10" t="n">
-        <v>170.8394855257262</v>
+        <v>170.8394855257264</v>
       </c>
       <c r="J10" t="n">
         <v>168.2626588543069</v>
       </c>
       <c r="K10" t="n">
-        <v>167.1877790157367</v>
+        <v>167.187779015737</v>
       </c>
       <c r="L10" t="n">
-        <v>169.0567603468652</v>
+        <v>169.0567603468654</v>
       </c>
       <c r="M10" t="n">
         <v>168.9811803745736</v>
@@ -2365,19 +2365,19 @@
         <v>166.6877468028903</v>
       </c>
       <c r="O10" t="n">
-        <v>166.2010990673525</v>
+        <v>166.2010990673527</v>
       </c>
       <c r="P10" t="n">
-        <v>162.9449370719005</v>
+        <v>162.9449370719008</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.6636996477448</v>
+        <v>170.663699647745</v>
       </c>
       <c r="R10" t="n">
-        <v>171.0149871879698</v>
+        <v>171.0149871879699</v>
       </c>
       <c r="S10" t="n">
-        <v>167.352292562801</v>
+        <v>167.3522925628011</v>
       </c>
       <c r="T10" t="n">
         <v>167.9044502654319</v>
@@ -2395,16 +2395,16 @@
         <v>163.0775450223054</v>
       </c>
       <c r="Y10" t="n">
-        <v>164.1928201959775</v>
+        <v>164.1928201959776</v>
       </c>
       <c r="Z10" t="n">
-        <v>170.3650969051621</v>
+        <v>170.3650969051622</v>
       </c>
       <c r="AA10" t="n">
-        <v>165.0647676561657</v>
+        <v>165.0647676561659</v>
       </c>
       <c r="AB10" t="n">
-        <v>168.8862253175333</v>
+        <v>168.8862253175334</v>
       </c>
     </row>
     <row r="11">
@@ -2414,19 +2414,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>169.9925264321333</v>
+        <v>169.9925264321334</v>
       </c>
       <c r="C11" t="n">
-        <v>169.7055293874531</v>
+        <v>169.7055293874532</v>
       </c>
       <c r="D11" t="n">
-        <v>169.4696121125459</v>
+        <v>169.469612112546</v>
       </c>
       <c r="E11" t="n">
-        <v>157.0963852842069</v>
+        <v>157.096385284207</v>
       </c>
       <c r="F11" t="n">
-        <v>168.9871454170174</v>
+        <v>168.9871454170175</v>
       </c>
       <c r="G11" t="n">
         <v>168.614108630934</v>
@@ -2435,16 +2435,16 @@
         <v>168.7490190529966</v>
       </c>
       <c r="I11" t="n">
-        <v>169.5455542583881</v>
+        <v>169.545554258388</v>
       </c>
       <c r="J11" t="n">
         <v>168.7975141559793</v>
       </c>
       <c r="K11" t="n">
-        <v>168.5054687449619</v>
+        <v>168.5054687449618</v>
       </c>
       <c r="L11" t="n">
-        <v>169.0323117775088</v>
+        <v>169.0323117775087</v>
       </c>
       <c r="M11" t="n">
         <v>169.0191164735705</v>
@@ -2453,40 +2453,40 @@
         <v>168.3602921695527</v>
       </c>
       <c r="O11" t="n">
-        <v>168.2078419501634</v>
+        <v>168.2078419501635</v>
       </c>
       <c r="P11" t="n">
-        <v>167.2715482297818</v>
+        <v>167.2715482297817</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.494044975665</v>
+        <v>169.4940449756652</v>
       </c>
       <c r="R11" t="n">
-        <v>169.5960140549714</v>
+        <v>169.5960140549715</v>
       </c>
       <c r="S11" t="n">
-        <v>168.542156319417</v>
+        <v>168.5421563194169</v>
       </c>
       <c r="T11" t="n">
         <v>168.7110835093913</v>
       </c>
       <c r="U11" t="n">
-        <v>168.4534272580863</v>
+        <v>168.4534272580865</v>
       </c>
       <c r="V11" t="n">
-        <v>173.9673488755098</v>
+        <v>173.9673488755097</v>
       </c>
       <c r="W11" t="n">
-        <v>167.3088121190609</v>
+        <v>167.3088121190608</v>
       </c>
       <c r="X11" t="n">
         <v>167.336758644489</v>
       </c>
       <c r="Y11" t="n">
-        <v>167.6467254232257</v>
+        <v>167.6467254232259</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.4041953297433</v>
+        <v>169.4041953297436</v>
       </c>
       <c r="AA11" t="n">
         <v>167.894437165875</v>
@@ -2667,13 +2667,13 @@
         <v>173.2466605937916</v>
       </c>
       <c r="E2" t="n">
-        <v>159.802501689349</v>
+        <v>159.8025016893493</v>
       </c>
       <c r="F2" t="n">
         <v>173.1256475127568</v>
       </c>
       <c r="G2" t="n">
-        <v>174.3549917827277</v>
+        <v>174.3549917827276</v>
       </c>
       <c r="H2" t="n">
         <v>174.1266319052058</v>
@@ -2691,7 +2691,7 @@
         <v>174.1266319052058</v>
       </c>
       <c r="M2" t="n">
-        <v>175.0906493160491</v>
+        <v>175.0906493160492</v>
       </c>
       <c r="N2" t="n">
         <v>174.0263076010239</v>
@@ -2718,7 +2718,7 @@
         <v>174.1266319052058</v>
       </c>
       <c r="V2" t="n">
-        <v>178.5689293105455</v>
+        <v>178.5689293105456</v>
       </c>
       <c r="W2" t="n">
         <v>174.1266319052058</v>
@@ -2730,7 +2730,7 @@
         <v>174.1266319052058</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.8678999503274</v>
+        <v>173.8678999503275</v>
       </c>
       <c r="AA2" t="n">
         <v>174.1266319052058</v>
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="C3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="D3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="E3" t="n">
-        <v>161.2155327732864</v>
+        <v>161.2155327732866</v>
       </c>
       <c r="F3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="G3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="H3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="I3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="J3" t="n">
-        <v>174.8497878494625</v>
+        <v>174.8497878494624</v>
       </c>
       <c r="K3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="L3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="M3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="N3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="O3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="P3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="Q3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="R3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="S3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="T3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="U3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="V3" t="n">
         <v>179.8601686415647</v>
       </c>
       <c r="W3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="X3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="Y3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="AA3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
       <c r="AB3" t="n">
-        <v>174.8708239417661</v>
+        <v>174.870823941766</v>
       </c>
     </row>
     <row r="4">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>356.9349044030645</v>
+        <v>356.934904403062</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0068989635771</v>
+        <v>131.006898963577</v>
       </c>
       <c r="D4" t="n">
-        <v>314.4977436936924</v>
+        <v>314.4977436936921</v>
       </c>
       <c r="E4" t="n">
-        <v>297.7116846244503</v>
+        <v>297.7116846244505</v>
       </c>
       <c r="F4" t="n">
-        <v>279.6357234524173</v>
+        <v>279.6357234524179</v>
       </c>
       <c r="G4" t="n">
-        <v>569.49735820115</v>
+        <v>569.4973582011488</v>
       </c>
       <c r="H4" t="n">
-        <v>478.0647475034278</v>
+        <v>478.0647475034285</v>
       </c>
       <c r="I4" t="n">
-        <v>246.9164055452851</v>
+        <v>246.9164055452853</v>
       </c>
       <c r="J4" t="n">
-        <v>525.2636762969087</v>
+        <v>525.2636762969084</v>
       </c>
       <c r="K4" t="n">
-        <v>384.3923519795349</v>
+        <v>384.3923519795346</v>
       </c>
       <c r="L4" t="n">
-        <v>476.5207575621219</v>
+        <v>476.520757562123</v>
       </c>
       <c r="M4" t="n">
-        <v>842.6542165648603</v>
+        <v>842.6542165648623</v>
       </c>
       <c r="N4" t="n">
         <v>604.7415612629551</v>
       </c>
       <c r="O4" t="n">
-        <v>448.6959241321855</v>
+        <v>448.6959241321858</v>
       </c>
       <c r="P4" t="n">
-        <v>650.1600245114832</v>
+        <v>650.1600245114844</v>
       </c>
       <c r="Q4" t="n">
-        <v>397.3134705915606</v>
+        <v>397.3134705915609</v>
       </c>
       <c r="R4" t="n">
-        <v>335.8955277841437</v>
+        <v>335.8955277841439</v>
       </c>
       <c r="S4" t="n">
-        <v>476.2155409717128</v>
+        <v>476.2155409717148</v>
       </c>
       <c r="T4" t="n">
-        <v>418.8534651336325</v>
+        <v>418.8534651336316</v>
       </c>
       <c r="U4" t="n">
-        <v>604.7415612629551</v>
+        <v>604.7415612629547</v>
       </c>
       <c r="V4" t="n">
-        <v>372.2384483728285</v>
+        <v>372.2384483728284</v>
       </c>
       <c r="W4" t="n">
-        <v>742.4581974083338</v>
+        <v>742.458197408333</v>
       </c>
       <c r="X4" t="n">
-        <v>439.6520527835086</v>
+        <v>439.6520527835096</v>
       </c>
       <c r="Y4" t="n">
-        <v>770.7399916562131</v>
+        <v>770.739991656213</v>
       </c>
       <c r="Z4" t="n">
-        <v>444.9939088565435</v>
+        <v>444.9939088565427</v>
       </c>
       <c r="AA4" t="n">
-        <v>389.2052035384045</v>
+        <v>389.2052035384056</v>
       </c>
       <c r="AB4" t="n">
-        <v>752.4791564410604</v>
+        <v>752.4791564410591</v>
       </c>
     </row>
     <row r="5">
@@ -2925,37 +2925,37 @@
         <v>10.54864171836104</v>
       </c>
       <c r="C5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="D5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="E5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="F5" t="n">
         <v>10.54864171836104</v>
       </c>
       <c r="G5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="H5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="I5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="J5" t="n">
         <v>10.54947137040704</v>
       </c>
       <c r="K5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="L5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="M5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="N5" t="n">
         <v>10.54864171836104</v>
@@ -2970,19 +2970,19 @@
         <v>10.54864171836104</v>
       </c>
       <c r="R5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="S5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="T5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="U5" t="n">
-        <v>10.43678153210747</v>
+        <v>10.4367815321074</v>
       </c>
       <c r="V5" t="n">
-        <v>10.55411774104406</v>
+        <v>10.55411774104403</v>
       </c>
       <c r="W5" t="n">
         <v>10.54864171836104</v>
@@ -2991,13 +2991,13 @@
         <v>10.54864171836104</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.43678153210747</v>
+        <v>10.4367815321074</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.54864171836102</v>
+        <v>10.54864171836104</v>
       </c>
       <c r="AB5" t="n">
         <v>10.54864171836104</v>
@@ -3010,82 +3010,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>825.6503431350561</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="C6" t="n">
-        <v>825.6503431350561</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="D6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="E6" t="n">
-        <v>689.6128486057689</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="F6" t="n">
-        <v>825.6503431350561</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="G6" t="n">
-        <v>825.6503431350561</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="H6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="I6" t="n">
-        <v>689.6128486057689</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="J6" t="n">
-        <v>825.6511727871024</v>
+        <v>825.6511727871023</v>
       </c>
       <c r="K6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="L6" t="n">
-        <v>689.6128486057689</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="M6" t="n">
-        <v>689.6128486057689</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="N6" t="n">
-        <v>689.6693632150386</v>
+        <v>689.6693632150387</v>
       </c>
       <c r="O6" t="n">
         <v>826.0256695888875</v>
       </c>
       <c r="P6" t="n">
-        <v>826.0250908043964</v>
+        <v>826.0250908043971</v>
       </c>
       <c r="Q6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="R6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="S6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="T6" t="n">
-        <v>825.6503431350561</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="U6" t="n">
-        <v>825.6503431350561</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="V6" t="n">
-        <v>825.6558191577394</v>
+        <v>825.6558191577392</v>
       </c>
       <c r="W6" t="n">
-        <v>826.0258169909852</v>
+        <v>826.0258169909853</v>
       </c>
       <c r="X6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="Y6" t="n">
-        <v>719.4594061393715</v>
+        <v>719.4594061393718</v>
       </c>
       <c r="Z6" t="n">
-        <v>689.6128486057689</v>
+        <v>825.6503431350563</v>
       </c>
       <c r="AA6" t="n">
-        <v>825.6503431350561</v>
+        <v>689.6128486057687</v>
       </c>
       <c r="AB6" t="n">
         <v>689.7394366082822</v>
@@ -3098,85 +3098,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="C7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="D7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="E7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="F7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="G7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="H7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="I7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="J7" t="n">
-        <v>17.66387147328879</v>
+        <v>17.6638714732888</v>
       </c>
       <c r="K7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="L7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="M7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="N7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="O7" t="n">
-        <v>17.66297024844054</v>
+        <v>17.6629702484405</v>
       </c>
       <c r="P7" t="n">
-        <v>17.66297024844054</v>
+        <v>17.6629702484405</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="R7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="S7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="T7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="U7" t="n">
-        <v>17.65976720905545</v>
+        <v>17.65976720905549</v>
       </c>
       <c r="V7" t="n">
-        <v>17.66851784392581</v>
+        <v>17.66851784392578</v>
       </c>
       <c r="W7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="X7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.66304182124281</v>
+        <v>17.66304182124279</v>
       </c>
     </row>
     <row r="8">
@@ -3186,85 +3186,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.66694148109617</v>
+        <v>20.66694148109619</v>
       </c>
       <c r="C8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="D8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="E8" t="n">
-        <v>28.3956003919128</v>
+        <v>24.28031750540348</v>
       </c>
       <c r="F8" t="n">
-        <v>21.87097621134026</v>
+        <v>21.87097621134027</v>
       </c>
       <c r="G8" t="n">
-        <v>28.3956003919128</v>
+        <v>29.99818816372528</v>
       </c>
       <c r="H8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="I8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="J8" t="n">
-        <v>28.39643004395876</v>
+        <v>28.3964300439588</v>
       </c>
       <c r="K8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="L8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="M8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.3956003919116</v>
       </c>
       <c r="N8" t="n">
-        <v>22.40459675663127</v>
+        <v>22.40459675663125</v>
       </c>
       <c r="O8" t="n">
-        <v>24.05097656868758</v>
+        <v>24.05097656868756</v>
       </c>
       <c r="P8" t="n">
-        <v>23.64740909526972</v>
+        <v>23.64740909526967</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.14808361021327</v>
+        <v>19.14808361021332</v>
       </c>
       <c r="R8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="S8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="T8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="U8" t="n">
-        <v>23.63745528906355</v>
+        <v>24.62086284707489</v>
       </c>
       <c r="V8" t="n">
-        <v>28.40107641459579</v>
+        <v>26.2859795146924</v>
       </c>
       <c r="W8" t="n">
         <v>28.39711928338684</v>
       </c>
       <c r="X8" t="n">
-        <v>19.85643054942401</v>
+        <v>19.85643054942402</v>
       </c>
       <c r="Y8" t="n">
         <v>36.07578357453112</v>
       </c>
       <c r="Z8" t="n">
-        <v>28.3956003919128</v>
+        <v>20.5233776749421</v>
       </c>
       <c r="AA8" t="n">
-        <v>28.3956003919128</v>
+        <v>28.39560039191282</v>
       </c>
       <c r="AB8" t="n">
-        <v>36.46883087348214</v>
+        <v>36.46883087348212</v>
       </c>
     </row>
     <row r="9">
@@ -3274,85 +3274,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.47703340206089</v>
+        <v>37.4770334020609</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="D9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="E9" t="n">
-        <v>45.48987367838829</v>
+        <v>43.64054457042557</v>
       </c>
       <c r="F9" t="n">
-        <v>45.48987367838829</v>
+        <v>27.01808697038359</v>
       </c>
       <c r="G9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987594570991</v>
       </c>
       <c r="H9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="I9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="J9" t="n">
-        <v>45.49070333043434</v>
+        <v>45.49070333043429</v>
       </c>
       <c r="K9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="L9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="M9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="N9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="O9" t="n">
-        <v>48.14532147275362</v>
+        <v>48.14532147275356</v>
       </c>
       <c r="P9" t="n">
         <v>48.72283531511324</v>
       </c>
       <c r="Q9" t="n">
-        <v>45.48987594570993</v>
+        <v>45.48987594570991</v>
       </c>
       <c r="R9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="S9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="T9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="U9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="V9" t="n">
-        <v>45.49534970107132</v>
+        <v>54.74198801515002</v>
       </c>
       <c r="W9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="X9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="Z9" t="n">
-        <v>45.48987367838829</v>
+        <v>40.65884442164975</v>
       </c>
       <c r="AA9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
       <c r="AB9" t="n">
-        <v>45.48987367838829</v>
+        <v>45.48987367838827</v>
       </c>
     </row>
     <row r="10">
@@ -3371,43 +3371,43 @@
         <v>168.6078857440523</v>
       </c>
       <c r="E10" t="n">
-        <v>154.9054701330351</v>
+        <v>154.9054701330353</v>
       </c>
       <c r="F10" t="n">
-        <v>169.3438405399137</v>
+        <v>169.3438405399136</v>
       </c>
       <c r="G10" t="n">
         <v>161.9234052651528</v>
       </c>
       <c r="H10" t="n">
-        <v>165.6267023745941</v>
+        <v>165.6267023745939</v>
       </c>
       <c r="I10" t="n">
-        <v>170.0597533847523</v>
+        <v>170.0597533847522</v>
       </c>
       <c r="J10" t="n">
         <v>163.320219185455</v>
       </c>
       <c r="K10" t="n">
-        <v>166.5394282016465</v>
+        <v>166.5394282016466</v>
       </c>
       <c r="L10" t="n">
-        <v>164.6640967910475</v>
+        <v>164.6640967910473</v>
       </c>
       <c r="M10" t="n">
-        <v>157.8714319784792</v>
+        <v>157.8714319784791</v>
       </c>
       <c r="N10" t="n">
         <v>163.995249506416</v>
       </c>
       <c r="O10" t="n">
-        <v>164.1436055524564</v>
+        <v>164.1436055524563</v>
       </c>
       <c r="P10" t="n">
-        <v>159.9793085974977</v>
+        <v>159.9793085974976</v>
       </c>
       <c r="Q10" t="n">
-        <v>166.6683758311894</v>
+        <v>166.6683758311893</v>
       </c>
       <c r="R10" t="n">
         <v>168.3458835213149</v>
@@ -3419,28 +3419,28 @@
         <v>166.4495580040764</v>
       </c>
       <c r="U10" t="n">
-        <v>161.5516710915688</v>
+        <v>161.5516710915687</v>
       </c>
       <c r="V10" t="n">
-        <v>171.0623472124629</v>
+        <v>171.062347212463</v>
       </c>
       <c r="W10" t="n">
-        <v>158.9900295739666</v>
+        <v>158.9900295739665</v>
       </c>
       <c r="X10" t="n">
-        <v>165.8569823412865</v>
+        <v>165.8569823412864</v>
       </c>
       <c r="Y10" t="n">
-        <v>158.1902329251984</v>
+        <v>158.1902329251983</v>
       </c>
       <c r="Z10" t="n">
-        <v>164.8251396869777</v>
+        <v>164.8251396869778</v>
       </c>
       <c r="AA10" t="n">
         <v>166.6403060672853</v>
       </c>
       <c r="AB10" t="n">
-        <v>160.3057798531088</v>
+        <v>160.3057798531087</v>
       </c>
     </row>
     <row r="11">
@@ -3450,22 +3450,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>170.3770282882065</v>
+        <v>170.3770282882064</v>
       </c>
       <c r="C11" t="n">
-        <v>171.4442212096394</v>
+        <v>171.4442212096395</v>
       </c>
       <c r="D11" t="n">
-        <v>170.3970037550322</v>
+        <v>170.3970037550321</v>
       </c>
       <c r="E11" t="n">
-        <v>156.9314030790584</v>
+        <v>156.9314030790585</v>
       </c>
       <c r="F11" t="n">
-        <v>170.6108524514629</v>
+        <v>170.6108524514628</v>
       </c>
       <c r="G11" t="n">
-        <v>168.4638750238935</v>
+        <v>168.4638750238934</v>
       </c>
       <c r="H11" t="n">
         <v>169.920527132875</v>
@@ -3480,25 +3480,25 @@
         <v>170.3358202928686</v>
       </c>
       <c r="L11" t="n">
-        <v>169.4825385247194</v>
+        <v>169.4825385247193</v>
       </c>
       <c r="M11" t="n">
         <v>167.3558717989058</v>
       </c>
       <c r="N11" t="n">
-        <v>169.0778865745402</v>
+        <v>169.0778865745401</v>
       </c>
       <c r="O11" t="n">
-        <v>169.2457133524534</v>
+        <v>169.2457133524533</v>
       </c>
       <c r="P11" t="n">
-        <v>167.3509449671202</v>
+        <v>167.35094496712</v>
       </c>
       <c r="Q11" t="n">
         <v>170.3944918752423</v>
       </c>
       <c r="R11" t="n">
-        <v>171.1577632201493</v>
+        <v>171.1577632201492</v>
       </c>
       <c r="S11" t="n">
         <v>169.2343589398209</v>
@@ -3513,22 +3513,22 @@
         <v>174.5658925233108</v>
       </c>
       <c r="W11" t="n">
-        <v>166.9008198587684</v>
+        <v>166.9008198587683</v>
       </c>
       <c r="X11" t="n">
-        <v>170.0253052515788</v>
+        <v>170.0253052515789</v>
       </c>
       <c r="Y11" t="n">
-        <v>166.5369098347782</v>
+        <v>166.5369098347781</v>
       </c>
       <c r="Z11" t="n">
         <v>169.2970816007027</v>
       </c>
       <c r="AA11" t="n">
-        <v>170.3817200432129</v>
+        <v>170.3817200432128</v>
       </c>
       <c r="AB11" t="n">
-        <v>167.4994904288253</v>
+        <v>167.4994904288252</v>
       </c>
     </row>
   </sheetData>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="C2" t="n">
-        <v>172.4416887691393</v>
+        <v>172.4416887691392</v>
       </c>
       <c r="D2" t="n">
         <v>173.0586211577409</v>
@@ -3712,19 +3712,19 @@
         <v>173.8710147802991</v>
       </c>
       <c r="H2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="I2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="J2" t="n">
-        <v>173.5940990261327</v>
+        <v>173.5940990261325</v>
       </c>
       <c r="K2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="L2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="M2" t="n">
         <v>174.4246563088034</v>
@@ -3733,46 +3733,46 @@
         <v>173.3052888590005</v>
       </c>
       <c r="O2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="P2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="Q2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="R2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="S2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="T2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="U2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="V2" t="n">
         <v>178.1013161285377</v>
       </c>
       <c r="W2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="X2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.2656150003541</v>
+        <v>173.2656150003542</v>
       </c>
       <c r="AA2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
       <c r="AB2" t="n">
-        <v>173.6119078076354</v>
+        <v>173.6119078076355</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>174.4843539571189</v>
       </c>
       <c r="E3" t="n">
-        <v>160.9838596077795</v>
+        <v>160.9838596077797</v>
       </c>
       <c r="F3" t="n">
         <v>174.4843539571189</v>
@@ -3806,7 +3806,7 @@
         <v>174.4843539571189</v>
       </c>
       <c r="J3" t="n">
-        <v>174.4665431069786</v>
+        <v>174.4665431069785</v>
       </c>
       <c r="K3" t="n">
         <v>174.4843539571189</v>
@@ -3870,82 +3870,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>277.767813066058</v>
+        <v>277.7678130660582</v>
       </c>
       <c r="C4" t="n">
-        <v>169.7300768973824</v>
+        <v>169.7300768973826</v>
       </c>
       <c r="D4" t="n">
-        <v>341.300469605519</v>
+        <v>341.3004696055203</v>
       </c>
       <c r="E4" t="n">
-        <v>238.8203584332286</v>
+        <v>238.8203584332289</v>
       </c>
       <c r="F4" t="n">
-        <v>252.5496092645987</v>
+        <v>252.5496092645983</v>
       </c>
       <c r="G4" t="n">
-        <v>497.9440503271051</v>
+        <v>497.9440503271059</v>
       </c>
       <c r="H4" t="n">
-        <v>405.6978012370685</v>
+        <v>405.697801237068</v>
       </c>
       <c r="I4" t="n">
-        <v>284.1601716712339</v>
+        <v>284.160171671234</v>
       </c>
       <c r="J4" t="n">
-        <v>453.4720710448785</v>
+        <v>453.4720710448789</v>
       </c>
       <c r="K4" t="n">
-        <v>289.6201328988254</v>
+        <v>289.6201328988263</v>
       </c>
       <c r="L4" t="n">
-        <v>389.9617624049982</v>
+        <v>389.9617624049986</v>
       </c>
       <c r="M4" t="n">
-        <v>710.9084020259065</v>
+        <v>710.9084020259072</v>
       </c>
       <c r="N4" t="n">
-        <v>452.7735300074975</v>
+        <v>452.7735300074996</v>
       </c>
       <c r="O4" t="n">
-        <v>400.0025454684053</v>
+        <v>400.0025454684059</v>
       </c>
       <c r="P4" t="n">
-        <v>580.8012010653515</v>
+        <v>580.8012010653548</v>
       </c>
       <c r="Q4" t="n">
-        <v>314.2527840607789</v>
+        <v>314.2527840607793</v>
       </c>
       <c r="R4" t="n">
-        <v>269.4996005855097</v>
+        <v>269.4996005855096</v>
       </c>
       <c r="S4" t="n">
-        <v>411.980192735366</v>
+        <v>411.9801927353667</v>
       </c>
       <c r="T4" t="n">
-        <v>396.5368774405634</v>
+        <v>396.5368774405645</v>
       </c>
       <c r="U4" t="n">
-        <v>452.7735300074975</v>
+        <v>452.7735300074996</v>
       </c>
       <c r="V4" t="n">
-        <v>332.2785252696237</v>
+        <v>332.2785252696245</v>
       </c>
       <c r="W4" t="n">
-        <v>635.3250691141176</v>
+        <v>635.3250691141158</v>
       </c>
       <c r="X4" t="n">
-        <v>478.283244547931</v>
+        <v>478.2832445479322</v>
       </c>
       <c r="Y4" t="n">
-        <v>717.7809423618326</v>
+        <v>717.7809423618339</v>
       </c>
       <c r="Z4" t="n">
-        <v>339.8260485714776</v>
+        <v>339.8260485714773</v>
       </c>
       <c r="AA4" t="n">
-        <v>367.2076325057167</v>
+        <v>367.2076325057172</v>
       </c>
       <c r="AB4" t="n">
         <v>666.4704441334439</v>
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084427</v>
       </c>
       <c r="C5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="D5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="E5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="F5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
       <c r="G5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="H5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="I5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="J5" t="n">
-        <v>9.77509426897576</v>
+        <v>9.775094268975728</v>
       </c>
       <c r="K5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="L5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="M5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="N5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
       <c r="O5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
       <c r="P5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
       <c r="R5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="S5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="T5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="U5" t="n">
-        <v>9.666011346527554</v>
+        <v>9.666011346527513</v>
       </c>
       <c r="V5" t="n">
-        <v>9.782784228592115</v>
+        <v>9.78278422859211</v>
       </c>
       <c r="W5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084447</v>
       </c>
       <c r="X5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.666011346527554</v>
+        <v>9.666011346527513</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.773693675084466</v>
+        <v>9.773693675084445</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.773693675084465</v>
+        <v>9.773693675084429</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>768.9312167181438</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="C6" t="n">
-        <v>642.4586746385293</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="D6" t="n">
-        <v>768.9312167181438</v>
+        <v>768.931216718144</v>
       </c>
       <c r="E6" t="n">
-        <v>642.4586746385293</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="F6" t="n">
-        <v>642.4586746385293</v>
+        <v>768.931216718144</v>
       </c>
       <c r="G6" t="n">
-        <v>768.9312167181438</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="H6" t="n">
-        <v>642.4586746385293</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="I6" t="n">
-        <v>768.9312167181438</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="J6" t="n">
-        <v>768.9326173120349</v>
+        <v>768.9326173120353</v>
       </c>
       <c r="K6" t="n">
-        <v>642.4586746385293</v>
+        <v>768.931216718144</v>
       </c>
       <c r="L6" t="n">
-        <v>768.9312167181438</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="M6" t="n">
-        <v>768.9312167181438</v>
+        <v>768.931216718144</v>
       </c>
       <c r="N6" t="n">
-        <v>642.5121334188535</v>
+        <v>642.5121334188539</v>
       </c>
       <c r="O6" t="n">
-        <v>769.2919380158999</v>
+        <v>642.5121334188534</v>
       </c>
       <c r="P6" t="n">
         <v>769.2906016116608</v>
       </c>
       <c r="Q6" t="n">
-        <v>768.9312167181438</v>
+        <v>768.931216718144</v>
       </c>
       <c r="R6" t="n">
-        <v>768.9312167181438</v>
+        <v>768.931216718144</v>
       </c>
       <c r="S6" t="n">
-        <v>642.4586746385293</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="T6" t="n">
-        <v>642.4586746385293</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="U6" t="n">
-        <v>768.9312167181438</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="V6" t="n">
-        <v>768.9403072716516</v>
+        <v>768.9403072716526</v>
       </c>
       <c r="W6" t="n">
-        <v>769.292116622179</v>
+        <v>674.8420479366528</v>
       </c>
       <c r="X6" t="n">
-        <v>642.4586746385293</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="Y6" t="n">
-        <v>670.2644794942513</v>
+        <v>670.2644794942511</v>
       </c>
       <c r="Z6" t="n">
-        <v>768.9312167181438</v>
+        <v>642.4586746385303</v>
       </c>
       <c r="AA6" t="n">
-        <v>642.4586746385293</v>
+        <v>768.931216718144</v>
       </c>
       <c r="AB6" t="n">
-        <v>642.5785305766007</v>
+        <v>642.5785305766005</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="C7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="D7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="E7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="F7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="G7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="H7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="I7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="J7" t="n">
-        <v>15.99019068781817</v>
+        <v>15.99019068781815</v>
       </c>
       <c r="K7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="L7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="M7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="N7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="O7" t="n">
-        <v>15.98874792295023</v>
+        <v>15.98874792295021</v>
       </c>
       <c r="P7" t="n">
-        <v>15.98874792295023</v>
+        <v>15.98874792295021</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="R7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="S7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="T7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="U7" t="n">
-        <v>15.95949106720444</v>
+        <v>15.9594910672044</v>
       </c>
       <c r="V7" t="n">
-        <v>15.99788064743454</v>
+        <v>15.99788064743453</v>
       </c>
       <c r="W7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="X7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.98879009392688</v>
+        <v>15.98879009392687</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.53527184631306</v>
+        <v>18.53527184631302</v>
       </c>
       <c r="C8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="E8" t="n">
-        <v>25.2300113464046</v>
+        <v>21.66526004722119</v>
       </c>
       <c r="F8" t="n">
-        <v>19.57823401616067</v>
+        <v>19.57823401616065</v>
       </c>
       <c r="G8" t="n">
-        <v>25.2300113464046</v>
+        <v>26.61820919310625</v>
       </c>
       <c r="H8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="I8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="J8" t="n">
-        <v>25.23141194029589</v>
+        <v>25.23141194029592</v>
       </c>
       <c r="K8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="L8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="M8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640314</v>
       </c>
       <c r="N8" t="n">
-        <v>20.04046822562981</v>
+        <v>20.04046822562979</v>
       </c>
       <c r="O8" t="n">
         <v>21.4665997297921</v>
       </c>
       <c r="P8" t="n">
-        <v>21.11702043852783</v>
+        <v>21.11702043852785</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.21960273747768</v>
+        <v>17.21960273747765</v>
       </c>
       <c r="R8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="S8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="T8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="U8" t="n">
-        <v>21.08912729486044</v>
+        <v>21.93972499881269</v>
       </c>
       <c r="V8" t="n">
-        <v>25.23910189991225</v>
+        <v>23.38432060789629</v>
       </c>
       <c r="W8" t="n">
-        <v>25.2313270439901</v>
+        <v>25.23132704399007</v>
       </c>
       <c r="X8" t="n">
-        <v>17.83318890881489</v>
+        <v>17.8331889088149</v>
       </c>
       <c r="Y8" t="n">
-        <v>31.84765094966423</v>
+        <v>31.84765094966426</v>
       </c>
       <c r="Z8" t="n">
-        <v>25.2300113464046</v>
+        <v>18.41091362397569</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.2300113464046</v>
+        <v>25.23001134640461</v>
       </c>
       <c r="AB8" t="n">
-        <v>32.22322654933227</v>
+        <v>32.22322654933225</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.92540632498245</v>
+        <v>31.92540632498247</v>
       </c>
       <c r="C9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="D9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="E9" t="n">
-        <v>38.54242339536945</v>
+        <v>37.01524421429304</v>
       </c>
       <c r="F9" t="n">
-        <v>38.54242339536945</v>
+        <v>23.28839077068996</v>
       </c>
       <c r="G9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242517441299</v>
       </c>
       <c r="H9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="I9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="J9" t="n">
-        <v>38.54382398926074</v>
+        <v>38.54382398926073</v>
       </c>
       <c r="K9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="L9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="M9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="N9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="O9" t="n">
-        <v>40.73529655686777</v>
+        <v>40.7352965568678</v>
       </c>
       <c r="P9" t="n">
-        <v>41.21220845921508</v>
+        <v>41.21220845921506</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.54242517441297</v>
+        <v>38.54242517441299</v>
       </c>
       <c r="R9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="S9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="T9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="U9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="V9" t="n">
-        <v>38.55151394887712</v>
+        <v>46.18740323766734</v>
       </c>
       <c r="W9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="X9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="Y9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="Z9" t="n">
-        <v>38.54242339536945</v>
+        <v>34.55295121648078</v>
       </c>
       <c r="AA9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
       <c r="AB9" t="n">
-        <v>38.54242339536945</v>
+        <v>38.54242339536941</v>
       </c>
     </row>
     <row r="10">
@@ -4398,19 +4398,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167.7611223522586</v>
+        <v>167.7611223522587</v>
       </c>
       <c r="C10" t="n">
         <v>170.6931301059023</v>
       </c>
       <c r="D10" t="n">
-        <v>167.0838238663995</v>
+        <v>167.0838238663996</v>
       </c>
       <c r="E10" t="n">
-        <v>155.6010916488672</v>
+        <v>155.6010916488669</v>
       </c>
       <c r="F10" t="n">
-        <v>169.0510921994534</v>
+        <v>169.0510921994535</v>
       </c>
       <c r="G10" t="n">
         <v>162.1417949019655</v>
@@ -4422,7 +4422,7 @@
         <v>168.4693440183496</v>
       </c>
       <c r="J10" t="n">
-        <v>163.7291745976885</v>
+        <v>163.7291745976884</v>
       </c>
       <c r="K10" t="n">
         <v>167.473877085986</v>
@@ -4431,13 +4431,13 @@
         <v>165.5002701120619</v>
       </c>
       <c r="M10" t="n">
-        <v>159.1406904196469</v>
+        <v>159.140690419647</v>
       </c>
       <c r="N10" t="n">
         <v>165.6015263838367</v>
       </c>
       <c r="O10" t="n">
-        <v>164.1233836227297</v>
+        <v>164.1233836227298</v>
       </c>
       <c r="P10" t="n">
         <v>160.0293151481321</v>
@@ -4446,13 +4446,13 @@
         <v>167.4004375865369</v>
       </c>
       <c r="R10" t="n">
-        <v>168.8940893244333</v>
+        <v>168.8940893244335</v>
       </c>
       <c r="S10" t="n">
-        <v>164.4257851856503</v>
+        <v>164.4257851856504</v>
       </c>
       <c r="T10" t="n">
-        <v>165.9448728823921</v>
+        <v>165.9448728823922</v>
       </c>
       <c r="U10" t="n">
         <v>163.6939370201211</v>
@@ -4461,10 +4461,10 @@
         <v>170.8874304928016</v>
       </c>
       <c r="W10" t="n">
-        <v>159.9240078313837</v>
+        <v>159.9240078313838</v>
       </c>
       <c r="X10" t="n">
-        <v>163.8700594944949</v>
+        <v>163.8700594944948</v>
       </c>
       <c r="Y10" t="n">
         <v>157.8632026588886</v>
@@ -4476,7 +4476,7 @@
         <v>166.1707837711701</v>
       </c>
       <c r="AB10" t="n">
-        <v>160.7018732501549</v>
+        <v>160.701873250155</v>
       </c>
     </row>
     <row r="11">
@@ -4489,28 +4489,28 @@
         <v>170.5528160017562</v>
       </c>
       <c r="C11" t="n">
-        <v>170.7166698349221</v>
+        <v>170.7166698349222</v>
       </c>
       <c r="D11" t="n">
         <v>169.6913563823735</v>
       </c>
       <c r="E11" t="n">
-        <v>156.9666102291368</v>
+        <v>156.9666102291365</v>
       </c>
       <c r="F11" t="n">
-        <v>170.2551677830415</v>
+        <v>170.2551677830416</v>
       </c>
       <c r="G11" t="n">
-        <v>168.2551110768024</v>
+        <v>168.2551110768025</v>
       </c>
       <c r="H11" t="n">
-        <v>169.8158376079672</v>
+        <v>169.8158376079673</v>
       </c>
       <c r="I11" t="n">
         <v>170.8750591167961</v>
       </c>
       <c r="J11" t="n">
-        <v>168.7085621364425</v>
+        <v>168.7085621364424</v>
       </c>
       <c r="K11" t="n">
         <v>170.4221184902059</v>
@@ -4519,13 +4519,13 @@
         <v>169.524121027558</v>
       </c>
       <c r="M11" t="n">
-        <v>167.4432405018993</v>
+        <v>167.4432405018994</v>
       </c>
       <c r="N11" t="n">
         <v>169.2635740052652</v>
       </c>
       <c r="O11" t="n">
-        <v>168.8976332870351</v>
+        <v>168.8976332870352</v>
       </c>
       <c r="P11" t="n">
         <v>167.034819084071</v>
@@ -4534,13 +4534,13 @@
         <v>170.3887032839186</v>
       </c>
       <c r="R11" t="n">
-        <v>171.0683195846471</v>
+        <v>171.0683195846472</v>
       </c>
       <c r="S11" t="n">
         <v>169.0352269618606</v>
       </c>
       <c r="T11" t="n">
-        <v>169.7264167049232</v>
+        <v>169.7264167049233</v>
       </c>
       <c r="U11" t="n">
         <v>168.702233714283</v>
@@ -4552,7 +4552,7 @@
         <v>166.986903919356</v>
       </c>
       <c r="X11" t="n">
-        <v>168.7823700013921</v>
+        <v>168.7823700013922</v>
       </c>
       <c r="Y11" t="n">
         <v>166.0492309984745</v>
@@ -4561,10 +4561,10 @@
         <v>169.2897498754108</v>
       </c>
       <c r="AA11" t="n">
-        <v>169.8292068792525</v>
+        <v>169.8292068792526</v>
       </c>
       <c r="AB11" t="n">
-        <v>167.3408351638071</v>
+        <v>167.340835163807</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="C2" t="n">
-        <v>172.0422499691996</v>
+        <v>172.0422499691997</v>
       </c>
       <c r="D2" t="n">
-        <v>172.3380466904759</v>
+        <v>172.3380466904758</v>
       </c>
       <c r="E2" t="n">
-        <v>158.6838411423721</v>
+        <v>158.683841142372</v>
       </c>
       <c r="F2" t="n">
-        <v>172.5859908225756</v>
+        <v>172.5859908225757</v>
       </c>
       <c r="G2" t="n">
         <v>173.2564779418284</v>
       </c>
       <c r="H2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="I2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="J2" t="n">
-        <v>173.0338853532493</v>
+        <v>173.0338853532495</v>
       </c>
       <c r="K2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="L2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="M2" t="n">
         <v>173.766166175471</v>
       </c>
       <c r="N2" t="n">
-        <v>172.6959707826057</v>
+        <v>172.6959707826056</v>
       </c>
       <c r="O2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="P2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="Q2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="R2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="S2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="T2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="U2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="V2" t="n">
         <v>177.5476489041246</v>
       </c>
       <c r="W2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="X2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="Z2" t="n">
-        <v>172.4725906901628</v>
+        <v>172.4725906901627</v>
       </c>
       <c r="AA2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
       <c r="AB2" t="n">
-        <v>173.0471444662007</v>
+        <v>173.0471444662006</v>
       </c>
     </row>
     <row r="3">
@@ -4827,7 +4827,7 @@
         <v>174.0528283562179</v>
       </c>
       <c r="E3" t="n">
-        <v>160.6435054612336</v>
+        <v>160.6435054612334</v>
       </c>
       <c r="F3" t="n">
         <v>174.0528283562179</v>
@@ -4878,7 +4878,7 @@
         <v>174.0528283562179</v>
       </c>
       <c r="V3" t="n">
-        <v>178.9601424670095</v>
+        <v>178.9601424670093</v>
       </c>
       <c r="W3" t="n">
         <v>174.0528283562179</v>
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>247.4400685062077</v>
+        <v>247.4400685062081</v>
       </c>
       <c r="C4" t="n">
-        <v>174.4725487222873</v>
+        <v>174.4725487222875</v>
       </c>
       <c r="D4" t="n">
-        <v>253.1886674865338</v>
+        <v>253.1886674865342</v>
       </c>
       <c r="E4" t="n">
-        <v>131.4855186270236</v>
+        <v>131.4855186270239</v>
       </c>
       <c r="F4" t="n">
-        <v>323.3137619976876</v>
+        <v>323.3137619976875</v>
       </c>
       <c r="G4" t="n">
-        <v>437.6703405279162</v>
+        <v>437.6703405279171</v>
       </c>
       <c r="H4" t="n">
-        <v>379.431418412095</v>
+        <v>379.4314184120958</v>
       </c>
       <c r="I4" t="n">
-        <v>342.7400225256941</v>
+        <v>342.7400225256943</v>
       </c>
       <c r="J4" t="n">
-        <v>411.480581760431</v>
+        <v>411.4805817604313</v>
       </c>
       <c r="K4" t="n">
-        <v>389.2799810275637</v>
+        <v>389.2799810275666</v>
       </c>
       <c r="L4" t="n">
-        <v>390.5246834422496</v>
+        <v>390.5246834422501</v>
       </c>
       <c r="M4" t="n">
-        <v>620.6577956517893</v>
+        <v>620.6577956517898</v>
       </c>
       <c r="N4" t="n">
-        <v>410.0253401989967</v>
+        <v>410.0253401989943</v>
       </c>
       <c r="O4" t="n">
-        <v>325.6895860551385</v>
+        <v>325.6895860551381</v>
       </c>
       <c r="P4" t="n">
-        <v>500.2067416771126</v>
+        <v>500.2067416771132</v>
       </c>
       <c r="Q4" t="n">
         <v>339.9434484293701</v>
       </c>
       <c r="R4" t="n">
-        <v>300.9353675747413</v>
+        <v>300.9353675747417</v>
       </c>
       <c r="S4" t="n">
-        <v>422.5054216978519</v>
+        <v>422.5054216978526</v>
       </c>
       <c r="T4" t="n">
-        <v>410.9193487363168</v>
+        <v>410.9193487363166</v>
       </c>
       <c r="U4" t="n">
-        <v>410.0253401989961</v>
+        <v>410.0253401989945</v>
       </c>
       <c r="V4" t="n">
-        <v>308.7334314424424</v>
+        <v>308.7334314424425</v>
       </c>
       <c r="W4" t="n">
-        <v>600.7105926703191</v>
+        <v>600.7105926703193</v>
       </c>
       <c r="X4" t="n">
-        <v>485.5630374056607</v>
+        <v>485.563037405664</v>
       </c>
       <c r="Y4" t="n">
-        <v>694.4972295849738</v>
+        <v>694.4972295849743</v>
       </c>
       <c r="Z4" t="n">
-        <v>243.5252686699229</v>
+        <v>243.525268669923</v>
       </c>
       <c r="AA4" t="n">
-        <v>405.7719990786951</v>
+        <v>405.771999078696</v>
       </c>
       <c r="AB4" t="n">
-        <v>601.5981422143478</v>
+        <v>601.5981422143483</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="C5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="D5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="E5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="F5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="G5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="H5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="I5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="J5" t="n">
         <v>9.121013404914883</v>
       </c>
       <c r="K5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="L5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="M5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="N5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="O5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="P5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="R5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="S5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="T5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="U5" t="n">
-        <v>8.995197854934444</v>
+        <v>8.995197854934448</v>
       </c>
       <c r="V5" t="n">
-        <v>9.13306687746088</v>
+        <v>9.133066877460879</v>
       </c>
       <c r="W5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="X5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.995197854934444</v>
+        <v>8.995197854934448</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.11880744406167</v>
+        <v>9.118807444061666</v>
       </c>
     </row>
     <row r="6">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>641.6752916590423</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="C6" t="n">
         <v>641.6752916590423</v>
@@ -5091,76 +5091,76 @@
         <v>641.6752916590423</v>
       </c>
       <c r="E6" t="n">
-        <v>641.6752916590423</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="F6" t="n">
         <v>641.6752916590423</v>
       </c>
       <c r="G6" t="n">
+        <v>767.8060755657004</v>
+      </c>
+      <c r="H6" t="n">
         <v>641.6752916590423</v>
-      </c>
-      <c r="H6" t="n">
-        <v>767.8060755657003</v>
       </c>
       <c r="I6" t="n">
         <v>641.6752916590423</v>
       </c>
       <c r="J6" t="n">
-        <v>641.6774976198956</v>
+        <v>767.808281526554</v>
       </c>
       <c r="K6" t="n">
-        <v>767.8060755657003</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="L6" t="n">
-        <v>641.6752916590423</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="M6" t="n">
         <v>641.6752916590423</v>
       </c>
       <c r="N6" t="n">
-        <v>641.7536827144243</v>
+        <v>641.7536827144244</v>
       </c>
       <c r="O6" t="n">
-        <v>641.7536827144243</v>
+        <v>768.1853991290305</v>
       </c>
       <c r="P6" t="n">
-        <v>768.1836011545295</v>
+        <v>605.1305959871619</v>
       </c>
       <c r="Q6" t="n">
-        <v>767.8060755657003</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="R6" t="n">
-        <v>767.8060755657003</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="S6" t="n">
-        <v>767.8060755657003</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="T6" t="n">
+        <v>767.8060755657004</v>
+      </c>
+      <c r="U6" t="n">
         <v>641.6752916590423</v>
       </c>
-      <c r="U6" t="n">
-        <v>767.8060755657003</v>
-      </c>
       <c r="V6" t="n">
-        <v>767.8203349991002</v>
+        <v>641.6895510924417</v>
       </c>
       <c r="W6" t="n">
-        <v>768.1856693420683</v>
+        <v>768.1856693420682</v>
       </c>
       <c r="X6" t="n">
         <v>641.6752916590423</v>
       </c>
       <c r="Y6" t="n">
-        <v>669.5008332204492</v>
+        <v>669.5008332204488</v>
       </c>
       <c r="Z6" t="n">
-        <v>767.8060755657003</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="AA6" t="n">
-        <v>767.8060755657003</v>
+        <v>767.8060755657004</v>
       </c>
       <c r="AB6" t="n">
-        <v>641.8113864672903</v>
+        <v>641.8113864672907</v>
       </c>
     </row>
     <row r="7">
@@ -5170,43 +5170,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="C7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="D7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="E7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="F7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="G7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="H7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="I7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="J7" t="n">
-        <v>15.04233190061235</v>
+        <v>15.04233190061234</v>
       </c>
       <c r="K7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="L7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="M7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="N7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="O7" t="n">
         <v>15.04011801769622</v>
@@ -5215,40 +5215,40 @@
         <v>15.04011801769622</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="R7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="S7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="T7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="U7" t="n">
         <v>14.96242846239987</v>
       </c>
       <c r="V7" t="n">
-        <v>15.05438537315835</v>
+        <v>15.05438537315833</v>
       </c>
       <c r="W7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="X7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.04012593975913</v>
+        <v>15.04012593975912</v>
       </c>
     </row>
     <row r="8">
@@ -5261,79 +5261,79 @@
         <v>17.40093943717711</v>
       </c>
       <c r="C8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="D8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="E8" t="n">
-        <v>23.73568380634057</v>
+        <v>20.36261929514377</v>
       </c>
       <c r="F8" t="n">
-        <v>18.38781857300502</v>
+        <v>18.38781857300501</v>
       </c>
       <c r="G8" t="n">
-        <v>23.73568380634057</v>
+        <v>25.0492343175027</v>
       </c>
       <c r="H8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="I8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="J8" t="n">
-        <v>23.73788976719378</v>
+        <v>23.73788976719377</v>
       </c>
       <c r="K8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="L8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="M8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380633811</v>
       </c>
       <c r="N8" t="n">
-        <v>18.82519713796863</v>
+        <v>18.82519713796862</v>
       </c>
       <c r="O8" t="n">
-        <v>20.17464150610963</v>
+        <v>20.17464150610962</v>
       </c>
       <c r="P8" t="n">
-        <v>19.84386008488764</v>
+        <v>19.84386008488763</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.15601758799856</v>
+        <v>16.15601758799857</v>
       </c>
       <c r="R8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="S8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="T8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="U8" t="n">
-        <v>19.78107798855656</v>
+        <v>20.58357212426627</v>
       </c>
       <c r="V8" t="n">
-        <v>23.74994323973979</v>
+        <v>21.95215497267754</v>
       </c>
       <c r="W8" t="n">
-        <v>23.73692875478019</v>
+        <v>23.73692875478015</v>
       </c>
       <c r="X8" t="n">
-        <v>16.73660949039638</v>
+        <v>16.73660949039637</v>
       </c>
       <c r="Y8" t="n">
-        <v>29.93117842925143</v>
+        <v>29.93117842925142</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.73568380634057</v>
+        <v>17.28326830920181</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.73568380634057</v>
+        <v>23.73568380634055</v>
       </c>
       <c r="AB8" t="n">
         <v>30.35285399290554</v>
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.57801027866565</v>
+        <v>28.5780102786656</v>
       </c>
       <c r="C9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="D9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="E9" t="n">
-        <v>34.4263052519991</v>
+        <v>33.07654318905592</v>
       </c>
       <c r="F9" t="n">
-        <v>34.4263052519991</v>
+        <v>20.9443882334259</v>
       </c>
       <c r="G9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630598280802</v>
       </c>
       <c r="H9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="I9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="J9" t="n">
-        <v>34.4285112128523</v>
+        <v>34.42851121285229</v>
       </c>
       <c r="K9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="L9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="M9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="N9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="O9" t="n">
-        <v>36.36442352147135</v>
+        <v>36.36442352147136</v>
       </c>
       <c r="P9" t="n">
-        <v>36.78593083363384</v>
+        <v>36.78593083363386</v>
       </c>
       <c r="Q9" t="n">
         <v>34.42630598280802</v>
       </c>
       <c r="R9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="S9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="T9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="U9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="V9" t="n">
-        <v>34.44056468539829</v>
+        <v>41.18936472638176</v>
       </c>
       <c r="W9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="X9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="Y9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="Z9" t="n">
-        <v>34.4263052519991</v>
+        <v>30.90030372395531</v>
       </c>
       <c r="AA9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
       <c r="AB9" t="n">
-        <v>34.4263052519991</v>
+        <v>34.42630525199905</v>
       </c>
     </row>
     <row r="10">
@@ -5434,61 +5434,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167.8746295892816</v>
+        <v>167.8746295892815</v>
       </c>
       <c r="C10" t="n">
-        <v>170.1007564601643</v>
+        <v>170.1007564601642</v>
       </c>
       <c r="D10" t="n">
         <v>168.3726987213202</v>
       </c>
       <c r="E10" t="n">
-        <v>157.5946307562302</v>
+        <v>157.5946307562303</v>
       </c>
       <c r="F10" t="n">
         <v>166.9551758760283</v>
       </c>
       <c r="G10" t="n">
-        <v>162.82613028251</v>
+        <v>162.8261302825098</v>
       </c>
       <c r="H10" t="n">
-        <v>166.276017669797</v>
+        <v>166.2760176697969</v>
       </c>
       <c r="I10" t="n">
         <v>166.6037282248955</v>
       </c>
       <c r="J10" t="n">
-        <v>164.1287674896906</v>
+        <v>164.1287674896905</v>
       </c>
       <c r="K10" t="n">
         <v>164.5130714065335</v>
       </c>
       <c r="L10" t="n">
-        <v>164.6667402706746</v>
+        <v>164.6667402706744</v>
       </c>
       <c r="M10" t="n">
-        <v>160.0607552091219</v>
+        <v>160.0607552091218</v>
       </c>
       <c r="N10" t="n">
         <v>166.2432352440477</v>
       </c>
       <c r="O10" t="n">
-        <v>165.6703825827827</v>
+        <v>165.6703825827825</v>
       </c>
       <c r="P10" t="n">
-        <v>161.1562346870106</v>
+        <v>161.1562346870103</v>
       </c>
       <c r="Q10" t="n">
-        <v>166.1479625869415</v>
+        <v>166.1479625869413</v>
       </c>
       <c r="R10" t="n">
-        <v>167.7733284137084</v>
+        <v>167.7733284137083</v>
       </c>
       <c r="S10" t="n">
         <v>163.5644446113516</v>
       </c>
       <c r="T10" t="n">
-        <v>165.1934837869549</v>
+        <v>165.1934837869547</v>
       </c>
       <c r="U10" t="n">
         <v>163.9170543279785</v>
@@ -5497,10 +5497,10 @@
         <v>170.9450350460434</v>
       </c>
       <c r="W10" t="n">
-        <v>160.3076344697277</v>
+        <v>160.3076344697276</v>
       </c>
       <c r="X10" t="n">
-        <v>162.9019980166128</v>
+        <v>162.9019980166125</v>
       </c>
       <c r="Y10" t="n">
         <v>158.2962349688627</v>
@@ -5509,7 +5509,7 @@
         <v>167.4906458099147</v>
       </c>
       <c r="AA10" t="n">
-        <v>164.8823836550598</v>
+        <v>164.8823836550596</v>
       </c>
       <c r="AB10" t="n">
         <v>161.4295242315821</v>
@@ -5525,7 +5525,7 @@
         <v>170.2360443384935</v>
       </c>
       <c r="C11" t="n">
-        <v>170.2440446619894</v>
+        <v>170.2440446619893</v>
       </c>
       <c r="D11" t="n">
         <v>169.7535696050982</v>
@@ -5534,13 +5534,13 @@
         <v>157.2965934354085</v>
       </c>
       <c r="F11" t="n">
-        <v>169.356536325213</v>
+        <v>169.3565363252131</v>
       </c>
       <c r="G11" t="n">
-        <v>168.1482945409274</v>
+        <v>168.1482945409272</v>
       </c>
       <c r="H11" t="n">
-        <v>169.5086708206541</v>
+        <v>169.508670820654</v>
       </c>
       <c r="I11" t="n">
         <v>169.6577801675754</v>
@@ -5549,10 +5549,10 @@
         <v>168.5244396745851</v>
       </c>
       <c r="K11" t="n">
-        <v>168.7065246526928</v>
+        <v>168.7065246526927</v>
       </c>
       <c r="L11" t="n">
-        <v>168.7764444755908</v>
+        <v>168.7764444755907</v>
       </c>
       <c r="M11" t="n">
         <v>167.3997283034509</v>
@@ -5561,13 +5561,13 @@
         <v>169.1425810288716</v>
       </c>
       <c r="O11" t="n">
-        <v>169.2331049260181</v>
+        <v>169.233104926018</v>
       </c>
       <c r="P11" t="n">
-        <v>167.1791532477061</v>
+        <v>167.1791532477059</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.4504053498676</v>
+        <v>169.4504053498675</v>
       </c>
       <c r="R11" t="n">
         <v>170.18995198078</v>
@@ -5576,7 +5576,7 @@
         <v>168.2748964377907</v>
       </c>
       <c r="T11" t="n">
-        <v>169.0161144541302</v>
+        <v>169.0161144541301</v>
       </c>
       <c r="U11" t="n">
         <v>168.4353349825565</v>
@@ -5588,7 +5588,7 @@
         <v>166.7930374445139</v>
       </c>
       <c r="X11" t="n">
-        <v>167.9734811260927</v>
+        <v>167.9734811260925</v>
       </c>
       <c r="Y11" t="n">
         <v>165.8778442616704</v>
@@ -5766,85 +5766,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="C2" t="n">
-        <v>171.1986953503229</v>
+        <v>171.198695350323</v>
       </c>
       <c r="D2" t="n">
-        <v>171.5128143324219</v>
+        <v>171.512814332422</v>
       </c>
       <c r="E2" t="n">
         <v>158.7847450989996</v>
       </c>
       <c r="F2" t="n">
-        <v>171.4155412076396</v>
+        <v>171.4155412076397</v>
       </c>
       <c r="G2" t="n">
-        <v>172.1438238359966</v>
+        <v>172.1438238359968</v>
       </c>
       <c r="H2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="I2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="J2" t="n">
-        <v>172.2502896551545</v>
+        <v>172.2502896551547</v>
       </c>
       <c r="K2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="L2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="M2" t="n">
-        <v>172.4442373389846</v>
+        <v>172.4442373389847</v>
       </c>
       <c r="N2" t="n">
-        <v>172.5886283804898</v>
+        <v>172.5886283804899</v>
       </c>
       <c r="O2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="P2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="R2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="S2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="T2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="U2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="V2" t="n">
-        <v>177.1758950925696</v>
+        <v>177.1758950925695</v>
       </c>
       <c r="W2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="X2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="Y2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="Z2" t="n">
-        <v>172.1795292170411</v>
+        <v>172.1795292170412</v>
       </c>
       <c r="AA2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
       <c r="AB2" t="n">
-        <v>172.2441080455648</v>
+        <v>172.2441080455649</v>
       </c>
     </row>
     <row r="3">
@@ -5878,7 +5878,7 @@
         <v>173.7288513334916</v>
       </c>
       <c r="J3" t="n">
-        <v>173.7350336277513</v>
+        <v>173.7350336277514</v>
       </c>
       <c r="K3" t="n">
         <v>173.7288513334916</v>
@@ -5914,7 +5914,7 @@
         <v>173.7288513334916</v>
       </c>
       <c r="V3" t="n">
-        <v>178.7099488363803</v>
+        <v>178.7099488363801</v>
       </c>
       <c r="W3" t="n">
         <v>173.7288513334916</v>
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.49792618049298</v>
+        <v>81.49792618049308</v>
       </c>
       <c r="C4" t="n">
-        <v>49.82390513076797</v>
+        <v>49.82390513076792</v>
       </c>
       <c r="D4" t="n">
-        <v>138.4205472657823</v>
+        <v>138.4205472657827</v>
       </c>
       <c r="E4" t="n">
-        <v>203.7960765450382</v>
+        <v>203.7960765450383</v>
       </c>
       <c r="F4" t="n">
-        <v>110.6394480930874</v>
+        <v>110.6394480930879</v>
       </c>
       <c r="G4" t="n">
-        <v>263.2585788911913</v>
+        <v>263.258578891192</v>
       </c>
       <c r="H4" t="n">
         <v>277.0226074679724</v>
       </c>
       <c r="I4" t="n">
-        <v>145.2882797220808</v>
+        <v>145.2882797220806</v>
       </c>
       <c r="J4" t="n">
         <v>305.7839459112486</v>
       </c>
       <c r="K4" t="n">
-        <v>208.1800723108735</v>
+        <v>208.1800723108731</v>
       </c>
       <c r="L4" t="n">
-        <v>230.5004932624307</v>
+        <v>230.5004932624309</v>
       </c>
       <c r="M4" t="n">
-        <v>367.2510075675322</v>
+        <v>367.2510075675325</v>
       </c>
       <c r="N4" t="n">
-        <v>415.0451347108337</v>
+        <v>415.045134710834</v>
       </c>
       <c r="O4" t="n">
-        <v>392.4301674519655</v>
+        <v>392.4301674519653</v>
       </c>
       <c r="P4" t="n">
-        <v>549.2979579621082</v>
+        <v>549.2979579621085</v>
       </c>
       <c r="Q4" t="n">
-        <v>241.0159055949698</v>
+        <v>241.0159055949699</v>
       </c>
       <c r="R4" t="n">
-        <v>156.6843094567558</v>
+        <v>156.6843094567557</v>
       </c>
       <c r="S4" t="n">
-        <v>198.6675288302131</v>
+        <v>198.667528830213</v>
       </c>
       <c r="T4" t="n">
         <v>288.6561246077598</v>
       </c>
       <c r="U4" t="n">
-        <v>415.0451347108337</v>
+        <v>415.045134710834</v>
       </c>
       <c r="V4" t="n">
-        <v>305.6137688111747</v>
+        <v>305.6137688111745</v>
       </c>
       <c r="W4" t="n">
-        <v>814.116928156734</v>
+        <v>814.1169281567353</v>
       </c>
       <c r="X4" t="n">
-        <v>278.5378179353303</v>
+        <v>278.5378179353305</v>
       </c>
       <c r="Y4" t="n">
-        <v>654.2088942970789</v>
+        <v>654.208894297076</v>
       </c>
       <c r="Z4" t="n">
-        <v>280.3127804360925</v>
+        <v>280.312780436092</v>
       </c>
       <c r="AA4" t="n">
-        <v>266.8391838543744</v>
+        <v>266.8391838543745</v>
       </c>
       <c r="AB4" t="n">
-        <v>492.0151137590345</v>
+        <v>492.0151137590356</v>
       </c>
     </row>
     <row r="5">
@@ -6030,85 +6030,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="C5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="D5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="E5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="F5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="G5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="H5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="I5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="J5" t="n">
-        <v>7.855795127187775</v>
+        <v>7.855795127187776</v>
       </c>
       <c r="K5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="L5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="M5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="N5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="O5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="P5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="R5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="S5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="T5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="U5" t="n">
-        <v>7.852824701880134</v>
+        <v>7.852824701880136</v>
       </c>
       <c r="V5" t="n">
-        <v>7.890806745020489</v>
+        <v>7.890806745020502</v>
       </c>
       <c r="W5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="X5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.852824701880134</v>
+        <v>7.852824701880136</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.849324570535612</v>
+        <v>7.84932457053561</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.849324570535613</v>
+        <v>7.849324570535614</v>
       </c>
     </row>
     <row r="6">
@@ -6118,85 +6118,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>686.6612171889883</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="C6" t="n">
-        <v>821.2227000998197</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="D6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="E6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="F6" t="n">
-        <v>821.2227000998197</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="G6" t="n">
-        <v>686.6612171889883</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="H6" t="n">
-        <v>686.6612171889883</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="I6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="J6" t="n">
-        <v>686.6676877456406</v>
+        <v>686.6676877456401</v>
       </c>
       <c r="K6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="L6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="M6" t="n">
-        <v>686.6612171889883</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="N6" t="n">
-        <v>686.7027010371251</v>
+        <v>686.7027010371245</v>
       </c>
       <c r="O6" t="n">
         <v>821.6303937380004</v>
       </c>
       <c r="P6" t="n">
-        <v>821.6297968609468</v>
+        <v>647.4134296526696</v>
       </c>
       <c r="Q6" t="n">
-        <v>821.2227000998197</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="R6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="S6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="T6" t="n">
-        <v>686.6612171889883</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="U6" t="n">
-        <v>821.2227000998197</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="V6" t="n">
-        <v>686.702699363474</v>
+        <v>821.2641822743042</v>
       </c>
       <c r="W6" t="n">
-        <v>721.4526779380756</v>
+        <v>721.4526779380751</v>
       </c>
       <c r="X6" t="n">
-        <v>686.6612171889883</v>
+        <v>686.6612171889882</v>
       </c>
       <c r="Y6" t="n">
         <v>716.4895890842329</v>
       </c>
       <c r="Z6" t="n">
-        <v>686.6612171889883</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="AA6" t="n">
-        <v>686.6612171889883</v>
+        <v>821.2227000998195</v>
       </c>
       <c r="AB6" t="n">
-        <v>686.747317460985</v>
+        <v>686.7473174609851</v>
       </c>
     </row>
     <row r="7">
@@ -6245,10 +6245,10 @@
         <v>13.78393627981734</v>
       </c>
       <c r="O7" t="n">
-        <v>13.78390868959883</v>
+        <v>13.78390868959885</v>
       </c>
       <c r="P7" t="n">
-        <v>13.78390868959883</v>
+        <v>13.78390868959885</v>
       </c>
       <c r="Q7" t="n">
         <v>13.78393627981734</v>
@@ -6266,7 +6266,7 @@
         <v>13.74742579668887</v>
       </c>
       <c r="V7" t="n">
-        <v>13.82541845430221</v>
+        <v>13.82541845430223</v>
       </c>
       <c r="W7" t="n">
         <v>13.78393627981734</v>
@@ -6294,82 +6294,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.83877341705542</v>
+        <v>15.83877341705543</v>
       </c>
       <c r="C8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="D8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="E8" t="n">
-        <v>21.94733134831933</v>
+        <v>18.69470444330175</v>
       </c>
       <c r="F8" t="n">
-        <v>16.79041534925929</v>
+        <v>16.79041534925927</v>
       </c>
       <c r="G8" t="n">
-        <v>21.94733134831933</v>
+        <v>23.21398062806261</v>
       </c>
       <c r="H8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="I8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="J8" t="n">
-        <v>21.9538019049715</v>
+        <v>21.95380190497151</v>
       </c>
       <c r="K8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="L8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="M8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831458</v>
       </c>
       <c r="N8" t="n">
-        <v>17.21217700929998</v>
+        <v>17.21217700929997</v>
       </c>
       <c r="O8" t="n">
-        <v>18.5134385306649</v>
+        <v>18.51343853066489</v>
       </c>
       <c r="P8" t="n">
-        <v>18.19446788949561</v>
+        <v>18.1944678894956</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.63830236548843</v>
+        <v>14.63830236548842</v>
       </c>
       <c r="R8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="S8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="T8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="U8" t="n">
-        <v>18.16189459269702</v>
+        <v>18.93755239915087</v>
       </c>
       <c r="V8" t="n">
-        <v>21.9888135228042</v>
+        <v>20.28806785419798</v>
       </c>
       <c r="W8" t="n">
-        <v>21.94853184405412</v>
+        <v>21.9485318440541</v>
       </c>
       <c r="X8" t="n">
-        <v>15.19816383106751</v>
+        <v>15.19816383106753</v>
       </c>
       <c r="Y8" t="n">
         <v>27.97256398686665</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.94733134831933</v>
+        <v>15.72530381829892</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.94733134831933</v>
+        <v>21.94733134831934</v>
       </c>
       <c r="AB8" t="n">
         <v>28.3282308866119</v>
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.9189589611341</v>
+        <v>28.91895896113414</v>
       </c>
       <c r="C9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="D9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="E9" t="n">
-        <v>35.19511966599755</v>
+        <v>33.74660935995168</v>
       </c>
       <c r="F9" t="n">
-        <v>35.19511966599755</v>
+        <v>20.72685294674775</v>
       </c>
       <c r="G9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19512224612322</v>
       </c>
       <c r="H9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="I9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="J9" t="n">
-        <v>35.20159022264974</v>
+        <v>35.20159022264976</v>
       </c>
       <c r="K9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="L9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="M9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="N9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="O9" t="n">
-        <v>37.27503454083399</v>
+        <v>37.27503454083401</v>
       </c>
       <c r="P9" t="n">
-        <v>37.72737977964862</v>
+        <v>37.72737977964861</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.19512224612319</v>
+        <v>35.19512224612322</v>
       </c>
       <c r="R9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="S9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="T9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="U9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="V9" t="n">
-        <v>35.23660184048246</v>
+        <v>42.47915587250148</v>
       </c>
       <c r="W9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="X9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="Y9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="Z9" t="n">
-        <v>35.19511966599755</v>
+        <v>31.41115388348963</v>
       </c>
       <c r="AA9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
       <c r="AB9" t="n">
-        <v>35.19511966599755</v>
+        <v>35.19511966599757</v>
       </c>
     </row>
     <row r="10">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171.9670139935539</v>
+        <v>171.9670139935538</v>
       </c>
       <c r="C10" t="n">
-        <v>172.8350541506788</v>
+        <v>172.8350541506789</v>
       </c>
       <c r="D10" t="n">
-        <v>170.9961302128745</v>
+        <v>170.9961302128744</v>
       </c>
       <c r="E10" t="n">
-        <v>156.2284101047433</v>
+        <v>156.2284101047435</v>
       </c>
       <c r="F10" t="n">
         <v>171.5764769818882</v>
@@ -6491,13 +6491,13 @@
         <v>168.3851948930385</v>
       </c>
       <c r="I10" t="n">
-        <v>170.8972619127935</v>
+        <v>170.8972619127936</v>
       </c>
       <c r="J10" t="n">
-        <v>166.6473163779084</v>
+        <v>166.6473163779085</v>
       </c>
       <c r="K10" t="n">
-        <v>169.1249836383718</v>
+        <v>169.1249836383716</v>
       </c>
       <c r="L10" t="n">
         <v>168.2123593066141</v>
@@ -6518,10 +6518,10 @@
         <v>168.5291211905196</v>
       </c>
       <c r="R10" t="n">
-        <v>170.7406282242445</v>
+        <v>170.7406282242446</v>
       </c>
       <c r="S10" t="n">
-        <v>168.668711368678</v>
+        <v>168.6687113686781</v>
       </c>
       <c r="T10" t="n">
         <v>167.6154672868676</v>
@@ -6530,7 +6530,7 @@
         <v>164.3334252364335</v>
       </c>
       <c r="V10" t="n">
-        <v>171.4269551460817</v>
+        <v>171.4269551460816</v>
       </c>
       <c r="W10" t="n">
         <v>156.2288609308951</v>
@@ -6542,7 +6542,7 @@
         <v>159.5071290661718</v>
       </c>
       <c r="Z10" t="n">
-        <v>166.9944083629079</v>
+        <v>166.9944083629078</v>
       </c>
       <c r="AA10" t="n">
         <v>168.091311712809</v>
@@ -6561,79 +6561,79 @@
         <v>171.4424664412506</v>
       </c>
       <c r="C11" t="n">
-        <v>170.7920147837802</v>
+        <v>170.7920147837804</v>
       </c>
       <c r="D11" t="n">
-        <v>170.2694175138755</v>
+        <v>170.2694175138754</v>
       </c>
       <c r="E11" t="n">
-        <v>156.8260417214424</v>
+        <v>156.8260417214425</v>
       </c>
       <c r="F11" t="n">
-        <v>170.4362040184499</v>
+        <v>170.43620401845</v>
       </c>
       <c r="G11" t="n">
-        <v>169.1745342365249</v>
+        <v>169.1745342365251</v>
       </c>
       <c r="H11" t="n">
-        <v>169.8127273359358</v>
+        <v>169.8127273359359</v>
       </c>
       <c r="I11" t="n">
-        <v>170.955725835407</v>
+        <v>170.9557258354071</v>
       </c>
       <c r="J11" t="n">
-        <v>169.0253557192613</v>
+        <v>169.0253557192614</v>
       </c>
       <c r="K11" t="n">
-        <v>170.1493335726293</v>
+        <v>170.1493335726295</v>
       </c>
       <c r="L11" t="n">
-        <v>169.7340865933184</v>
+        <v>169.7340865933185</v>
       </c>
       <c r="M11" t="n">
         <v>168.7325594328066</v>
       </c>
       <c r="N11" t="n">
-        <v>168.4605814207368</v>
+        <v>168.4605814207369</v>
       </c>
       <c r="O11" t="n">
-        <v>167.8804711993692</v>
+        <v>167.8804711993693</v>
       </c>
       <c r="P11" t="n">
-        <v>166.4438923214612</v>
+        <v>166.4438923214613</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.8782142599558</v>
+        <v>169.8782142599559</v>
       </c>
       <c r="R11" t="n">
-        <v>170.8844570079552</v>
+        <v>170.8844570079553</v>
       </c>
       <c r="S11" t="n">
-        <v>169.9417282358653</v>
+        <v>169.9417282358654</v>
       </c>
       <c r="T11" t="n">
-        <v>169.4624988221517</v>
+        <v>169.4624988221518</v>
       </c>
       <c r="U11" t="n">
-        <v>167.9691592299568</v>
+        <v>167.9691592299569</v>
       </c>
       <c r="V11" t="n">
-        <v>173.8621097539599</v>
+        <v>173.8621097539597</v>
       </c>
       <c r="W11" t="n">
         <v>164.2815566432229</v>
       </c>
       <c r="X11" t="n">
-        <v>169.6282540206474</v>
+        <v>169.6282540206475</v>
       </c>
       <c r="Y11" t="n">
-        <v>165.7731790919944</v>
+        <v>165.7731790919945</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.1153362040291</v>
+        <v>169.1153362040292</v>
       </c>
       <c r="AA11" t="n">
-        <v>169.6790095523813</v>
+        <v>169.6790095523814</v>
       </c>
       <c r="AB11" t="n">
         <v>167.7328902293892</v>
@@ -6805,19 +6805,19 @@
         <v>170.9550327340115</v>
       </c>
       <c r="C2" t="n">
-        <v>170.3890704209802</v>
+        <v>170.3890704209803</v>
       </c>
       <c r="D2" t="n">
-        <v>170.3442525530513</v>
+        <v>170.3442525530514</v>
       </c>
       <c r="E2" t="n">
-        <v>157.7786439844263</v>
+        <v>157.7786439844262</v>
       </c>
       <c r="F2" t="n">
         <v>170.5801662991548</v>
       </c>
       <c r="G2" t="n">
-        <v>171.0003310981415</v>
+        <v>171.0003310981416</v>
       </c>
       <c r="H2" t="n">
         <v>170.9550327340115</v>
@@ -6826,7 +6826,7 @@
         <v>170.9550327340115</v>
       </c>
       <c r="J2" t="n">
-        <v>170.9621034884188</v>
+        <v>170.9621034884189</v>
       </c>
       <c r="K2" t="n">
         <v>170.9550327340115</v>
@@ -6835,10 +6835,10 @@
         <v>170.9550327340115</v>
       </c>
       <c r="M2" t="n">
-        <v>170.7376305220995</v>
+        <v>170.7376305220996</v>
       </c>
       <c r="N2" t="n">
-        <v>171.3490163204927</v>
+        <v>171.3490163204928</v>
       </c>
       <c r="O2" t="n">
         <v>170.9550327340115</v>
@@ -6862,7 +6862,7 @@
         <v>170.9550327340115</v>
       </c>
       <c r="V2" t="n">
-        <v>175.8640928233289</v>
+        <v>175.8640928233287</v>
       </c>
       <c r="W2" t="n">
         <v>170.9550327340115</v>
@@ -6874,7 +6874,7 @@
         <v>170.9550327340115</v>
       </c>
       <c r="Z2" t="n">
-        <v>170.6948406484248</v>
+        <v>170.694840648425</v>
       </c>
       <c r="AA2" t="n">
         <v>170.9550327340115</v>
@@ -6890,85 +6890,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="C3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="D3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="E3" t="n">
-        <v>159.9700051448065</v>
+        <v>159.9700051448067</v>
       </c>
       <c r="F3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="G3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="H3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="I3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="J3" t="n">
         <v>172.8569337771939</v>
       </c>
       <c r="K3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="L3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="M3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="N3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="O3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="P3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="Q3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="R3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="S3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="T3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="U3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="V3" t="n">
-        <v>177.7126298712366</v>
+        <v>177.7126298712365</v>
       </c>
       <c r="W3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="X3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="Y3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="Z3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="AA3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
       <c r="AB3" t="n">
-        <v>172.8498622308326</v>
+        <v>172.8498622308328</v>
       </c>
     </row>
     <row r="4">
@@ -6978,19 +6978,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.631611770111</v>
+        <v>25.63161177011098</v>
       </c>
       <c r="C4" t="n">
-        <v>59.05534395655653</v>
+        <v>59.0553439565566</v>
       </c>
       <c r="D4" t="n">
-        <v>48.27169398666552</v>
+        <v>48.27169398666546</v>
       </c>
       <c r="E4" t="n">
-        <v>76.40821304171773</v>
+        <v>76.40821304171783</v>
       </c>
       <c r="F4" t="n">
-        <v>108.1177919358617</v>
+        <v>108.1177919358619</v>
       </c>
       <c r="G4" t="n">
         <v>179.393000536534</v>
@@ -6999,64 +6999,64 @@
         <v>207.9188085844052</v>
       </c>
       <c r="I4" t="n">
-        <v>92.91514583723863</v>
+        <v>92.91514583723921</v>
       </c>
       <c r="J4" t="n">
         <v>182.3998038870588</v>
       </c>
       <c r="K4" t="n">
-        <v>76.86326089097881</v>
+        <v>76.86326089097888</v>
       </c>
       <c r="L4" t="n">
         <v>41.4193468086453</v>
       </c>
       <c r="M4" t="n">
-        <v>132.9876173854385</v>
+        <v>132.9876173854387</v>
       </c>
       <c r="N4" t="n">
-        <v>182.596014300596</v>
+        <v>182.5960143005965</v>
       </c>
       <c r="O4" t="n">
-        <v>313.6231364624369</v>
+        <v>313.6231364624367</v>
       </c>
       <c r="P4" t="n">
-        <v>426.2327688909319</v>
+        <v>426.2327688909311</v>
       </c>
       <c r="Q4" t="n">
-        <v>96.18809306311516</v>
+        <v>96.18809306311512</v>
       </c>
       <c r="R4" t="n">
-        <v>64.75848040914693</v>
+        <v>64.75848040914684</v>
       </c>
       <c r="S4" t="n">
         <v>122.7465443220184</v>
       </c>
       <c r="T4" t="n">
-        <v>177.8611365264355</v>
+        <v>177.8611365264354</v>
       </c>
       <c r="U4" t="n">
-        <v>182.596014300596</v>
+        <v>182.5960143005965</v>
       </c>
       <c r="V4" t="n">
-        <v>204.7394082222059</v>
+        <v>204.7394082222061</v>
       </c>
       <c r="W4" t="n">
-        <v>454.1778112427771</v>
+        <v>454.1778112427768</v>
       </c>
       <c r="X4" t="n">
-        <v>360.9333337193237</v>
+        <v>360.9333337193235</v>
       </c>
       <c r="Y4" t="n">
-        <v>492.7898953057354</v>
+        <v>492.7898953057349</v>
       </c>
       <c r="Z4" t="n">
-        <v>121.1739596298971</v>
+        <v>121.1739596298973</v>
       </c>
       <c r="AA4" t="n">
-        <v>293.9941451463408</v>
+        <v>293.9941451463403</v>
       </c>
       <c r="AB4" t="n">
-        <v>298.2002164354764</v>
+        <v>298.2002164354759</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="C5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="D5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="E5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="F5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="G5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="H5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="I5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="J5" t="n">
-        <v>6.218470173064168</v>
+        <v>6.218470173064166</v>
       </c>
       <c r="K5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="L5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="M5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="N5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="O5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="P5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="R5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="S5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="T5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="U5" t="n">
-        <v>6.204184498611024</v>
+        <v>6.204184498611054</v>
       </c>
       <c r="V5" t="n">
-        <v>6.253577874638982</v>
+        <v>6.253577874638996</v>
       </c>
       <c r="W5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="X5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.204184498611024</v>
+        <v>6.204184498611054</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.211949894775557</v>
+        <v>6.211949894775562</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.211949894775461</v>
+        <v>6.211949894775575</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>638.2312355074837</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="C6" t="n">
-        <v>763.0533304547445</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="D6" t="n">
-        <v>638.2312355074837</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="E6" t="n">
-        <v>763.0533304547445</v>
+        <v>763.053330454745</v>
       </c>
       <c r="F6" t="n">
-        <v>763.0533304547445</v>
+        <v>763.053330454745</v>
       </c>
       <c r="G6" t="n">
-        <v>763.0533304547445</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="H6" t="n">
-        <v>763.0533304547445</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="I6" t="n">
-        <v>638.2312355074837</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="J6" t="n">
-        <v>763.059850733033</v>
+        <v>638.2377557857722</v>
       </c>
       <c r="K6" t="n">
-        <v>638.2312355074837</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="L6" t="n">
-        <v>763.0533304547445</v>
+        <v>763.053330454745</v>
       </c>
       <c r="M6" t="n">
-        <v>638.2312355074837</v>
+        <v>763.053330454745</v>
       </c>
       <c r="N6" t="n">
-        <v>638.2748417867169</v>
+        <v>638.2748417867168</v>
       </c>
       <c r="O6" t="n">
-        <v>638.2748417867169</v>
+        <v>638.2748417867168</v>
       </c>
       <c r="P6" t="n">
-        <v>763.4112041556428</v>
+        <v>601.7059850632521</v>
       </c>
       <c r="Q6" t="n">
-        <v>763.0533304547445</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="R6" t="n">
-        <v>763.0533304547445</v>
+        <v>763.053330454745</v>
       </c>
       <c r="S6" t="n">
-        <v>763.0533304547445</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="T6" t="n">
-        <v>763.0533304547445</v>
+        <v>763.053330454745</v>
       </c>
       <c r="U6" t="n">
-        <v>638.2312355074837</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="V6" t="n">
-        <v>638.2728634873472</v>
+        <v>763.0949584346085</v>
       </c>
       <c r="W6" t="n">
-        <v>670.5616940593598</v>
+        <v>670.5616940593594</v>
       </c>
       <c r="X6" t="n">
-        <v>638.2312355074837</v>
+        <v>638.2312355074836</v>
       </c>
       <c r="Y6" t="n">
-        <v>665.9990876719503</v>
+        <v>665.99908767195</v>
       </c>
       <c r="Z6" t="n">
-        <v>763.0533304547445</v>
+        <v>763.053330454745</v>
       </c>
       <c r="AA6" t="n">
-        <v>638.2312355074837</v>
+        <v>763.053330454745</v>
       </c>
       <c r="AB6" t="n">
-        <v>638.3031768481608</v>
+        <v>638.3031768481603</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="C7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="D7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="E7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="F7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="G7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="H7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="I7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="J7" t="n">
-        <v>11.08053511056852</v>
+        <v>11.08053511056854</v>
       </c>
       <c r="K7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="L7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="M7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="N7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="O7" t="n">
-        <v>11.07400727071471</v>
+        <v>11.0740072707147</v>
       </c>
       <c r="P7" t="n">
-        <v>11.07400727071471</v>
+        <v>11.0740072707147</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="R7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="S7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="T7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="U7" t="n">
-        <v>11.0197831497198</v>
+        <v>11.01978314971975</v>
       </c>
       <c r="V7" t="n">
         <v>11.11564281214337</v>
       </c>
       <c r="W7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="X7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.07401483227999</v>
+        <v>11.07401483227994</v>
       </c>
     </row>
     <row r="8">
@@ -7333,82 +7333,82 @@
         <v>12.41479943236556</v>
       </c>
       <c r="C8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="D8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="E8" t="n">
-        <v>17.1580083287907</v>
+        <v>14.63238950919724</v>
       </c>
       <c r="F8" t="n">
-        <v>13.15373594233852</v>
+        <v>13.15373594233847</v>
       </c>
       <c r="G8" t="n">
-        <v>17.1580083287907</v>
+        <v>18.14154359188482</v>
       </c>
       <c r="H8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="I8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="J8" t="n">
-        <v>17.16452860707934</v>
+        <v>17.16452860707935</v>
       </c>
       <c r="K8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="L8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="M8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832877921</v>
       </c>
       <c r="N8" t="n">
-        <v>13.48122791017276</v>
+        <v>13.48122791017275</v>
       </c>
       <c r="O8" t="n">
-        <v>14.49163908944143</v>
+        <v>14.49163908944145</v>
       </c>
       <c r="P8" t="n">
-        <v>14.2439628949492</v>
+        <v>14.24396289494924</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.48265062825159</v>
+        <v>11.48265062825157</v>
       </c>
       <c r="R8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="S8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="T8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="U8" t="n">
-        <v>14.19982615179493</v>
+        <v>14.80088900526544</v>
       </c>
       <c r="V8" t="n">
-        <v>17.19963630865415</v>
+        <v>15.85689635677245</v>
       </c>
       <c r="W8" t="n">
-        <v>17.15894049614568</v>
+        <v>17.1589404961457</v>
       </c>
       <c r="X8" t="n">
-        <v>11.91737514290611</v>
+        <v>11.91737514290621</v>
       </c>
       <c r="Y8" t="n">
-        <v>21.80218493325561</v>
+        <v>21.80218493325571</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.1580083287907</v>
+        <v>12.32669189275927</v>
       </c>
       <c r="AA8" t="n">
-        <v>17.1580083287907</v>
+        <v>17.15800832879069</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.11268663324182</v>
+        <v>22.11268663324174</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.86257108380178</v>
+        <v>21.86257108380174</v>
       </c>
       <c r="C9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="D9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="E9" t="n">
-        <v>26.53989667723395</v>
+        <v>25.46039067377188</v>
       </c>
       <c r="F9" t="n">
-        <v>26.53989667723395</v>
+        <v>15.75738179567721</v>
       </c>
       <c r="G9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989884185901</v>
       </c>
       <c r="H9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="I9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="J9" t="n">
-        <v>26.5464169555225</v>
+        <v>26.54641695552244</v>
       </c>
       <c r="K9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="L9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="M9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="N9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="O9" t="n">
-        <v>28.08995913644093</v>
+        <v>28.08995913644087</v>
       </c>
       <c r="P9" t="n">
-        <v>28.42707065595684</v>
+        <v>28.42707065595677</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.53989884185902</v>
+        <v>26.53989884185901</v>
       </c>
       <c r="R9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="S9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="T9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="U9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="V9" t="n">
-        <v>26.58152465709728</v>
+        <v>31.97905978352556</v>
       </c>
       <c r="W9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="X9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="Y9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.53989667723395</v>
+        <v>23.71988612796292</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
       <c r="AB9" t="n">
-        <v>26.53989667723395</v>
+        <v>26.53989667723384</v>
       </c>
     </row>
     <row r="10">
@@ -7506,85 +7506,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172.3608089172004</v>
+        <v>172.3608089172003</v>
       </c>
       <c r="C10" t="n">
-        <v>171.6023056728377</v>
+        <v>171.6023056728378</v>
       </c>
       <c r="D10" t="n">
         <v>171.8662751112057</v>
       </c>
       <c r="E10" t="n">
-        <v>158.3078222764554</v>
+        <v>158.3078222764555</v>
       </c>
       <c r="F10" t="n">
-        <v>170.4959560278638</v>
+        <v>170.495956027864</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9504558803097</v>
+        <v>167.9504558803098</v>
       </c>
       <c r="H10" t="n">
-        <v>168.491145278684</v>
+        <v>168.4911452786842</v>
       </c>
       <c r="I10" t="n">
-        <v>170.8817561761773</v>
+        <v>170.8817561761775</v>
       </c>
       <c r="J10" t="n">
-        <v>168.2509641447885</v>
+        <v>168.2509641447886</v>
       </c>
       <c r="K10" t="n">
-        <v>171.0885645344307</v>
+        <v>171.0885645344308</v>
       </c>
       <c r="L10" t="n">
         <v>171.8983728292118</v>
       </c>
       <c r="M10" t="n">
-        <v>169.5745361234239</v>
+        <v>169.5745361234241</v>
       </c>
       <c r="N10" t="n">
         <v>165.9517703607279</v>
       </c>
       <c r="O10" t="n">
-        <v>164.5836660282548</v>
+        <v>164.5836660282551</v>
       </c>
       <c r="P10" t="n">
-        <v>162.0416108295013</v>
+        <v>162.0416108295014</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.5088848749369</v>
+        <v>170.508884874937</v>
       </c>
       <c r="R10" t="n">
         <v>171.554694581938</v>
       </c>
       <c r="S10" t="n">
-        <v>169.5811705230632</v>
+        <v>169.5811705230634</v>
       </c>
       <c r="T10" t="n">
-        <v>168.7342538018464</v>
+        <v>168.7342538018466</v>
       </c>
       <c r="U10" t="n">
-        <v>167.9251155299021</v>
+        <v>167.9251155299022</v>
       </c>
       <c r="V10" t="n">
-        <v>172.3624227052522</v>
+        <v>172.362422705252</v>
       </c>
       <c r="W10" t="n">
         <v>161.712580136373</v>
       </c>
       <c r="X10" t="n">
-        <v>164.2429798852764</v>
+        <v>164.2429798852765</v>
       </c>
       <c r="Y10" t="n">
-        <v>161.5067813826419</v>
+        <v>161.5067813826421</v>
       </c>
       <c r="Z10" t="n">
-        <v>169.7685646511762</v>
+        <v>169.7685646511764</v>
       </c>
       <c r="AA10" t="n">
-        <v>166.123762109455</v>
+        <v>166.1237621094552</v>
       </c>
       <c r="AB10" t="n">
-        <v>166.1342703481111</v>
+        <v>166.1342703481112</v>
       </c>
     </row>
     <row r="11">
@@ -7594,46 +7594,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>170.7325119177884</v>
+        <v>170.7325119177885</v>
       </c>
       <c r="C11" t="n">
-        <v>169.8214282113655</v>
+        <v>169.8214282113657</v>
       </c>
       <c r="D11" t="n">
-        <v>169.8967172791147</v>
+        <v>169.896717279115</v>
       </c>
       <c r="E11" t="n">
-        <v>157.0223454822637</v>
+        <v>157.0223454822638</v>
       </c>
       <c r="F11" t="n">
-        <v>169.5091314753499</v>
+        <v>169.50913147535</v>
       </c>
       <c r="G11" t="n">
-        <v>168.7710855951717</v>
+        <v>168.7710855951719</v>
       </c>
       <c r="H11" t="n">
         <v>168.9718026303771</v>
       </c>
       <c r="I11" t="n">
-        <v>170.0595382071614</v>
+        <v>170.0595382071616</v>
       </c>
       <c r="J11" t="n">
-        <v>168.86637262732</v>
+        <v>168.8663726273198</v>
       </c>
       <c r="K11" t="n">
         <v>170.153636669226</v>
       </c>
       <c r="L11" t="n">
-        <v>170.5221020240571</v>
+        <v>170.5221020240572</v>
       </c>
       <c r="M11" t="n">
-        <v>169.2473467053834</v>
+        <v>169.2473467053835</v>
       </c>
       <c r="N11" t="n">
-        <v>168.2103625366805</v>
+        <v>168.2103625366806</v>
       </c>
       <c r="O11" t="n">
-        <v>167.1938871190343</v>
+        <v>167.1938871190344</v>
       </c>
       <c r="P11" t="n">
         <v>166.0372439025522</v>
@@ -7642,34 +7642,34 @@
         <v>169.8898805768269</v>
       </c>
       <c r="R11" t="n">
-        <v>170.36572732631</v>
+        <v>170.3657273263102</v>
       </c>
       <c r="S11" t="n">
-        <v>169.4677675902741</v>
+        <v>169.4677675902742</v>
       </c>
       <c r="T11" t="n">
         <v>169.082417783157</v>
       </c>
       <c r="U11" t="n">
-        <v>168.7142572908515</v>
+        <v>168.7142572908517</v>
       </c>
       <c r="V11" t="n">
-        <v>173.4297315127074</v>
+        <v>173.4297315127073</v>
       </c>
       <c r="W11" t="n">
-        <v>165.8875338886202</v>
+        <v>165.8875338886203</v>
       </c>
       <c r="X11" t="n">
-        <v>167.0388738382769</v>
+        <v>167.038873838277</v>
       </c>
       <c r="Y11" t="n">
-        <v>165.7938947998308</v>
+        <v>165.7938947998309</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.2928404301684</v>
+        <v>169.2928404301686</v>
       </c>
       <c r="AA11" t="n">
-        <v>167.8946357439754</v>
+        <v>167.8946357439756</v>
       </c>
       <c r="AB11" t="n">
         <v>167.8994170260517</v>
@@ -7838,85 +7838,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="C2" t="n">
-        <v>169.7939699100471</v>
+        <v>169.7939699100469</v>
       </c>
       <c r="D2" t="n">
-        <v>169.9082714254774</v>
+        <v>169.9082714254773</v>
       </c>
       <c r="E2" t="n">
-        <v>157.2763422202592</v>
+        <v>157.2763422202589</v>
       </c>
       <c r="F2" t="n">
-        <v>170.2166741025596</v>
+        <v>170.2166741025595</v>
       </c>
       <c r="G2" t="n">
         <v>170.1138549662788</v>
       </c>
       <c r="H2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="I2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="J2" t="n">
-        <v>170.2112624305701</v>
+        <v>170.21126243057</v>
       </c>
       <c r="K2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="L2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="M2" t="n">
-        <v>170.1934740412859</v>
+        <v>170.1934740412858</v>
       </c>
       <c r="N2" t="n">
-        <v>170.4506253560198</v>
+        <v>170.4506253560197</v>
       </c>
       <c r="O2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="P2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="Q2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="R2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="S2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="T2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="U2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="V2" t="n">
-        <v>174.9861395223911</v>
+        <v>174.9861395223908</v>
       </c>
       <c r="W2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="X2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="Y2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="Z2" t="n">
-        <v>169.8909124768744</v>
+        <v>169.8909124768743</v>
       </c>
       <c r="AA2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
       <c r="AB2" t="n">
-        <v>170.2047322588159</v>
+        <v>170.2047322588157</v>
       </c>
     </row>
     <row r="3">
@@ -7926,85 +7926,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="C3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="D3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="E3" t="n">
-        <v>159.6539215374489</v>
+        <v>159.6539215374488</v>
       </c>
       <c r="F3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="G3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="H3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="I3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="J3" t="n">
-        <v>172.3141832041807</v>
+        <v>172.3141832041806</v>
       </c>
       <c r="K3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="L3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="M3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="N3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="O3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="P3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="Q3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="R3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="S3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="T3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="U3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="V3" t="n">
-        <v>177.1059463736879</v>
+        <v>177.1059463736878</v>
       </c>
       <c r="W3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="X3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="Y3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="Z3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="AA3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
       <c r="AB3" t="n">
-        <v>172.3076522996136</v>
+        <v>172.3076522996137</v>
       </c>
     </row>
     <row r="4">
@@ -8017,34 +8017,34 @@
         <v>24.3937061787897</v>
       </c>
       <c r="C4" t="n">
-        <v>44.35910409797009</v>
+        <v>44.35910409797012</v>
       </c>
       <c r="D4" t="n">
-        <v>73.17234191334754</v>
+        <v>73.17234191334762</v>
       </c>
       <c r="E4" t="n">
-        <v>28.23007099173307</v>
+        <v>28.23007099173306</v>
       </c>
       <c r="F4" t="n">
-        <v>154.7124911158696</v>
+        <v>154.7124911158701</v>
       </c>
       <c r="G4" t="n">
-        <v>111.1733929859202</v>
+        <v>111.17339298592</v>
       </c>
       <c r="H4" t="n">
         <v>199.3489902646893</v>
       </c>
       <c r="I4" t="n">
-        <v>91.76226662422084</v>
+        <v>91.76226662422083</v>
       </c>
       <c r="J4" t="n">
-        <v>139.4625664145653</v>
+        <v>139.4625664145654</v>
       </c>
       <c r="K4" t="n">
-        <v>88.73391119660437</v>
+        <v>88.73391119660434</v>
       </c>
       <c r="L4" t="n">
-        <v>48.00334340217724</v>
+        <v>48.00334340217719</v>
       </c>
       <c r="M4" t="n">
         <v>142.0083427043211</v>
@@ -8053,19 +8053,19 @@
         <v>188.5750146706064</v>
       </c>
       <c r="O4" t="n">
-        <v>237.9177977488288</v>
+        <v>237.9177977488291</v>
       </c>
       <c r="P4" t="n">
-        <v>362.9034763043973</v>
+        <v>362.903476304397</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.10102365607602</v>
+        <v>71.10102365607598</v>
       </c>
       <c r="R4" t="n">
-        <v>58.85455752762428</v>
+        <v>58.85455752762426</v>
       </c>
       <c r="S4" t="n">
-        <v>166.6656679324934</v>
+        <v>166.6656679324932</v>
       </c>
       <c r="T4" t="n">
         <v>168.639045575692</v>
@@ -8074,25 +8074,25 @@
         <v>188.5750146706064</v>
       </c>
       <c r="V4" t="n">
-        <v>146.7343447281433</v>
+        <v>146.7343447281435</v>
       </c>
       <c r="W4" t="n">
-        <v>276.8876470060513</v>
+        <v>276.8876470060516</v>
       </c>
       <c r="X4" t="n">
-        <v>388.6601972787473</v>
+        <v>388.6601972787478</v>
       </c>
       <c r="Y4" t="n">
-        <v>351.6135776456399</v>
+        <v>351.61357764564</v>
       </c>
       <c r="Z4" t="n">
-        <v>60.54947924588724</v>
+        <v>60.54947924588731</v>
       </c>
       <c r="AA4" t="n">
-        <v>313.7942547184248</v>
+        <v>313.7942547184244</v>
       </c>
       <c r="AB4" t="n">
-        <v>262.6672147572726</v>
+        <v>262.6672147572729</v>
       </c>
     </row>
     <row r="5">
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="C5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="D5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="E5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="F5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="G5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="H5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="I5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="J5" t="n">
-        <v>5.406941268274975</v>
+        <v>5.406941268274977</v>
       </c>
       <c r="K5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="L5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="M5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="N5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="O5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="P5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="R5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="S5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="T5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="U5" t="n">
-        <v>5.393962900910119</v>
+        <v>5.393962900910118</v>
       </c>
       <c r="V5" t="n">
-        <v>5.441105399436911</v>
+        <v>5.441105399436914</v>
       </c>
       <c r="W5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="X5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.393962900910119</v>
+        <v>5.393962900910118</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.400580950750313</v>
+        <v>5.400580950750316</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.400580950750315</v>
+        <v>5.400580950750318</v>
       </c>
     </row>
     <row r="6">
@@ -8190,85 +8190,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="C6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="D6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="E6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="F6" t="n">
-        <v>637.0704353756474</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="G6" t="n">
-        <v>637.0704353756474</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="H6" t="n">
-        <v>637.0704353756474</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="I6" t="n">
-        <v>761.4738952514615</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="J6" t="n">
-        <v>761.4802555689868</v>
+        <v>637.0767956931716</v>
       </c>
       <c r="K6" t="n">
-        <v>637.0704353756474</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="L6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="M6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="N6" t="n">
-        <v>637.1161429301541</v>
+        <v>637.1161429301535</v>
       </c>
       <c r="O6" t="n">
-        <v>637.1161429301534</v>
+        <v>761.783038303842</v>
       </c>
       <c r="P6" t="n">
-        <v>761.7823705748206</v>
+        <v>761.7823705748204</v>
       </c>
       <c r="Q6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="R6" t="n">
-        <v>761.4738952514615</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="S6" t="n">
-        <v>637.0704353756474</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="T6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="U6" t="n">
-        <v>761.4738952514615</v>
+        <v>761.4738952514621</v>
       </c>
       <c r="V6" t="n">
-        <v>637.1109598243335</v>
+        <v>637.1109598243336</v>
       </c>
       <c r="W6" t="n">
-        <v>761.783831988545</v>
+        <v>761.7838319885448</v>
       </c>
       <c r="X6" t="n">
-        <v>761.4738952514615</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="Y6" t="n">
-        <v>664.8168740838744</v>
+        <v>664.8168740838742</v>
       </c>
       <c r="Z6" t="n">
-        <v>761.4738952514615</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="AA6" t="n">
-        <v>761.4738952514615</v>
+        <v>637.0704353756475</v>
       </c>
       <c r="AB6" t="n">
-        <v>637.1428865148887</v>
+        <v>637.1428865148883</v>
       </c>
     </row>
     <row r="7">
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="C7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="D7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="E7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="F7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="G7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="H7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="I7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="J7" t="n">
-        <v>9.940286284538745</v>
+        <v>9.940286284538741</v>
       </c>
       <c r="K7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="L7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="M7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="N7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="O7" t="n">
-        <v>9.933926435419055</v>
+        <v>9.93392643541905</v>
       </c>
       <c r="P7" t="n">
-        <v>9.933926435419055</v>
+        <v>9.93392643541905</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="R7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="S7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="T7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="U7" t="n">
-        <v>9.877409082741696</v>
+        <v>9.877409082741698</v>
       </c>
       <c r="V7" t="n">
-        <v>9.974450415700687</v>
+        <v>9.974450415700682</v>
       </c>
       <c r="W7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="X7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.933925967014089</v>
+        <v>9.933925967014082</v>
       </c>
     </row>
     <row r="8">
@@ -8366,85 +8366,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.97394790486371</v>
+        <v>10.97394790486369</v>
       </c>
       <c r="C8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="D8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="E8" t="n">
-        <v>15.1977128855031</v>
+        <v>12.94868262812765</v>
       </c>
       <c r="F8" t="n">
-        <v>11.63196112378585</v>
+        <v>11.63196112378583</v>
       </c>
       <c r="G8" t="n">
-        <v>15.1977128855031</v>
+        <v>16.07353806891647</v>
       </c>
       <c r="H8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="I8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="J8" t="n">
-        <v>15.20407320302775</v>
+        <v>15.20407320302773</v>
       </c>
       <c r="K8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="L8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="M8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288548798</v>
       </c>
       <c r="N8" t="n">
-        <v>11.92358840306324</v>
+        <v>11.92358840306322</v>
       </c>
       <c r="O8" t="n">
-        <v>12.82334623563257</v>
+        <v>12.82334623563254</v>
       </c>
       <c r="P8" t="n">
-        <v>12.60279385009263</v>
+        <v>12.60279385009259</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.14388168551613</v>
+        <v>10.14388168551612</v>
       </c>
       <c r="R8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="S8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="T8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="U8" t="n">
-        <v>12.55750068484483</v>
+        <v>13.09235000694938</v>
       </c>
       <c r="V8" t="n">
-        <v>15.23823733418968</v>
+        <v>14.0355090399556</v>
       </c>
       <c r="W8" t="n">
-        <v>15.19854296871996</v>
+        <v>15.19854296871993</v>
       </c>
       <c r="X8" t="n">
-        <v>10.53099813404557</v>
+        <v>10.53099813404554</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.32237795909733</v>
+        <v>19.32237795909728</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.1977128855031</v>
+        <v>10.89548930253494</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.1977128855031</v>
+        <v>15.19771288550305</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.60978858612943</v>
+        <v>19.6097885861294</v>
       </c>
     </row>
     <row r="9">
@@ -8457,82 +8457,82 @@
         <v>18.43352730841991</v>
       </c>
       <c r="C9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="D9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="E9" t="n">
-        <v>22.33491981149818</v>
+        <v>21.4344949378221</v>
       </c>
       <c r="F9" t="n">
-        <v>22.33491981149818</v>
+        <v>13.3411442784007</v>
       </c>
       <c r="G9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33492059483283</v>
       </c>
       <c r="H9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="I9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="J9" t="n">
-        <v>22.34128012902284</v>
+        <v>22.34128012902285</v>
       </c>
       <c r="K9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="L9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="M9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="N9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="O9" t="n">
-        <v>23.62783722151119</v>
+        <v>23.62783722151123</v>
       </c>
       <c r="P9" t="n">
-        <v>23.90902440510046</v>
+        <v>23.90902440510045</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.33492059483282</v>
+        <v>22.33492059483283</v>
       </c>
       <c r="R9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="S9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="T9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="U9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="V9" t="n">
-        <v>22.37544426018477</v>
+        <v>26.87756710788747</v>
       </c>
       <c r="W9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="X9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.33491981149818</v>
+        <v>19.98272736855286</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.33491981149818</v>
+        <v>22.33491981149819</v>
       </c>
     </row>
     <row r="10">
@@ -8542,16 +8542,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171.8278300680454</v>
+        <v>171.8278300680455</v>
       </c>
       <c r="C10" t="n">
-        <v>171.3998135068287</v>
+        <v>171.3998135068286</v>
       </c>
       <c r="D10" t="n">
-        <v>170.7313424414059</v>
+        <v>170.7313424414058</v>
       </c>
       <c r="E10" t="n">
-        <v>159.1016497093802</v>
+        <v>159.10164970938</v>
       </c>
       <c r="F10" t="n">
         <v>168.9413805934384</v>
@@ -8566,7 +8566,7 @@
         <v>170.3686239970733</v>
       </c>
       <c r="J10" t="n">
-        <v>168.9760439135701</v>
+        <v>168.97604391357</v>
       </c>
       <c r="K10" t="n">
         <v>170.2955520885043</v>
@@ -8578,34 +8578,34 @@
         <v>169.0730880772261</v>
       </c>
       <c r="N10" t="n">
-        <v>167.5343701061167</v>
+        <v>167.5343701061166</v>
       </c>
       <c r="O10" t="n">
-        <v>166.1014760261512</v>
+        <v>166.1014760261511</v>
       </c>
       <c r="P10" t="n">
-        <v>162.8358247851686</v>
+        <v>162.8358247851685</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.7000513610153</v>
+        <v>170.7000513610152</v>
       </c>
       <c r="R10" t="n">
         <v>171.136943881139</v>
       </c>
       <c r="S10" t="n">
-        <v>168.0504657258582</v>
+        <v>168.050465725858</v>
       </c>
       <c r="T10" t="n">
         <v>168.5431824267413</v>
       </c>
       <c r="U10" t="n">
-        <v>167.3938317698697</v>
+        <v>167.3938317698696</v>
       </c>
       <c r="V10" t="n">
-        <v>173.4026964616597</v>
+        <v>173.4026964616594</v>
       </c>
       <c r="W10" t="n">
-        <v>165.6998584738015</v>
+        <v>165.6998584738014</v>
       </c>
       <c r="X10" t="n">
         <v>162.8569695917787</v>
@@ -8620,7 +8620,7 @@
         <v>165.1308817701826</v>
       </c>
       <c r="AB10" t="n">
-        <v>166.647538818231</v>
+        <v>166.6475388182309</v>
       </c>
     </row>
     <row r="11">
@@ -8630,19 +8630,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>169.9864116143496</v>
+        <v>169.9864116143495</v>
       </c>
       <c r="C11" t="n">
         <v>169.3809003662194</v>
       </c>
       <c r="D11" t="n">
-        <v>169.1910454165914</v>
+        <v>169.1910454165915</v>
       </c>
       <c r="E11" t="n">
-        <v>157.0250567785019</v>
+        <v>157.0250567785017</v>
       </c>
       <c r="F11" t="n">
-        <v>168.6850097485785</v>
+        <v>168.6850097485784</v>
       </c>
       <c r="G11" t="n">
         <v>168.8296165803673</v>
@@ -8651,13 +8651,13 @@
         <v>168.2793014203403</v>
       </c>
       <c r="I11" t="n">
-        <v>169.3224682018435</v>
+        <v>169.3224682018434</v>
       </c>
       <c r="J11" t="n">
-        <v>168.6923984153234</v>
+        <v>168.6923984153235</v>
       </c>
       <c r="K11" t="n">
-        <v>169.2892202505783</v>
+        <v>169.2892202505782</v>
       </c>
       <c r="L11" t="n">
         <v>169.6924080747735</v>
@@ -8669,46 +8669,46 @@
         <v>168.278766746431</v>
       </c>
       <c r="O11" t="n">
-        <v>167.38090227648</v>
+        <v>167.3809022764801</v>
       </c>
       <c r="P11" t="n">
-        <v>165.8950205548201</v>
+        <v>165.89502055482</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.4732687086334</v>
+        <v>169.4732687086333</v>
       </c>
       <c r="R11" t="n">
-        <v>169.6720561975837</v>
+        <v>169.6720561975835</v>
       </c>
       <c r="S11" t="n">
-        <v>168.2676988009085</v>
+        <v>168.2676988009084</v>
       </c>
       <c r="T11" t="n">
-        <v>168.4918864700054</v>
+        <v>168.4918864700052</v>
       </c>
       <c r="U11" t="n">
-        <v>167.9689282583655</v>
+        <v>167.9689282583653</v>
       </c>
       <c r="V11" t="n">
-        <v>173.3011490108609</v>
+        <v>173.3011490108607</v>
       </c>
       <c r="W11" t="n">
-        <v>167.1981650102817</v>
+        <v>167.1981650102815</v>
       </c>
       <c r="X11" t="n">
-        <v>165.9046415092124</v>
+        <v>165.9046415092123</v>
       </c>
       <c r="Y11" t="n">
-        <v>166.5830368716217</v>
+        <v>166.5830368716216</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.2101965749862</v>
+        <v>169.210196574986</v>
       </c>
       <c r="AA11" t="n">
-        <v>166.9392787969141</v>
+        <v>166.9392787969139</v>
       </c>
       <c r="AB11" t="n">
-        <v>167.6293625870754</v>
+        <v>167.6293625870753</v>
       </c>
     </row>
   </sheetData>
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="C2" t="n">
-        <v>172.0751767528926</v>
+        <v>172.0751767528925</v>
       </c>
       <c r="D2" t="n">
         <v>172.6448158197726</v>
@@ -8886,73 +8886,73 @@
         <v>159.4199891414144</v>
       </c>
       <c r="F2" t="n">
-        <v>172.4510917213526</v>
+        <v>172.4510917213525</v>
       </c>
       <c r="G2" t="n">
-        <v>173.9339811695986</v>
+        <v>173.9339811695983</v>
       </c>
       <c r="H2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="I2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="J2" t="n">
         <v>173.5996264153971</v>
       </c>
       <c r="K2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="L2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="M2" t="n">
-        <v>174.6792893743017</v>
+        <v>174.6792893743015</v>
       </c>
       <c r="N2" t="n">
-        <v>173.4391857852668</v>
+        <v>173.439185785267</v>
       </c>
       <c r="O2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="P2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="Q2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="R2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="S2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="T2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="U2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="V2" t="n">
-        <v>178.1423567863387</v>
+        <v>178.1423567863386</v>
       </c>
       <c r="W2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="X2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.3461133823269</v>
+        <v>173.3461133823268</v>
       </c>
       <c r="AA2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
       <c r="AB2" t="n">
-        <v>173.6170183209364</v>
+        <v>173.6170183209363</v>
       </c>
     </row>
     <row r="3">
@@ -8962,85 +8962,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="C3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="D3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="E3" t="n">
-        <v>160.9870486001035</v>
+        <v>160.9870486001037</v>
       </c>
       <c r="F3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="G3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="H3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="I3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="J3" t="n">
-        <v>174.5033064276078</v>
+        <v>174.5033064276077</v>
       </c>
       <c r="K3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="L3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="M3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="N3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="O3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="P3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="Q3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="R3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="S3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="T3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="U3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="V3" t="n">
-        <v>179.4827322117174</v>
+        <v>179.4827322117175</v>
       </c>
       <c r="W3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="X3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="Y3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="AA3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
       <c r="AB3" t="n">
-        <v>174.520700353857</v>
+        <v>174.5207003538569</v>
       </c>
     </row>
     <row r="4">
@@ -9050,85 +9050,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238.3478100039721</v>
+        <v>238.3478100039804</v>
       </c>
       <c r="C4" t="n">
-        <v>76.84656221463329</v>
+        <v>76.84656221463345</v>
       </c>
       <c r="D4" t="n">
-        <v>241.0202084934536</v>
+        <v>241.0202084934547</v>
       </c>
       <c r="E4" t="n">
-        <v>254.9598384211711</v>
+        <v>254.9598384211712</v>
       </c>
       <c r="F4" t="n">
-        <v>183.6522656194277</v>
+        <v>183.6522656194282</v>
       </c>
       <c r="G4" t="n">
-        <v>525.0189772081674</v>
+        <v>525.0189772081681</v>
       </c>
       <c r="H4" t="n">
-        <v>428.3402847156615</v>
+        <v>428.3402847156839</v>
       </c>
       <c r="I4" t="n">
-        <v>220.5840872533965</v>
+        <v>220.5840872534019</v>
       </c>
       <c r="J4" t="n">
-        <v>464.1538212654344</v>
+        <v>464.1538212654374</v>
       </c>
       <c r="K4" t="n">
-        <v>265.3017166270141</v>
+        <v>265.3017166270088</v>
       </c>
       <c r="L4" t="n">
-        <v>411.4084978519747</v>
+        <v>411.4084978519456</v>
       </c>
       <c r="M4" t="n">
-        <v>756.2768326581598</v>
+        <v>756.2768326581602</v>
       </c>
       <c r="N4" t="n">
-        <v>530.3078742165517</v>
+        <v>530.3078742165876</v>
       </c>
       <c r="O4" t="n">
-        <v>383.7492111293471</v>
+        <v>383.7492111293751</v>
       </c>
       <c r="P4" t="n">
-        <v>575.1383166729468</v>
+        <v>575.1383166729438</v>
       </c>
       <c r="Q4" t="n">
-        <v>292.4774665716586</v>
+        <v>292.477466571667</v>
       </c>
       <c r="R4" t="n">
-        <v>262.4658556900357</v>
+        <v>262.4658556900421</v>
       </c>
       <c r="S4" t="n">
-        <v>330.644751138845</v>
+        <v>330.6447511388121</v>
       </c>
       <c r="T4" t="n">
-        <v>321.5939112823903</v>
+        <v>321.5939112823968</v>
       </c>
       <c r="U4" t="n">
-        <v>530.3078742165517</v>
+        <v>530.3078742165874</v>
       </c>
       <c r="V4" t="n">
-        <v>356.88702709911</v>
+        <v>356.8870270991102</v>
       </c>
       <c r="W4" t="n">
         <v>757.7736819386455</v>
       </c>
       <c r="X4" t="n">
-        <v>413.4227607219108</v>
+        <v>413.4227607219225</v>
       </c>
       <c r="Y4" t="n">
-        <v>755.3635794836484</v>
+        <v>755.3635794836512</v>
       </c>
       <c r="Z4" t="n">
-        <v>389.1372580441503</v>
+        <v>389.1372580441508</v>
       </c>
       <c r="AA4" t="n">
-        <v>350.9814115186075</v>
+        <v>350.9814115186246</v>
       </c>
       <c r="AB4" t="n">
-        <v>684.6925799830194</v>
+        <v>684.6925799830184</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="C5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="D5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="E5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="F5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="G5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="H5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="I5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="J5" t="n">
-        <v>9.815963624424146</v>
+        <v>9.815963624424183</v>
       </c>
       <c r="K5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="L5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="M5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="N5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127903</v>
       </c>
       <c r="O5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="P5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="R5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="S5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="T5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="U5" t="n">
-        <v>9.714031692178139</v>
+        <v>9.714031692178201</v>
       </c>
       <c r="V5" t="n">
-        <v>9.824583903698377</v>
+        <v>9.824583903698439</v>
       </c>
       <c r="W5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="X5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.714031692178139</v>
+        <v>9.714031692178201</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.814387775127901</v>
+        <v>9.814387775127891</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.814387775127898</v>
+        <v>9.814387775127887</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="C6" t="n">
-        <v>688.7923386469962</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="D6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="E6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="F6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="G6" t="n">
-        <v>688.7923386469962</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="H6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="I6" t="n">
-        <v>688.7923386469962</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="J6" t="n">
-        <v>824.5540774458846</v>
+        <v>688.7939144962921</v>
       </c>
       <c r="K6" t="n">
-        <v>688.7923386469962</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="L6" t="n">
-        <v>688.7923386469962</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="M6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="N6" t="n">
-        <v>688.8482545026266</v>
+        <v>688.8482545026247</v>
       </c>
       <c r="O6" t="n">
-        <v>688.8482545026266</v>
+        <v>688.8482545026247</v>
       </c>
       <c r="P6" t="n">
-        <v>824.951010261598</v>
+        <v>824.9510102615984</v>
       </c>
       <c r="Q6" t="n">
-        <v>688.7923386469962</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="R6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="S6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="T6" t="n">
-        <v>824.5525015965885</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="U6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="V6" t="n">
-        <v>688.8025347755666</v>
+        <v>824.562697725159</v>
       </c>
       <c r="W6" t="n">
-        <v>723.5713957757087</v>
+        <v>723.5713957757099</v>
       </c>
       <c r="X6" t="n">
-        <v>824.5525015965885</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="Y6" t="n">
-        <v>718.6330921844514</v>
+        <v>718.6330921845341</v>
       </c>
       <c r="Z6" t="n">
-        <v>688.7923386469962</v>
+        <v>688.7923386469964</v>
       </c>
       <c r="AA6" t="n">
-        <v>824.5525015965885</v>
+        <v>824.5525015965884</v>
       </c>
       <c r="AB6" t="n">
-        <v>688.9136542647467</v>
+        <v>688.9136542647461</v>
       </c>
     </row>
     <row r="7">
@@ -9314,85 +9314,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="C7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="D7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="F7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="G7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="H7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="I7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="J7" t="n">
-        <v>16.53042973909328</v>
+        <v>16.53042973909333</v>
       </c>
       <c r="K7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="L7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="M7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="N7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="O7" t="n">
-        <v>16.52879515916476</v>
+        <v>16.52879515916478</v>
       </c>
       <c r="P7" t="n">
-        <v>16.52879515916476</v>
+        <v>16.52879515916478</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="R7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="S7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="T7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="U7" t="n">
-        <v>16.51594585200067</v>
+        <v>16.5159458520007</v>
       </c>
       <c r="V7" t="n">
-        <v>16.5390500183675</v>
+        <v>16.53905001836753</v>
       </c>
       <c r="W7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="X7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="AA7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.52885388979703</v>
+        <v>16.52885388979706</v>
       </c>
     </row>
     <row r="8">
@@ -9402,85 +9402,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.2274935276535</v>
+        <v>19.22749352765349</v>
       </c>
       <c r="C8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="D8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="E8" t="n">
-        <v>26.43239888129066</v>
+        <v>22.59599931418797</v>
       </c>
       <c r="F8" t="n">
-        <v>20.349933574932</v>
+        <v>20.34993357493203</v>
       </c>
       <c r="G8" t="n">
-        <v>26.43239888129066</v>
+        <v>27.92638294107752</v>
       </c>
       <c r="H8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="I8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="J8" t="n">
-        <v>26.43397473058691</v>
+        <v>26.43397473058697</v>
       </c>
       <c r="K8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="L8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="M8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888128728</v>
       </c>
       <c r="N8" t="n">
-        <v>20.84739187489862</v>
+        <v>20.84739187489858</v>
       </c>
       <c r="O8" t="n">
-        <v>22.38220028815659</v>
+        <v>22.38220028815657</v>
       </c>
       <c r="P8" t="n">
-        <v>22.00598166052403</v>
+        <v>22.00598166052411</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.81156518482975</v>
+        <v>17.81156518482983</v>
       </c>
       <c r="R8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="S8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="T8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="U8" t="n">
-        <v>21.98952494727955</v>
+        <v>22.90582283655927</v>
       </c>
       <c r="V8" t="n">
-        <v>26.44259500986113</v>
+        <v>24.46240246353146</v>
       </c>
       <c r="W8" t="n">
-        <v>26.4338148402428</v>
+        <v>26.43381484024277</v>
       </c>
       <c r="X8" t="n">
-        <v>18.47190906984591</v>
+        <v>18.47190906984593</v>
       </c>
       <c r="Y8" t="n">
-        <v>33.57903721135868</v>
+        <v>33.57903721135877</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.43239888129066</v>
+        <v>19.09365871271186</v>
       </c>
       <c r="AA8" t="n">
-        <v>26.43239888129066</v>
+        <v>26.43239888129078</v>
       </c>
       <c r="AB8" t="n">
-        <v>33.95852497688455</v>
+        <v>33.95852497688465</v>
       </c>
     </row>
     <row r="9">
@@ -9490,85 +9490,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.63299531064249</v>
+        <v>35.63299531064257</v>
       </c>
       <c r="C9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="D9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="E9" t="n">
-        <v>43.30597972131316</v>
+        <v>41.5350870456347</v>
       </c>
       <c r="F9" t="n">
-        <v>43.30597972131316</v>
+        <v>25.617655092235</v>
       </c>
       <c r="G9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30598079875225</v>
       </c>
       <c r="H9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="I9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="J9" t="n">
-        <v>43.3075555706094</v>
+        <v>43.30755557060947</v>
       </c>
       <c r="K9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="L9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="M9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="N9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="O9" t="n">
-        <v>45.84879814259476</v>
+        <v>45.84879814259497</v>
       </c>
       <c r="P9" t="n">
-        <v>46.40181728748247</v>
+        <v>46.40181728748258</v>
       </c>
       <c r="Q9" t="n">
-        <v>43.3059807987522</v>
+        <v>43.30598079875225</v>
       </c>
       <c r="R9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="S9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="T9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="U9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="V9" t="n">
-        <v>43.31617584988362</v>
+        <v>52.1706271038146</v>
       </c>
       <c r="W9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="X9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="Y9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.30597972131316</v>
+        <v>38.67985285791363</v>
       </c>
       <c r="AA9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
       <c r="AB9" t="n">
-        <v>43.30597972131316</v>
+        <v>43.30597972131324</v>
       </c>
     </row>
     <row r="10">
@@ -9578,13 +9578,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169.0506871657159</v>
+        <v>169.0506871657157</v>
       </c>
       <c r="C10" t="n">
-        <v>173.0897248153922</v>
+        <v>173.0897248153921</v>
       </c>
       <c r="D10" t="n">
-        <v>169.754706596499</v>
+        <v>169.7547065964989</v>
       </c>
       <c r="E10" t="n">
         <v>155.5991506484075</v>
@@ -9596,67 +9596,67 @@
         <v>162.0175872528343</v>
       </c>
       <c r="H10" t="n">
-        <v>166.2312211221056</v>
+        <v>166.2312211221054</v>
       </c>
       <c r="I10" t="n">
-        <v>170.1808515018094</v>
+        <v>170.1808515018093</v>
       </c>
       <c r="J10" t="n">
-        <v>163.9370606935998</v>
+        <v>163.9370606935994</v>
       </c>
       <c r="K10" t="n">
         <v>168.6263387026149</v>
       </c>
       <c r="L10" t="n">
-        <v>165.3887458254352</v>
+        <v>165.3887458254351</v>
       </c>
       <c r="M10" t="n">
-        <v>157.9010348562264</v>
+        <v>157.9010348562263</v>
       </c>
       <c r="N10" t="n">
-        <v>165.0617990128167</v>
+        <v>165.0617990128163</v>
       </c>
       <c r="O10" t="n">
-        <v>165.2939207286499</v>
+        <v>165.29392072865</v>
       </c>
       <c r="P10" t="n">
-        <v>161.3415490374869</v>
+        <v>161.3415490374868</v>
       </c>
       <c r="Q10" t="n">
         <v>168.3700985109811</v>
       </c>
       <c r="R10" t="n">
-        <v>169.4520267760893</v>
+        <v>169.452026776089</v>
       </c>
       <c r="S10" t="n">
-        <v>166.5961242215834</v>
+        <v>166.5961242215833</v>
       </c>
       <c r="T10" t="n">
-        <v>168.082279914201</v>
+        <v>168.0822799142009</v>
       </c>
       <c r="U10" t="n">
-        <v>162.7691001935883</v>
+        <v>162.7691001935876</v>
       </c>
       <c r="V10" t="n">
         <v>171.0031097022491</v>
       </c>
       <c r="W10" t="n">
-        <v>158.2859191512571</v>
+        <v>158.285919151257</v>
       </c>
       <c r="X10" t="n">
-        <v>166.033947769575</v>
+        <v>166.0339477695747</v>
       </c>
       <c r="Y10" t="n">
-        <v>158.1048789319513</v>
+        <v>158.1048789319502</v>
       </c>
       <c r="Z10" t="n">
-        <v>165.517945724398</v>
+        <v>165.5179457243979</v>
       </c>
       <c r="AA10" t="n">
-        <v>167.0943283504303</v>
+        <v>167.0943283504305</v>
       </c>
       <c r="AB10" t="n">
-        <v>161.2175805227882</v>
+        <v>161.2175805227881</v>
       </c>
     </row>
     <row r="11">
@@ -9666,85 +9666,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>171.1281448884346</v>
+        <v>171.1281448884345</v>
       </c>
       <c r="C11" t="n">
-        <v>171.4240783226428</v>
+        <v>171.4240783226427</v>
       </c>
       <c r="D11" t="n">
         <v>170.4762734718539</v>
       </c>
       <c r="E11" t="n">
-        <v>156.9684784031806</v>
+        <v>156.9684784031807</v>
       </c>
       <c r="F11" t="n">
-        <v>170.8069306247812</v>
+        <v>170.8069306247811</v>
       </c>
       <c r="G11" t="n">
-        <v>168.2450248635759</v>
+        <v>168.2450248635757</v>
       </c>
       <c r="H11" t="n">
-        <v>169.8452788534867</v>
+        <v>169.8452788534865</v>
       </c>
       <c r="I11" t="n">
-        <v>171.6423732629773</v>
+        <v>171.642373262977</v>
       </c>
       <c r="J11" t="n">
-        <v>168.7919509337964</v>
+        <v>168.7919509337962</v>
       </c>
       <c r="K11" t="n">
-        <v>170.9350649854055</v>
+        <v>170.9350649854054</v>
       </c>
       <c r="L11" t="n">
-        <v>169.4619499086921</v>
+        <v>169.4619499086922</v>
       </c>
       <c r="M11" t="n">
-        <v>167.1172886091484</v>
+        <v>167.1172886091483</v>
       </c>
       <c r="N11" t="n">
-        <v>169.1353555313636</v>
+        <v>169.1353555313635</v>
       </c>
       <c r="O11" t="n">
         <v>169.4188041874652</v>
       </c>
       <c r="P11" t="n">
-        <v>167.620462472525</v>
+        <v>167.6204624725249</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.8184748816229</v>
+        <v>170.8184748816227</v>
       </c>
       <c r="R11" t="n">
-        <v>171.3107556901479</v>
+        <v>171.3107556901477</v>
       </c>
       <c r="S11" t="n">
-        <v>170.0113109266263</v>
+        <v>170.0113109266262</v>
       </c>
       <c r="T11" t="n">
-        <v>170.6875165028646</v>
+        <v>170.6875165028643</v>
       </c>
       <c r="U11" t="n">
-        <v>168.2700027978865</v>
+        <v>168.2700027978864</v>
       </c>
       <c r="V11" t="n">
-        <v>174.284101521577</v>
+        <v>174.2841015215769</v>
       </c>
       <c r="W11" t="n">
         <v>166.2301411365756</v>
       </c>
       <c r="X11" t="n">
-        <v>169.7555188494124</v>
+        <v>169.7555188494123</v>
       </c>
       <c r="Y11" t="n">
         <v>166.1477672598506</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.2498313358463</v>
+        <v>169.2498313358462</v>
       </c>
       <c r="AA11" t="n">
-        <v>170.2379953929339</v>
+        <v>170.2379953929338</v>
       </c>
       <c r="AB11" t="n">
-        <v>167.5640564032728</v>
+        <v>167.5640564032727</v>
       </c>
     </row>
   </sheetData>
@@ -9910,85 +9910,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="C2" t="n">
-        <v>171.0002162071843</v>
+        <v>171.0002162071845</v>
       </c>
       <c r="D2" t="n">
-        <v>171.130817173517</v>
+        <v>171.1308171735169</v>
       </c>
       <c r="E2" t="n">
-        <v>158.4032042034285</v>
+        <v>158.4032042034284</v>
       </c>
       <c r="F2" t="n">
-        <v>171.1851084768188</v>
+        <v>171.185108476819</v>
       </c>
       <c r="G2" t="n">
-        <v>172.6039858737911</v>
+        <v>172.603985873791</v>
       </c>
       <c r="H2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="I2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="J2" t="n">
-        <v>171.9461806099153</v>
+        <v>171.9461806099152</v>
       </c>
       <c r="K2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="L2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="M2" t="n">
-        <v>171.8410498472615</v>
+        <v>171.8410498472616</v>
       </c>
       <c r="N2" t="n">
-        <v>171.9057607813845</v>
+        <v>171.9057607813844</v>
       </c>
       <c r="O2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="P2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="Q2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="R2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="S2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="T2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="U2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="V2" t="n">
-        <v>176.4291959996382</v>
+        <v>176.4291959996383</v>
       </c>
       <c r="W2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="X2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="Y2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="Z2" t="n">
         <v>171.4462219279024</v>
       </c>
       <c r="AA2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
       <c r="AB2" t="n">
-        <v>171.9657036139189</v>
+        <v>171.9657036139191</v>
       </c>
     </row>
     <row r="3">
@@ -10007,7 +10007,7 @@
         <v>173.4668329828808</v>
       </c>
       <c r="E3" t="n">
-        <v>160.3873053351948</v>
+        <v>160.3873053351945</v>
       </c>
       <c r="F3" t="n">
         <v>173.4668329828808</v>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.73073883577421</v>
+        <v>32.73073883577408</v>
       </c>
       <c r="C4" t="n">
-        <v>60.56406261908135</v>
+        <v>60.56406261908118</v>
       </c>
       <c r="D4" t="n">
-        <v>95.51254151321776</v>
+        <v>95.51254151321764</v>
       </c>
       <c r="E4" t="n">
         <v>130.6616530234172</v>
@@ -10101,70 +10101,70 @@
         <v>109.1118063729308</v>
       </c>
       <c r="G4" t="n">
-        <v>404.3272760181718</v>
+        <v>404.3272760181695</v>
       </c>
       <c r="H4" t="n">
-        <v>330.3941713382978</v>
+        <v>330.3941713382972</v>
       </c>
       <c r="I4" t="n">
-        <v>75.93662291760211</v>
+        <v>75.93662291760182</v>
       </c>
       <c r="J4" t="n">
-        <v>279.2921686480702</v>
+        <v>279.2921686480697</v>
       </c>
       <c r="K4" t="n">
         <v>133.799345627201</v>
       </c>
       <c r="L4" t="n">
-        <v>138.6938427824019</v>
+        <v>138.6938427824015</v>
       </c>
       <c r="M4" t="n">
-        <v>260.2023096697819</v>
+        <v>260.2023096697815</v>
       </c>
       <c r="N4" t="n">
         <v>267.6906947317054</v>
       </c>
       <c r="O4" t="n">
-        <v>303.078544342633</v>
+        <v>303.0785443426331</v>
       </c>
       <c r="P4" t="n">
         <v>447.9846463392768</v>
       </c>
       <c r="Q4" t="n">
-        <v>140.4663088250035</v>
+        <v>140.4663088250032</v>
       </c>
       <c r="R4" t="n">
-        <v>96.46633703459658</v>
+        <v>96.4663370345959</v>
       </c>
       <c r="S4" t="n">
         <v>139.1608198401418</v>
       </c>
       <c r="T4" t="n">
-        <v>187.3383191126981</v>
+        <v>187.3383191126979</v>
       </c>
       <c r="U4" t="n">
-        <v>267.6906947317053</v>
+        <v>267.6906947317055</v>
       </c>
       <c r="V4" t="n">
-        <v>213.5304991793604</v>
+        <v>213.5304991793605</v>
       </c>
       <c r="W4" t="n">
-        <v>551.6069541843922</v>
+        <v>551.6069541843916</v>
       </c>
       <c r="X4" t="n">
-        <v>382.8699829693768</v>
+        <v>382.8699829693766</v>
       </c>
       <c r="Y4" t="n">
-        <v>663.5984576650324</v>
+        <v>663.5984576650299</v>
       </c>
       <c r="Z4" t="n">
-        <v>153.9729272220364</v>
+        <v>153.9729272220362</v>
       </c>
       <c r="AA4" t="n">
-        <v>206.7292647668302</v>
+        <v>206.7292647668304</v>
       </c>
       <c r="AB4" t="n">
-        <v>517.4771392074101</v>
+        <v>517.4771392074088</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="C5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="D5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="E5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="F5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="G5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="H5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="I5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="J5" t="n">
-        <v>7.607194192874108</v>
+        <v>7.607194192874069</v>
       </c>
       <c r="K5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="L5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="M5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="N5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="O5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="P5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="R5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="S5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="T5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="U5" t="n">
-        <v>7.48241789366315</v>
+        <v>7.482417893663026</v>
       </c>
       <c r="V5" t="n">
-        <v>7.613217423110247</v>
+        <v>7.613217423110227</v>
       </c>
       <c r="W5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="X5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.48241789366315</v>
+        <v>7.482417893663026</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.606078937476749</v>
+        <v>7.606078937476646</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.606078937476831</v>
+        <v>7.606078937476648</v>
       </c>
     </row>
     <row r="6">
@@ -10262,55 +10262,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>765.4649916770134</v>
+        <v>639.7214134693553</v>
       </c>
       <c r="C6" t="n">
-        <v>765.4649916770134</v>
+        <v>765.4649916770136</v>
       </c>
       <c r="D6" t="n">
         <v>639.7214134693553</v>
       </c>
       <c r="E6" t="n">
+        <v>765.4649916770136</v>
+      </c>
+      <c r="F6" t="n">
+        <v>765.4649916770136</v>
+      </c>
+      <c r="G6" t="n">
         <v>639.7214134693553</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
+        <v>765.4649916770136</v>
+      </c>
+      <c r="I6" t="n">
+        <v>765.4649916770136</v>
+      </c>
+      <c r="J6" t="n">
+        <v>639.7225287247534</v>
+      </c>
+      <c r="K6" t="n">
+        <v>765.4649916770136</v>
+      </c>
+      <c r="L6" t="n">
         <v>639.7214134693553</v>
       </c>
-      <c r="G6" t="n">
-        <v>765.4649916770134</v>
-      </c>
-      <c r="H6" t="n">
-        <v>639.7214134693553</v>
-      </c>
-      <c r="I6" t="n">
-        <v>639.7214134693553</v>
-      </c>
-      <c r="J6" t="n">
-        <v>765.4661069324108</v>
-      </c>
-      <c r="K6" t="n">
-        <v>639.7214134693553</v>
-      </c>
-      <c r="L6" t="n">
-        <v>765.4649916770134</v>
-      </c>
       <c r="M6" t="n">
-        <v>639.7214134693553</v>
+        <v>765.4649916770136</v>
       </c>
       <c r="N6" t="n">
-        <v>639.762758206029</v>
+        <v>639.762758206028</v>
       </c>
       <c r="O6" t="n">
-        <v>765.8515659126375</v>
+        <v>639.762758206028</v>
       </c>
       <c r="P6" t="n">
-        <v>603.1735940783784</v>
+        <v>603.1735940783768</v>
       </c>
       <c r="Q6" t="n">
-        <v>639.7214134693553</v>
+        <v>765.4649916770136</v>
       </c>
       <c r="R6" t="n">
-        <v>765.4649916770134</v>
+        <v>765.4649916770136</v>
       </c>
       <c r="S6" t="n">
         <v>639.7214134693553</v>
@@ -10319,28 +10319,28 @@
         <v>639.7214134693553</v>
       </c>
       <c r="U6" t="n">
-        <v>765.4649916770134</v>
+        <v>639.7214134693553</v>
       </c>
       <c r="V6" t="n">
-        <v>765.4721301626471</v>
+        <v>765.472130162647</v>
       </c>
       <c r="W6" t="n">
-        <v>672.0738880807191</v>
+        <v>672.0738880807183</v>
       </c>
       <c r="X6" t="n">
-        <v>765.4649916770134</v>
+        <v>639.7214134693553</v>
       </c>
       <c r="Y6" t="n">
-        <v>667.4788765906544</v>
+        <v>667.4788765906543</v>
       </c>
       <c r="Z6" t="n">
         <v>639.7214134693553</v>
       </c>
       <c r="AA6" t="n">
-        <v>765.4649916770134</v>
+        <v>765.4649916770136</v>
       </c>
       <c r="AB6" t="n">
-        <v>639.837453376068</v>
+        <v>639.8374533760671</v>
       </c>
     </row>
     <row r="7">
@@ -10350,43 +10350,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="C7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="D7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="E7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="F7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="G7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="H7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="I7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="J7" t="n">
-        <v>12.96954621667996</v>
+        <v>12.96954621668004</v>
       </c>
       <c r="K7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="L7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="M7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="N7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="O7" t="n">
         <v>12.96840878778449</v>
@@ -10395,40 +10395,40 @@
         <v>12.96840878778449</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="R7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="S7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="T7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="U7" t="n">
-        <v>12.9269281661829</v>
+        <v>12.92692816618286</v>
       </c>
       <c r="V7" t="n">
         <v>12.97556944691619</v>
       </c>
       <c r="W7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="X7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="AA7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.96843096128285</v>
+        <v>12.96843096128261</v>
       </c>
     </row>
     <row r="8">
@@ -10438,85 +10438,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.83560588257972</v>
+        <v>14.8356058825797</v>
       </c>
       <c r="C8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="D8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="E8" t="n">
-        <v>20.40646802363281</v>
+        <v>17.44014826575437</v>
       </c>
       <c r="F8" t="n">
-        <v>15.70348109496147</v>
+        <v>15.70348109496152</v>
       </c>
       <c r="G8" t="n">
-        <v>20.40646802363281</v>
+        <v>21.5616225785753</v>
       </c>
       <c r="H8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="I8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="J8" t="n">
-        <v>20.40758327903014</v>
+        <v>20.40758327903018</v>
       </c>
       <c r="K8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="L8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="M8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802362793</v>
       </c>
       <c r="N8" t="n">
-        <v>16.08811787678219</v>
+        <v>16.08811787678233</v>
       </c>
       <c r="O8" t="n">
-        <v>17.2748379874462</v>
+        <v>17.27483798744613</v>
       </c>
       <c r="P8" t="n">
-        <v>16.98394421370232</v>
+        <v>16.98394421370243</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.74080432594804</v>
+        <v>13.74080432594806</v>
       </c>
       <c r="R8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="S8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="T8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="U8" t="n">
-        <v>16.94826446001141</v>
+        <v>17.65525809650451</v>
       </c>
       <c r="V8" t="n">
-        <v>20.41360650926632</v>
+        <v>18.85554927326684</v>
       </c>
       <c r="W8" t="n">
-        <v>20.40756284745575</v>
+        <v>20.40756284745566</v>
       </c>
       <c r="X8" t="n">
-        <v>14.25138490436228</v>
+        <v>14.25138490436227</v>
       </c>
       <c r="Y8" t="n">
-        <v>25.89045620046973</v>
+        <v>25.89045620046962</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.40646802363281</v>
+        <v>14.73212425915324</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.40646802363281</v>
+        <v>20.40646802363275</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.22569934827048</v>
+        <v>26.22569934827051</v>
       </c>
     </row>
     <row r="9">
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.44449713533769</v>
+        <v>26.44449713533777</v>
       </c>
       <c r="C9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="D9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="E9" t="n">
-        <v>32.07972957453825</v>
+        <v>30.77914317072583</v>
       </c>
       <c r="F9" t="n">
-        <v>32.07972957453825</v>
+        <v>19.08897697061422</v>
       </c>
       <c r="G9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07973250933866</v>
       </c>
       <c r="H9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="I9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="J9" t="n">
-        <v>32.08084482993566</v>
+        <v>32.08084482993554</v>
       </c>
       <c r="K9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="L9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="M9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="N9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="O9" t="n">
-        <v>33.94724213357136</v>
+        <v>33.94724213357135</v>
       </c>
       <c r="P9" t="n">
-        <v>34.35339343577321</v>
+        <v>34.35339343577311</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.07973250933863</v>
+        <v>32.07973250933866</v>
       </c>
       <c r="R9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="S9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="T9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="U9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="V9" t="n">
-        <v>32.08686806017171</v>
+        <v>38.58980597474906</v>
       </c>
       <c r="W9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="X9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="Y9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="Z9" t="n">
-        <v>32.07972957453825</v>
+        <v>28.68218668349731</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
       <c r="AB9" t="n">
-        <v>32.07972957453825</v>
+        <v>32.07972957453812</v>
       </c>
     </row>
     <row r="10">
@@ -10614,37 +10614,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172.8325797262296</v>
+        <v>172.8325797262297</v>
       </c>
       <c r="C10" t="n">
-        <v>172.2215655534723</v>
+        <v>172.2215655534721</v>
       </c>
       <c r="D10" t="n">
-        <v>171.4580112946317</v>
+        <v>171.4580112946318</v>
       </c>
       <c r="E10" t="n">
-        <v>157.4857937664201</v>
+        <v>157.4857937664198</v>
       </c>
       <c r="F10" t="n">
         <v>171.1513643260591</v>
       </c>
       <c r="G10" t="n">
-        <v>162.6684181522022</v>
+        <v>162.6684181522023</v>
       </c>
       <c r="H10" t="n">
-        <v>166.658292244587</v>
+        <v>166.6582922445868</v>
       </c>
       <c r="I10" t="n">
-        <v>171.9579911041857</v>
+        <v>171.9579911041858</v>
       </c>
       <c r="J10" t="n">
-        <v>166.4766436087215</v>
+        <v>166.4766436087214</v>
       </c>
       <c r="K10" t="n">
-        <v>170.2713612602785</v>
+        <v>170.2713612602784</v>
       </c>
       <c r="L10" t="n">
-        <v>170.0832798607069</v>
+        <v>170.083279860707</v>
       </c>
       <c r="M10" t="n">
         <v>167.3212209978166</v>
@@ -10653,19 +10653,19 @@
         <v>166.8910420025487</v>
       </c>
       <c r="O10" t="n">
-        <v>165.553426915665</v>
+        <v>165.5534269156649</v>
       </c>
       <c r="P10" t="n">
-        <v>162.1430041127043</v>
+        <v>162.1430041127042</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.1326954637853</v>
+        <v>170.1326954637852</v>
       </c>
       <c r="R10" t="n">
         <v>171.5406766556829</v>
       </c>
       <c r="S10" t="n">
-        <v>169.9613547595387</v>
+        <v>169.9613547595388</v>
       </c>
       <c r="T10" t="n">
         <v>169.4314871395569</v>
@@ -10677,22 +10677,22 @@
         <v>172.7779773912599</v>
       </c>
       <c r="W10" t="n">
-        <v>160.8010539563971</v>
+        <v>160.8010539563969</v>
       </c>
       <c r="X10" t="n">
-        <v>164.7015904865208</v>
+        <v>164.7015904865209</v>
       </c>
       <c r="Y10" t="n">
-        <v>158.0059317386782</v>
+        <v>158.005931738678</v>
       </c>
       <c r="Z10" t="n">
-        <v>169.5544902611794</v>
+        <v>169.5544902611795</v>
       </c>
       <c r="AA10" t="n">
         <v>168.8270199662682</v>
       </c>
       <c r="AB10" t="n">
-        <v>162.4118710987807</v>
+        <v>162.4118710987806</v>
       </c>
     </row>
     <row r="11">
@@ -10711,46 +10711,46 @@
         <v>170.2167969036287</v>
       </c>
       <c r="E11" t="n">
-        <v>157.0830071930673</v>
+        <v>157.0830071930671</v>
       </c>
       <c r="F11" t="n">
-        <v>170.1315628590042</v>
+        <v>170.1315628590041</v>
       </c>
       <c r="G11" t="n">
-        <v>167.6906727133261</v>
+        <v>167.690672713326</v>
       </c>
       <c r="H11" t="n">
-        <v>168.8677958804634</v>
+        <v>168.8677958804633</v>
       </c>
       <c r="I11" t="n">
-        <v>171.2791757507193</v>
+        <v>171.2791757507192</v>
       </c>
       <c r="J11" t="n">
         <v>168.7745062243471</v>
       </c>
       <c r="K11" t="n">
-        <v>170.511753796771</v>
+        <v>170.5117537967706</v>
       </c>
       <c r="L11" t="n">
         <v>170.426176160586</v>
       </c>
       <c r="M11" t="n">
-        <v>169.044776809154</v>
+        <v>169.0447768091539</v>
       </c>
       <c r="N11" t="n">
-        <v>168.9137549295309</v>
+        <v>168.9137549295308</v>
       </c>
       <c r="O11" t="n">
         <v>168.3650786348071</v>
       </c>
       <c r="P11" t="n">
-        <v>166.8133253910875</v>
+        <v>166.8133253910873</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.4486604174647</v>
+        <v>170.4486604174648</v>
       </c>
       <c r="R11" t="n">
-        <v>171.089296346748</v>
+        <v>171.0892963467479</v>
       </c>
       <c r="S11" t="n">
         <v>170.3706998510022</v>
@@ -10759,19 +10759,19 @@
         <v>170.1296083953225</v>
       </c>
       <c r="U11" t="n">
-        <v>168.9227101834446</v>
+        <v>168.9227101834447</v>
       </c>
       <c r="V11" t="n">
-        <v>173.9344021792491</v>
+        <v>173.9344021792492</v>
       </c>
       <c r="W11" t="n">
-        <v>166.2027337934261</v>
+        <v>166.202733793426</v>
       </c>
       <c r="X11" t="n">
         <v>167.9774903449049</v>
       </c>
       <c r="Y11" t="n">
-        <v>164.930944276838</v>
+        <v>164.9309442768381</v>
       </c>
       <c r="Z11" t="n">
         <v>169.6660935216318</v>
@@ -10780,7 +10780,7 @@
         <v>169.8545739051536</v>
       </c>
       <c r="AB11" t="n">
-        <v>166.9356607265802</v>
+        <v>166.9356607265803</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen resource use fossils results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen resource use fossils results.xlsx
@@ -886,7 +886,7 @@
         <v>6.858661657424657</v>
       </c>
       <c r="N5" t="n">
-        <v>606.9426783224378</v>
+        <v>6.858661657424724</v>
       </c>
       <c r="O5" t="n">
         <v>6.858661657424724</v>
@@ -974,7 +974,7 @@
         <v>877.9564223372013</v>
       </c>
       <c r="N6" t="n">
-        <v>606.9426783224378</v>
+        <v>732.808417818064</v>
       </c>
       <c r="O6" t="n">
         <v>732.8083996058826</v>
@@ -1062,7 +1062,7 @@
         <v>14.49472704690083</v>
       </c>
       <c r="N7" t="n">
-        <v>606.9426783224378</v>
+        <v>14.49472704690083</v>
       </c>
       <c r="O7" t="n">
         <v>14.49464187432214</v>
@@ -1150,7 +1150,7 @@
         <v>26.01779536780445</v>
       </c>
       <c r="N8" t="n">
-        <v>606.9426783224378</v>
+        <v>19.61549661436698</v>
       </c>
       <c r="O8" t="n">
         <v>21.37490389584138</v>
@@ -1238,7 +1238,7 @@
         <v>47.26230692740856</v>
       </c>
       <c r="N9" t="n">
-        <v>606.9426783224378</v>
+        <v>47.26230692740856</v>
       </c>
       <c r="O9" t="n">
         <v>50.3137661197865</v>
@@ -1922,7 +1922,7 @@
         <v>4.259210775434627</v>
       </c>
       <c r="N5" t="n">
-        <v>272.4852654504973</v>
+        <v>4.259210775434608</v>
       </c>
       <c r="O5" t="n">
         <v>4.259210775434608</v>
@@ -2010,7 +2010,7 @@
         <v>635.8972473246583</v>
       </c>
       <c r="N6" t="n">
-        <v>272.4852654504973</v>
+        <v>635.9299807339407</v>
       </c>
       <c r="O6" t="n">
         <v>760.7915579158869</v>
@@ -2098,7 +2098,7 @@
         <v>9.01499044449899</v>
       </c>
       <c r="N7" t="n">
-        <v>272.4852654504973</v>
+        <v>9.01499044449899</v>
       </c>
       <c r="O7" t="n">
         <v>9.01498541849174</v>
@@ -2186,7 +2186,7 @@
         <v>14.82908382645299</v>
       </c>
       <c r="N8" t="n">
-        <v>272.4852654504973</v>
+        <v>11.31512402564988</v>
       </c>
       <c r="O8" t="n">
         <v>12.28079068675183</v>
@@ -2274,7 +2274,7 @@
         <v>22.44092127363832</v>
       </c>
       <c r="N9" t="n">
-        <v>272.4852654504973</v>
+        <v>22.44092127363832</v>
       </c>
       <c r="O9" t="n">
         <v>23.82508937678731</v>
@@ -2958,7 +2958,7 @@
         <v>6.353078108969522</v>
       </c>
       <c r="N5" t="n">
-        <v>520.4558486234436</v>
+        <v>6.353078108969481</v>
       </c>
       <c r="O5" t="n">
         <v>6.353078108969481</v>
@@ -3046,7 +3046,7 @@
         <v>821.0309222524356</v>
       </c>
       <c r="N6" t="n">
-        <v>520.4558486234436</v>
+        <v>685.4914706143513</v>
       </c>
       <c r="O6" t="n">
         <v>685.5007219615483</v>
@@ -3134,7 +3134,7 @@
         <v>13.17444728990796</v>
       </c>
       <c r="N7" t="n">
-        <v>520.4558486234436</v>
+        <v>13.17444728990796</v>
       </c>
       <c r="O7" t="n">
         <v>13.17436951488645</v>
@@ -3222,7 +3222,7 @@
         <v>23.25095020527766</v>
       </c>
       <c r="N8" t="n">
-        <v>520.4558486234436</v>
+        <v>17.61127850491952</v>
       </c>
       <c r="O8" t="n">
         <v>19.16110925124383</v>
@@ -3310,7 +3310,7 @@
         <v>38.89472298769169</v>
       </c>
       <c r="N9" t="n">
-        <v>520.4558486234436</v>
+        <v>38.89472298769169</v>
       </c>
       <c r="O9" t="n">
         <v>41.36227916868521</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172.4651057225251</v>
+        <v>172.465105722525</v>
       </c>
       <c r="C2" t="n">
         <v>172.0949453873781</v>
@@ -3703,7 +3703,7 @@
         <v>172.818785426485</v>
       </c>
       <c r="E2" t="n">
-        <v>159.0940065871001</v>
+        <v>159.0940065871</v>
       </c>
       <c r="F2" t="n">
         <v>172.405502220388</v>
@@ -3733,19 +3733,19 @@
         <v>172.9352460255229</v>
       </c>
       <c r="O2" t="n">
-        <v>173.1549108902275</v>
+        <v>173.1549108902274</v>
       </c>
       <c r="P2" t="n">
         <v>173.6665677070455</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.6245769340387</v>
+        <v>172.6245769340388</v>
       </c>
       <c r="R2" t="n">
-        <v>172.5703118626022</v>
+        <v>172.5703118626023</v>
       </c>
       <c r="S2" t="n">
-        <v>172.9493650691849</v>
+        <v>172.9493650691848</v>
       </c>
       <c r="T2" t="n">
         <v>172.8347020900327</v>
@@ -3760,19 +3760,19 @@
         <v>173.9270607512961</v>
       </c>
       <c r="X2" t="n">
-        <v>173.2211165074473</v>
+        <v>173.2211165074474</v>
       </c>
       <c r="Y2" t="n">
-        <v>174.1667867649372</v>
+        <v>174.1667867649373</v>
       </c>
       <c r="Z2" t="n">
-        <v>172.8834627878959</v>
+        <v>172.883462787896</v>
       </c>
       <c r="AA2" t="n">
         <v>172.7856200079183</v>
       </c>
       <c r="AB2" t="n">
-        <v>174.2143344853467</v>
+        <v>174.2143344853468</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="C3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="D3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="E3" t="n">
-        <v>160.7310709430198</v>
+        <v>160.73107094302</v>
       </c>
       <c r="F3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="G3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="H3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="I3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="J3" t="n">
         <v>174.1412328646676</v>
       </c>
       <c r="K3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="L3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="M3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="N3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="O3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="P3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="Q3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="R3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="S3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="T3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="U3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="V3" t="n">
-        <v>179.1241978528532</v>
+        <v>179.1241978528533</v>
       </c>
       <c r="W3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="X3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="Y3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="AA3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
       <c r="AB3" t="n">
-        <v>174.1476607935168</v>
+        <v>174.1476607935167</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>244.2074018352831</v>
+        <v>244.2074018352836</v>
       </c>
       <c r="C4" t="n">
-        <v>162.8652456331735</v>
+        <v>162.8652456331733</v>
       </c>
       <c r="D4" t="n">
-        <v>362.4114622176996</v>
+        <v>362.4114622176999</v>
       </c>
       <c r="E4" t="n">
-        <v>217.4911826478095</v>
+        <v>217.491182647809</v>
       </c>
       <c r="F4" t="n">
-        <v>252.0662158477791</v>
+        <v>252.0662158477789</v>
       </c>
       <c r="G4" t="n">
-        <v>385.5881116566436</v>
+        <v>385.5881116566437</v>
       </c>
       <c r="H4" t="n">
-        <v>402.9427065371395</v>
+        <v>402.9427065371388</v>
       </c>
       <c r="I4" t="n">
-        <v>271.8867733885376</v>
+        <v>271.8867733885367</v>
       </c>
       <c r="J4" t="n">
-        <v>406.9606456384355</v>
+        <v>406.9606456384349</v>
       </c>
       <c r="K4" t="n">
-        <v>251.0502039016471</v>
+        <v>251.0502039016468</v>
       </c>
       <c r="L4" t="n">
-        <v>427.0689523679243</v>
+        <v>427.0689523679209</v>
       </c>
       <c r="M4" t="n">
-        <v>670.3620754968299</v>
+        <v>670.3620754968275</v>
       </c>
       <c r="N4" t="n">
-        <v>386.6570478049064</v>
+        <v>386.6570478049059</v>
       </c>
       <c r="O4" t="n">
-        <v>385.9766245294464</v>
+        <v>385.9766245294469</v>
       </c>
       <c r="P4" t="n">
-        <v>525.4568763176892</v>
+        <v>525.4568763176882</v>
       </c>
       <c r="Q4" t="n">
-        <v>299.7935559262658</v>
+        <v>299.7935559262652</v>
       </c>
       <c r="R4" t="n">
-        <v>306.902184513901</v>
+        <v>306.9021845139006</v>
       </c>
       <c r="S4" t="n">
-        <v>359.0774448842647</v>
+        <v>359.0774448842636</v>
       </c>
       <c r="T4" t="n">
-        <v>370.3203814387253</v>
+        <v>370.3203814387256</v>
       </c>
       <c r="U4" t="n">
-        <v>456.5559196911684</v>
+        <v>456.5559196911718</v>
       </c>
       <c r="V4" t="n">
-        <v>323.0055529789338</v>
+        <v>323.0055529789347</v>
       </c>
       <c r="W4" t="n">
-        <v>631.4372012290501</v>
+        <v>631.4372012290496</v>
       </c>
       <c r="X4" t="n">
-        <v>461.6209483230409</v>
+        <v>461.6209483230419</v>
       </c>
       <c r="Y4" t="n">
-        <v>685.2460624615053</v>
+        <v>685.2460624615052</v>
       </c>
       <c r="Z4" t="n">
-        <v>325.3196430875386</v>
+        <v>325.3196430875379</v>
       </c>
       <c r="AA4" t="n">
-        <v>341.956035911008</v>
+        <v>341.9560359110076</v>
       </c>
       <c r="AB4" t="n">
-        <v>774.4054522284266</v>
+        <v>774.4054522284248</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.784026603074074</v>
+        <v>5.784026603073952</v>
       </c>
       <c r="C5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="D5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="E5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="F5" t="n">
-        <v>5.784026603074081</v>
+        <v>5.784026603073941</v>
       </c>
       <c r="G5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="H5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="I5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="J5" t="n">
-        <v>5.787802602635041</v>
+        <v>5.787802602634878</v>
       </c>
       <c r="K5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="L5" t="n">
-        <v>5.784026603074146</v>
+        <v>5.78402660307392</v>
       </c>
       <c r="M5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="N5" t="n">
-        <v>386.6570478049064</v>
+        <v>5.784026603073941</v>
       </c>
       <c r="O5" t="n">
-        <v>5.784026603074081</v>
+        <v>5.784026603073941</v>
       </c>
       <c r="P5" t="n">
-        <v>5.784026603074081</v>
+        <v>5.784026603073941</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.784026603074081</v>
+        <v>5.784026603073941</v>
       </c>
       <c r="R5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="S5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="T5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="U5" t="n">
-        <v>5.708091729762076</v>
+        <v>5.70809172976192</v>
       </c>
       <c r="V5" t="n">
         <v>5.808208370130568</v>
       </c>
       <c r="W5" t="n">
-        <v>5.784026603074081</v>
+        <v>5.784026603073941</v>
       </c>
       <c r="X5" t="n">
-        <v>5.784026603074074</v>
+        <v>5.784026603073952</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.708091729762076</v>
+        <v>5.70809172976192</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.78402660307415</v>
+        <v>5.78402660307391</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.784026603074081</v>
+        <v>5.784026603073941</v>
       </c>
     </row>
     <row r="6">
@@ -4049,82 +4049,82 @@
         <v>764.4123468731481</v>
       </c>
       <c r="C6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="D6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="E6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="F6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="G6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="H6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="I6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="J6" t="n">
         <v>764.4161228727089</v>
       </c>
       <c r="K6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="L6" t="n">
         <v>764.4123468731481</v>
       </c>
       <c r="M6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="N6" t="n">
-        <v>386.6570478049064</v>
+        <v>638.480786995905</v>
       </c>
       <c r="O6" t="n">
         <v>764.7350783408733</v>
       </c>
       <c r="P6" t="n">
-        <v>764.7321008897437</v>
+        <v>764.7321008897438</v>
       </c>
       <c r="Q6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="R6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="S6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="T6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="U6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="V6" t="n">
-        <v>764.4365286402049</v>
+        <v>764.4365286402045</v>
       </c>
       <c r="W6" t="n">
-        <v>764.7361027719139</v>
+        <v>764.7361027719136</v>
       </c>
       <c r="X6" t="n">
-        <v>638.4305938159454</v>
+        <v>638.4305938159443</v>
       </c>
       <c r="Y6" t="n">
         <v>666.244799155734</v>
       </c>
       <c r="Z6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="AA6" t="n">
-        <v>764.4123468731478</v>
+        <v>764.412346873148</v>
       </c>
       <c r="AB6" t="n">
-        <v>638.5949264986472</v>
+        <v>638.5949264986468</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.75960054663062</v>
+        <v>11.75960054663057</v>
       </c>
       <c r="C7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="D7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="E7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="G7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="H7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="I7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="J7" t="n">
-        <v>11.76337654619177</v>
+        <v>11.76337654619155</v>
       </c>
       <c r="K7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="L7" t="n">
-        <v>11.75960054663062</v>
+        <v>11.75960054663057</v>
       </c>
       <c r="M7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="N7" t="n">
-        <v>386.6570478049064</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="O7" t="n">
-        <v>11.75955478239073</v>
+        <v>11.75955478239061</v>
       </c>
       <c r="P7" t="n">
-        <v>11.75955478239073</v>
+        <v>11.75955478239061</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="R7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="S7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="T7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="U7" t="n">
-        <v>11.74443645415401</v>
+        <v>11.74443645415386</v>
       </c>
       <c r="V7" t="n">
-        <v>11.78378231368724</v>
+        <v>11.78378231368725</v>
       </c>
       <c r="W7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="X7" t="n">
-        <v>11.75960054663062</v>
+        <v>11.75960054663057</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.7596005466306</v>
+        <v>11.75960054663056</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.07155949496546</v>
+        <v>14.07155949496538</v>
       </c>
       <c r="C8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="D8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="E8" t="n">
-        <v>16.9850255471447</v>
+        <v>16.98502554714449</v>
       </c>
       <c r="F8" t="n">
-        <v>15.04237301927225</v>
+        <v>15.04237301927206</v>
       </c>
       <c r="G8" t="n">
-        <v>21.59534618459898</v>
+        <v>21.59534618459882</v>
       </c>
       <c r="H8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="I8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="J8" t="n">
-        <v>20.30695523614188</v>
+        <v>20.30695523614182</v>
       </c>
       <c r="K8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="L8" t="n">
-        <v>20.30317923658108</v>
+        <v>20.30317923658081</v>
       </c>
       <c r="M8" t="n">
-        <v>20.3031792365941</v>
+        <v>20.30317923659395</v>
       </c>
       <c r="N8" t="n">
-        <v>386.6570478049064</v>
+        <v>15.4726314074163</v>
       </c>
       <c r="O8" t="n">
-        <v>16.80010788949183</v>
+        <v>16.80010788949165</v>
       </c>
       <c r="P8" t="n">
-        <v>16.47471132785996</v>
+        <v>16.47471132785971</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.84690398822808</v>
+        <v>12.84690398822792</v>
       </c>
       <c r="R8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="S8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="T8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="U8" t="n">
-        <v>17.24989247496318</v>
+        <v>17.24989247496309</v>
       </c>
       <c r="V8" t="n">
         <v>18.61124258919156</v>
       </c>
       <c r="W8" t="n">
-        <v>20.30440392007019</v>
+        <v>20.30440392007008</v>
       </c>
       <c r="X8" t="n">
-        <v>13.41804431483093</v>
+        <v>13.41804431483085</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.47909366515268</v>
+        <v>26.47909366515263</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.95580395968659</v>
+        <v>13.95580395968653</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.30317923658105</v>
+        <v>20.3031792365808</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.81262712847535</v>
+        <v>26.81262712847516</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.35924359963428</v>
+        <v>26.359243599634</v>
       </c>
       <c r="C9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="E9" t="n">
-        <v>31.05950826055738</v>
+        <v>31.05950826055721</v>
       </c>
       <c r="F9" t="n">
-        <v>18.38330018679122</v>
+        <v>18.38330018679106</v>
       </c>
       <c r="G9" t="n">
-        <v>32.46979967922151</v>
+        <v>32.46979967922132</v>
       </c>
       <c r="H9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="I9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="J9" t="n">
-        <v>32.47357469630114</v>
+        <v>32.473574696301</v>
       </c>
       <c r="K9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="L9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673998</v>
       </c>
       <c r="M9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="N9" t="n">
-        <v>386.6570478049064</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="O9" t="n">
-        <v>34.49482996290681</v>
+        <v>34.49482996290664</v>
       </c>
       <c r="P9" t="n">
-        <v>34.93523930593992</v>
+        <v>34.93523930593978</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.46979967922151</v>
+        <v>32.46979967922132</v>
       </c>
       <c r="R9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="S9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="T9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="U9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="V9" t="n">
         <v>39.5454228444363</v>
       </c>
       <c r="W9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="X9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673998</v>
       </c>
       <c r="Y9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="Z9" t="n">
-        <v>28.78567773507808</v>
+        <v>28.78567773507787</v>
       </c>
       <c r="AA9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
       <c r="AB9" t="n">
-        <v>32.46979869674019</v>
+        <v>32.46979869673996</v>
       </c>
     </row>
     <row r="10">
@@ -4398,31 +4398,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168.1697779855663</v>
+        <v>168.1697779855662</v>
       </c>
       <c r="C10" t="n">
         <v>170.4258137347867</v>
       </c>
       <c r="D10" t="n">
-        <v>166.190212012857</v>
+        <v>166.1902120128572</v>
       </c>
       <c r="E10" t="n">
-        <v>155.7592062707918</v>
+        <v>155.7592062707919</v>
       </c>
       <c r="F10" t="n">
         <v>168.6380615280795</v>
       </c>
       <c r="G10" t="n">
-        <v>164.5504709360891</v>
+        <v>164.550470936089</v>
       </c>
       <c r="H10" t="n">
         <v>165.7819986832377</v>
       </c>
       <c r="I10" t="n">
-        <v>168.3175166077737</v>
+        <v>168.3175166077736</v>
       </c>
       <c r="J10" t="n">
-        <v>164.4735162506578</v>
+        <v>164.4735162506577</v>
       </c>
       <c r="K10" t="n">
         <v>168.0106031748397</v>
@@ -4431,28 +4431,28 @@
         <v>164.1969035474396</v>
       </c>
       <c r="M10" t="n">
-        <v>159.6069865773329</v>
+        <v>159.6069865773328</v>
       </c>
       <c r="N10" t="n">
-        <v>165.4714780274922</v>
+        <v>165.4714780274923</v>
       </c>
       <c r="O10" t="n">
-        <v>164.0550266070536</v>
+        <v>164.0550266070537</v>
       </c>
       <c r="P10" t="n">
-        <v>160.9961017381817</v>
+        <v>160.9961017381818</v>
       </c>
       <c r="Q10" t="n">
-        <v>167.3103492911012</v>
+        <v>167.3103492911011</v>
       </c>
       <c r="R10" t="n">
         <v>167.6712837213901</v>
       </c>
       <c r="S10" t="n">
-        <v>165.3161943240865</v>
+        <v>165.3161943240866</v>
       </c>
       <c r="T10" t="n">
-        <v>166.1020928755241</v>
+        <v>166.1020928755239</v>
       </c>
       <c r="U10" t="n">
         <v>163.1704727399612</v>
@@ -4464,19 +4464,19 @@
         <v>159.5888022169207</v>
       </c>
       <c r="X10" t="n">
-        <v>163.8236187171357</v>
+        <v>163.8236187171358</v>
       </c>
       <c r="Y10" t="n">
-        <v>158.1997443397384</v>
+        <v>158.1997443397383</v>
       </c>
       <c r="Z10" t="n">
-        <v>165.690281278102</v>
+        <v>165.6902812781019</v>
       </c>
       <c r="AA10" t="n">
         <v>166.3319165670777</v>
       </c>
       <c r="AB10" t="n">
-        <v>158.0194259115066</v>
+        <v>158.0194259115065</v>
       </c>
     </row>
     <row r="11">
@@ -4492,22 +4492,22 @@
         <v>170.4014931148332</v>
       </c>
       <c r="D11" t="n">
-        <v>169.1981208724003</v>
+        <v>169.1981208724004</v>
       </c>
       <c r="E11" t="n">
-        <v>156.8317923168439</v>
+        <v>156.8317923168437</v>
       </c>
       <c r="F11" t="n">
-        <v>169.898616996563</v>
+        <v>169.8986169965632</v>
       </c>
       <c r="G11" t="n">
-        <v>168.7076227188801</v>
+        <v>168.7076227188802</v>
       </c>
       <c r="H11" t="n">
         <v>169.0917724465108</v>
       </c>
       <c r="I11" t="n">
-        <v>169.8047444821569</v>
+        <v>169.804744482157</v>
       </c>
       <c r="J11" t="n">
         <v>168.6915472016057</v>
@@ -4519,22 +4519,22 @@
         <v>168.6158479226105</v>
       </c>
       <c r="M11" t="n">
-        <v>167.3360811294379</v>
+        <v>167.3360811294378</v>
       </c>
       <c r="N11" t="n">
-        <v>168.9875552176277</v>
+        <v>168.9875552176279</v>
       </c>
       <c r="O11" t="n">
-        <v>168.56273017207</v>
+        <v>168.5627301720701</v>
       </c>
       <c r="P11" t="n">
         <v>167.682566425336</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.5135784112207</v>
+        <v>169.5135784112208</v>
       </c>
       <c r="R11" t="n">
-        <v>169.6235396557956</v>
+        <v>169.6235396557955</v>
       </c>
       <c r="S11" t="n">
         <v>168.9310196813804</v>
@@ -4543,10 +4543,10 @@
         <v>169.1739430476423</v>
       </c>
       <c r="U11" t="n">
-        <v>168.320589259444</v>
+        <v>168.3205892594441</v>
       </c>
       <c r="V11" t="n">
-        <v>173.9503335408541</v>
+        <v>173.9503335408542</v>
       </c>
       <c r="W11" t="n">
         <v>167.3027337026154</v>
@@ -4558,10 +4558,10 @@
         <v>166.9104339554738</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.0353281563128</v>
+        <v>169.0353281563129</v>
       </c>
       <c r="AA11" t="n">
-        <v>169.2294314775895</v>
+        <v>169.2294314775896</v>
       </c>
       <c r="AB11" t="n">
         <v>166.8759362163973</v>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>171.9775869488316</v>
+        <v>171.9775869488317</v>
       </c>
       <c r="C2" t="n">
-        <v>171.7163770740889</v>
+        <v>171.716377074089</v>
       </c>
       <c r="D2" t="n">
-        <v>172.0942646533535</v>
+        <v>172.0942646533538</v>
       </c>
       <c r="E2" t="n">
-        <v>158.3802240093392</v>
+        <v>158.3802240093391</v>
       </c>
       <c r="F2" t="n">
-        <v>172.2686493829424</v>
+        <v>172.2686493829426</v>
       </c>
       <c r="G2" t="n">
-        <v>172.5392774741981</v>
+        <v>172.5392774741985</v>
       </c>
       <c r="H2" t="n">
-        <v>172.3824859527534</v>
+        <v>172.3824859527535</v>
       </c>
       <c r="I2" t="n">
-        <v>172.2539311418144</v>
+        <v>172.2539311418147</v>
       </c>
       <c r="J2" t="n">
-        <v>172.5717551883196</v>
+        <v>172.5717551883199</v>
       </c>
       <c r="K2" t="n">
-        <v>172.4955267095549</v>
+        <v>172.4955267095552</v>
       </c>
       <c r="L2" t="n">
         <v>172.7590298237418</v>
       </c>
       <c r="M2" t="n">
-        <v>173.3296070903945</v>
+        <v>173.3296070903947</v>
       </c>
       <c r="N2" t="n">
-        <v>172.3518096668423</v>
+        <v>172.3518096668427</v>
       </c>
       <c r="O2" t="n">
-        <v>172.4283818679339</v>
+        <v>172.4283818679341</v>
       </c>
       <c r="P2" t="n">
-        <v>173.0151590768775</v>
+        <v>173.0151590768776</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.3412347502885</v>
+        <v>172.3412347502886</v>
       </c>
       <c r="R2" t="n">
         <v>172.2326607460868</v>
       </c>
       <c r="S2" t="n">
-        <v>172.6313151136089</v>
+        <v>172.6313151136093</v>
       </c>
       <c r="T2" t="n">
-        <v>172.5020976722987</v>
+        <v>172.5020976722989</v>
       </c>
       <c r="U2" t="n">
-        <v>172.8010664797432</v>
+        <v>172.8010664797434</v>
       </c>
       <c r="V2" t="n">
         <v>177.2748906782128</v>
       </c>
       <c r="W2" t="n">
-        <v>173.3757771544426</v>
+        <v>173.3757771544428</v>
       </c>
       <c r="X2" t="n">
-        <v>172.9003687853475</v>
+        <v>172.9003687853477</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.5070333257528</v>
+        <v>173.5070333257529</v>
       </c>
       <c r="Z2" t="n">
-        <v>172.1022323613247</v>
+        <v>172.1022323613249</v>
       </c>
       <c r="AA2" t="n">
-        <v>172.4956178669107</v>
+        <v>172.4956178669108</v>
       </c>
       <c r="AB2" t="n">
-        <v>173.5547516543365</v>
+        <v>173.5547516543368</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="C3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="D3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="E3" t="n">
-        <v>160.3882807818292</v>
+        <v>160.3882807818294</v>
       </c>
       <c r="F3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="G3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="H3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="I3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="J3" t="n">
-        <v>173.7252128295002</v>
+        <v>173.7252128295004</v>
       </c>
       <c r="K3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="L3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="M3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="N3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="O3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="P3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="R3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="S3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="T3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="U3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="V3" t="n">
-        <v>178.728599622458</v>
+        <v>178.7285996224579</v>
       </c>
       <c r="W3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="X3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="Y3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="Z3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="AA3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
       <c r="AB3" t="n">
-        <v>173.7296170517013</v>
+        <v>173.7296170517016</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>219.4039977178014</v>
+        <v>219.4039977178023</v>
       </c>
       <c r="C4" t="n">
-        <v>169.9763590282179</v>
+        <v>169.976359028218</v>
       </c>
       <c r="D4" t="n">
-        <v>269.2813455589134</v>
+        <v>269.2813455589136</v>
       </c>
       <c r="E4" t="n">
-        <v>116.5441119451868</v>
+        <v>116.5441119451871</v>
       </c>
       <c r="F4" t="n">
-        <v>321.0361598297608</v>
+        <v>321.0361598297604</v>
       </c>
       <c r="G4" t="n">
-        <v>344.7074326360739</v>
+        <v>344.7074326360738</v>
       </c>
       <c r="H4" t="n">
-        <v>375.8790869680272</v>
+        <v>375.8790869680279</v>
       </c>
       <c r="I4" t="n">
-        <v>321.8861440005463</v>
+        <v>321.8861440005466</v>
       </c>
       <c r="J4" t="n">
-        <v>373.873016562933</v>
+        <v>373.8730165629325</v>
       </c>
       <c r="K4" t="n">
-        <v>344.5225273787111</v>
+        <v>344.5225273787121</v>
       </c>
       <c r="L4" t="n">
-        <v>417.0028050486811</v>
+        <v>417.0028050486814</v>
       </c>
       <c r="M4" t="n">
-        <v>587.9733367677208</v>
+        <v>587.9733367677211</v>
       </c>
       <c r="N4" t="n">
-        <v>343.7109337569927</v>
+        <v>343.7109337569929</v>
       </c>
       <c r="O4" t="n">
         <v>316.4581255681867</v>
       </c>
       <c r="P4" t="n">
-        <v>452.5809687786386</v>
+        <v>452.5809687786381</v>
       </c>
       <c r="Q4" t="n">
         <v>323.9046889922301</v>
       </c>
       <c r="R4" t="n">
-        <v>327.4000075328506</v>
+        <v>327.4000075328515</v>
       </c>
       <c r="S4" t="n">
-        <v>376.1890760574997</v>
+        <v>376.1890760575</v>
       </c>
       <c r="T4" t="n">
-        <v>392.1854930090839</v>
+        <v>392.1854930090852</v>
       </c>
       <c r="U4" t="n">
-        <v>416.2845087022958</v>
+        <v>416.2845087022965</v>
       </c>
       <c r="V4" t="n">
-        <v>296.0338264355122</v>
+        <v>296.0338264355114</v>
       </c>
       <c r="W4" t="n">
-        <v>597.4363927143245</v>
+        <v>597.4363927143231</v>
       </c>
       <c r="X4" t="n">
-        <v>470.1207319466226</v>
+        <v>470.1207319466224</v>
       </c>
       <c r="Y4" t="n">
         <v>636.3781589362229</v>
       </c>
       <c r="Z4" t="n">
-        <v>229.7478315380899</v>
+        <v>229.7478315380903</v>
       </c>
       <c r="AA4" t="n">
-        <v>375.3568853311311</v>
+        <v>375.3568853311314</v>
       </c>
       <c r="AB4" t="n">
-        <v>695.1201085975811</v>
+        <v>695.1201085975802</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.423594689004901</v>
+        <v>5.423594689005147</v>
       </c>
       <c r="C5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="D5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="E5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="F5" t="n">
-        <v>5.423594689004847</v>
+        <v>5.423594689005025</v>
       </c>
       <c r="G5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="H5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="I5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="J5" t="n">
-        <v>5.427792058692323</v>
+        <v>5.42779205869252</v>
       </c>
       <c r="K5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4235946890049</v>
+        <v>5.423594689005211</v>
       </c>
       <c r="M5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="N5" t="n">
-        <v>343.7109337569927</v>
+        <v>5.423594689005025</v>
       </c>
       <c r="O5" t="n">
-        <v>5.423594689004847</v>
+        <v>5.423594689005025</v>
       </c>
       <c r="P5" t="n">
-        <v>5.423594689004847</v>
+        <v>5.423594689005025</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.423594689004847</v>
+        <v>5.423594689005025</v>
       </c>
       <c r="R5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="S5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="T5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="U5" t="n">
-        <v>5.241177304512232</v>
+        <v>5.241177304512507</v>
       </c>
       <c r="V5" t="n">
-        <v>5.450468418765815</v>
+        <v>5.450468418765811</v>
       </c>
       <c r="W5" t="n">
-        <v>5.423594689004847</v>
+        <v>5.423594689005025</v>
       </c>
       <c r="X5" t="n">
-        <v>5.423594689004902</v>
+        <v>5.423594689005021</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.241177304512232</v>
+        <v>5.241177304512507</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.423594689004873</v>
+        <v>5.423594689005195</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.423594689004847</v>
+        <v>5.423594689005025</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="C6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="D6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="E6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="F6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="G6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="H6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="I6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="J6" t="n">
-        <v>763.5418455461997</v>
+        <v>763.5418455462002</v>
       </c>
       <c r="K6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="L6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="M6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="N6" t="n">
-        <v>343.7109337569927</v>
+        <v>637.9724842535311</v>
       </c>
       <c r="O6" t="n">
-        <v>637.9803953765343</v>
+        <v>637.9803953765347</v>
       </c>
       <c r="P6" t="n">
-        <v>763.87919053548</v>
+        <v>763.8791905354803</v>
       </c>
       <c r="Q6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="R6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="S6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="T6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="U6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="V6" t="n">
-        <v>637.92317221649</v>
+        <v>637.923172216489</v>
       </c>
       <c r="W6" t="n">
-        <v>670.2856267758682</v>
+        <v>670.2856267758673</v>
       </c>
       <c r="X6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="Y6" t="n">
-        <v>665.7247383956521</v>
+        <v>665.7247383956517</v>
       </c>
       <c r="Z6" t="n">
-        <v>637.8962984867286</v>
+        <v>637.8962984867281</v>
       </c>
       <c r="AA6" t="n">
-        <v>763.5376481765114</v>
+        <v>763.5376481765131</v>
       </c>
       <c r="AB6" t="n">
-        <v>638.0731697327744</v>
+        <v>638.0731697327741</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.13855490482913</v>
+        <v>11.13855490482939</v>
       </c>
       <c r="C7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="D7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="E7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="F7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="G7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="H7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="I7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="J7" t="n">
-        <v>11.14275227451654</v>
+        <v>11.1427522745167</v>
       </c>
       <c r="K7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="L7" t="n">
-        <v>11.13855490482913</v>
+        <v>11.13855490482939</v>
       </c>
       <c r="M7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="N7" t="n">
-        <v>343.7109337569927</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="O7" t="n">
-        <v>11.13853536443425</v>
+        <v>11.13853536443451</v>
       </c>
       <c r="P7" t="n">
-        <v>11.13853536443425</v>
+        <v>11.13853536443451</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="R7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="S7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="T7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="U7" t="n">
-        <v>11.09303029659385</v>
+        <v>11.09303029659393</v>
       </c>
       <c r="V7" t="n">
-        <v>11.16542863459003</v>
+        <v>11.16542863459</v>
       </c>
       <c r="W7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="X7" t="n">
-        <v>11.13855490482913</v>
+        <v>11.13855490482939</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.13855490482908</v>
+        <v>11.13855490482937</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.25219775224613</v>
+        <v>13.25219775224628</v>
       </c>
       <c r="C8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="D8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="E8" t="n">
-        <v>15.99585549005299</v>
+        <v>15.99585549005322</v>
       </c>
       <c r="F8" t="n">
-        <v>14.16642842815665</v>
+        <v>14.16642842815678</v>
       </c>
       <c r="G8" t="n">
-        <v>20.33746842284439</v>
+        <v>20.33746842284457</v>
       </c>
       <c r="H8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="I8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="J8" t="n">
-        <v>19.12481144030782</v>
+        <v>19.12481144030788</v>
       </c>
       <c r="K8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="L8" t="n">
-        <v>19.12061407062037</v>
+        <v>19.12061407062062</v>
       </c>
       <c r="M8" t="n">
-        <v>19.1206140706362</v>
+        <v>19.12061407063644</v>
       </c>
       <c r="N8" t="n">
-        <v>343.7109337569927</v>
+        <v>14.57160965729714</v>
       </c>
       <c r="O8" t="n">
-        <v>15.8217155645427</v>
+        <v>15.82171556454295</v>
       </c>
       <c r="P8" t="n">
-        <v>15.5152844002851</v>
+        <v>15.51528440028536</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.09892000764792</v>
+        <v>12.09892000764817</v>
       </c>
       <c r="R8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="S8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="T8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="U8" t="n">
-        <v>16.22105307552038</v>
+        <v>16.22105307552036</v>
       </c>
       <c r="V8" t="n">
-        <v>17.50466452573026</v>
+        <v>17.50466452573025</v>
       </c>
       <c r="W8" t="n">
-        <v>19.12176737508999</v>
+        <v>19.12176737509011</v>
       </c>
       <c r="X8" t="n">
-        <v>12.63677201934377</v>
+        <v>12.63677201934406</v>
       </c>
       <c r="Y8" t="n">
-        <v>24.89511815416399</v>
+        <v>24.89511815416423</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.14318890694104</v>
+        <v>13.14318890694134</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.12061407062034</v>
+        <v>19.1206140706206</v>
       </c>
       <c r="AB8" t="n">
-        <v>25.25066561718343</v>
+        <v>25.25066561718362</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.59272016264918</v>
+        <v>23.59272016264933</v>
       </c>
       <c r="C9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="D9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="E9" t="n">
-        <v>27.75717031278843</v>
+        <v>27.75717031278878</v>
       </c>
       <c r="F9" t="n">
-        <v>16.52600772424947</v>
+        <v>16.52600772424979</v>
       </c>
       <c r="G9" t="n">
-        <v>29.00669320859987</v>
+        <v>29.00669320859996</v>
       </c>
       <c r="H9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="I9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="J9" t="n">
-        <v>29.01089057505225</v>
+        <v>29.01089057505233</v>
       </c>
       <c r="K9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="L9" t="n">
-        <v>29.00669320536477</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="M9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="N9" t="n">
-        <v>343.7109337569927</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="O9" t="n">
-        <v>30.80087678703532</v>
+        <v>30.8008767870356</v>
       </c>
       <c r="P9" t="n">
-        <v>31.19108093233916</v>
+        <v>31.19108093233929</v>
       </c>
       <c r="Q9" t="n">
-        <v>29.00669320859987</v>
+        <v>29.00669320859996</v>
       </c>
       <c r="R9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="S9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="T9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="U9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="V9" t="n">
-        <v>35.28116813397067</v>
+        <v>35.28116813397065</v>
       </c>
       <c r="W9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="X9" t="n">
-        <v>29.00669320536477</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.742548891159</v>
+        <v>25.7425488911592</v>
       </c>
       <c r="AA9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
       <c r="AB9" t="n">
-        <v>29.00669320536475</v>
+        <v>29.00669320536507</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168.1872633079682</v>
+        <v>168.1872633079685</v>
       </c>
       <c r="C10" t="n">
-        <v>169.7981650636615</v>
+        <v>169.7981650636617</v>
       </c>
       <c r="D10" t="n">
-        <v>167.5892334648389</v>
+        <v>167.5892334648394</v>
       </c>
       <c r="E10" t="n">
-        <v>157.6245592010039</v>
+        <v>157.6245592010043</v>
       </c>
       <c r="F10" t="n">
-        <v>166.602729611377</v>
+        <v>166.6027296113773</v>
       </c>
       <c r="G10" t="n">
         <v>164.8506091264425</v>
       </c>
       <c r="H10" t="n">
-        <v>165.9537786226346</v>
+        <v>165.9537786226348</v>
       </c>
       <c r="I10" t="n">
-        <v>166.6672316284902</v>
+        <v>166.6672316284903</v>
       </c>
       <c r="J10" t="n">
-        <v>164.6962871950574</v>
+        <v>164.6962871950577</v>
       </c>
       <c r="K10" t="n">
-        <v>165.2267871374085</v>
+        <v>165.2267871374087</v>
       </c>
       <c r="L10" t="n">
-        <v>163.6022956766481</v>
+        <v>163.6022956766483</v>
       </c>
       <c r="M10" t="n">
-        <v>160.4039483228433</v>
+        <v>160.4039483228434</v>
       </c>
       <c r="N10" t="n">
-        <v>166.048284678595</v>
+        <v>166.0482846785951</v>
       </c>
       <c r="O10" t="n">
         <v>165.496448014452</v>
       </c>
       <c r="P10" t="n">
-        <v>161.991386810044</v>
+        <v>161.9913868100442</v>
       </c>
       <c r="Q10" t="n">
-        <v>166.1231919289612</v>
+        <v>166.1231919289614</v>
       </c>
       <c r="R10" t="n">
-        <v>166.8059728844276</v>
+        <v>166.8059728844277</v>
       </c>
       <c r="S10" t="n">
-        <v>164.3272480385497</v>
+        <v>164.3272480385499</v>
       </c>
       <c r="T10" t="n">
-        <v>165.2057557306127</v>
+        <v>165.2057557306129</v>
       </c>
       <c r="U10" t="n">
-        <v>163.3434207351212</v>
+        <v>163.3434207351214</v>
       </c>
       <c r="V10" t="n">
-        <v>170.9574167727565</v>
+        <v>170.9574167727564</v>
       </c>
       <c r="W10" t="n">
-        <v>159.9791698156313</v>
+        <v>159.9791698156314</v>
       </c>
       <c r="X10" t="n">
-        <v>162.8569996206384</v>
+        <v>162.8569996206386</v>
       </c>
       <c r="Y10" t="n">
-        <v>159.227958834239</v>
+        <v>159.2279588342394</v>
       </c>
       <c r="Z10" t="n">
-        <v>167.4526899595292</v>
+        <v>167.4526899595294</v>
       </c>
       <c r="AA10" t="n">
-        <v>165.1808036683825</v>
+        <v>165.1808036683826</v>
       </c>
       <c r="AB10" t="n">
-        <v>159.037742971155</v>
+        <v>159.0377429711551</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>169.4557983329994</v>
+        <v>169.4557983329996</v>
       </c>
       <c r="C11" t="n">
-        <v>169.9275538907366</v>
+        <v>169.9275538907367</v>
       </c>
       <c r="D11" t="n">
-        <v>169.3003705530897</v>
+        <v>169.3003705530899</v>
       </c>
       <c r="E11" t="n">
-        <v>157.1227218826054</v>
+        <v>157.1227218826057</v>
       </c>
       <c r="F11" t="n">
-        <v>169.0258928855521</v>
+        <v>169.0258928855524</v>
       </c>
       <c r="G11" t="n">
-        <v>168.4993005724862</v>
+        <v>168.4993005724864</v>
       </c>
       <c r="H11" t="n">
-        <v>168.8444546874011</v>
+        <v>168.8444546874012</v>
       </c>
       <c r="I11" t="n">
-        <v>169.0405232677665</v>
+        <v>169.0405232677666</v>
       </c>
       <c r="J11" t="n">
-        <v>168.4635652511695</v>
+        <v>168.4635652511697</v>
       </c>
       <c r="K11" t="n">
-        <v>168.6267120016406</v>
+        <v>168.6267120016408</v>
       </c>
       <c r="L11" t="n">
-        <v>168.1510663242342</v>
+        <v>168.1510663242344</v>
       </c>
       <c r="M11" t="n">
-        <v>167.2663853523775</v>
+        <v>167.2663853523776</v>
       </c>
       <c r="N11" t="n">
-        <v>168.8567789581252</v>
+        <v>168.8567789581253</v>
       </c>
       <c r="O11" t="n">
-        <v>168.6822637184325</v>
+        <v>168.6822637184327</v>
       </c>
       <c r="P11" t="n">
-        <v>167.6742269094032</v>
+        <v>167.6742269094034</v>
       </c>
       <c r="Q11" t="n">
-        <v>168.8802870792032</v>
+        <v>168.8802870792034</v>
       </c>
       <c r="R11" t="n">
-        <v>169.0823805856324</v>
+        <v>169.0823805856325</v>
       </c>
       <c r="S11" t="n">
-        <v>168.3532072490529</v>
+        <v>168.3532072490531</v>
       </c>
       <c r="T11" t="n">
-        <v>168.6237136072691</v>
+        <v>168.6237136072694</v>
       </c>
       <c r="U11" t="n">
-        <v>168.0753140568554</v>
+        <v>168.0753140568555</v>
       </c>
       <c r="V11" t="n">
-        <v>173.7389777163083</v>
+        <v>173.7389777163084</v>
       </c>
       <c r="W11" t="n">
-        <v>167.1192798419553</v>
+        <v>167.1192798419555</v>
       </c>
       <c r="X11" t="n">
-        <v>167.953293205238</v>
+        <v>167.9532932052383</v>
       </c>
       <c r="Y11" t="n">
-        <v>166.9087326227648</v>
+        <v>166.9087326227649</v>
       </c>
       <c r="Z11" t="n">
-        <v>169.2462105310068</v>
+        <v>169.246210531007</v>
       </c>
       <c r="AA11" t="n">
-        <v>168.6058805340489</v>
+        <v>168.605880534049</v>
       </c>
       <c r="AB11" t="n">
-        <v>166.8699021274632</v>
+        <v>166.8699021274635</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>5.426780208501076</v>
       </c>
       <c r="N5" t="n">
-        <v>416.8308364519177</v>
+        <v>5.426780208501124</v>
       </c>
       <c r="O5" t="n">
         <v>5.426780208501124</v>
@@ -6154,7 +6154,7 @@
         <v>818.4463195903928</v>
       </c>
       <c r="N6" t="n">
-        <v>416.8308364519177</v>
+        <v>684.2025046861365</v>
       </c>
       <c r="O6" t="n">
         <v>818.8540499043318</v>
@@ -6242,7 +6242,7 @@
         <v>11.21815309249012</v>
       </c>
       <c r="N7" t="n">
-        <v>416.8308364519177</v>
+        <v>11.21815309249012</v>
       </c>
       <c r="O7" t="n">
         <v>11.21812499409882</v>
@@ -6330,7 +6330,7 @@
         <v>18.95787377488732</v>
       </c>
       <c r="N8" t="n">
-        <v>416.8308364519177</v>
+        <v>14.44998182334048</v>
       </c>
       <c r="O8" t="n">
         <v>15.68878966842913</v>
@@ -6418,7 +6418,7 @@
         <v>31.88725152261904</v>
       </c>
       <c r="N9" t="n">
-        <v>416.8308364519177</v>
+        <v>31.88725152261904</v>
       </c>
       <c r="O9" t="n">
         <v>33.89012998907395</v>
@@ -6835,7 +6835,7 @@
         <v>170.1609896414295</v>
       </c>
       <c r="M2" t="n">
-        <v>170.568462660584</v>
+        <v>170.5684626605841</v>
       </c>
       <c r="N2" t="n">
         <v>171.176215954515</v>
@@ -6981,7 +6981,7 @@
         <v>23.24849507723148</v>
       </c>
       <c r="C4" t="n">
-        <v>56.7781528534291</v>
+        <v>56.77815285342909</v>
       </c>
       <c r="D4" t="n">
         <v>43.88056483534228</v>
@@ -7102,7 +7102,7 @@
         <v>4.585316045556392</v>
       </c>
       <c r="N5" t="n">
-        <v>289.8036832645923</v>
+        <v>4.585316045556352</v>
       </c>
       <c r="O5" t="n">
         <v>4.585316045556353</v>
@@ -7190,7 +7190,7 @@
         <v>761.0519813523588</v>
       </c>
       <c r="N6" t="n">
-        <v>289.8036832645923</v>
+        <v>636.4859678989335</v>
       </c>
       <c r="O6" t="n">
         <v>761.4063636345336</v>
@@ -7278,7 +7278,7 @@
         <v>9.374826227402025</v>
       </c>
       <c r="N7" t="n">
-        <v>289.8036832645923</v>
+        <v>9.374826227402025</v>
       </c>
       <c r="O7" t="n">
         <v>9.374809394756436</v>
@@ -7299,7 +7299,7 @@
         <v>9.374826227402025</v>
       </c>
       <c r="U7" t="n">
-        <v>9.345593857872478</v>
+        <v>9.345593857872476</v>
       </c>
       <c r="V7" t="n">
         <v>9.418378490667212</v>
@@ -7366,7 +7366,7 @@
         <v>15.10403718185548</v>
       </c>
       <c r="N8" t="n">
-        <v>289.8036832645923</v>
+        <v>11.61070979188588</v>
       </c>
       <c r="O8" t="n">
         <v>12.57070648739145</v>
@@ -7454,7 +7454,7 @@
         <v>24.50271022448729</v>
       </c>
       <c r="N9" t="n">
-        <v>289.8036832645923</v>
+        <v>24.50271022448729</v>
       </c>
       <c r="O9" t="n">
         <v>26.01024511148415</v>
@@ -8138,7 +8138,7 @@
         <v>4.121178715188286</v>
       </c>
       <c r="N5" t="n">
-        <v>206.4866000748666</v>
+        <v>4.121178715188329</v>
       </c>
       <c r="O5" t="n">
         <v>4.121178715188329</v>
@@ -8226,7 +8226,7 @@
         <v>759.890577886996</v>
       </c>
       <c r="N6" t="n">
-        <v>206.4866000748666</v>
+        <v>635.6896809621197</v>
       </c>
       <c r="O6" t="n">
         <v>635.6994911929473</v>
@@ -8314,7 +8314,7 @@
         <v>8.598166683409753</v>
       </c>
       <c r="N7" t="n">
-        <v>206.4866000748666</v>
+        <v>8.598166683409753</v>
       </c>
       <c r="O7" t="n">
         <v>8.598158697957293</v>
@@ -8402,7 +8402,7 @@
         <v>13.59839639647518</v>
       </c>
       <c r="N8" t="n">
-        <v>206.4866000748666</v>
+        <v>10.4610437228539</v>
       </c>
       <c r="O8" t="n">
         <v>11.32321547592136</v>
@@ -8490,7 +8490,7 @@
         <v>20.74224886080052</v>
       </c>
       <c r="N9" t="n">
-        <v>206.4866000748666</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="O9" t="n">
         <v>22.00303894267023</v>
@@ -9174,7 +9174,7 @@
         <v>6.090398877275047</v>
       </c>
       <c r="N5" t="n">
-        <v>440.9349012043079</v>
+        <v>6.090398877275066</v>
       </c>
       <c r="O5" t="n">
         <v>6.090398877275066</v>
@@ -9262,7 +9262,7 @@
         <v>685.0675768008595</v>
       </c>
       <c r="N6" t="n">
-        <v>440.9349012043079</v>
+        <v>685.1200795267611</v>
       </c>
       <c r="O6" t="n">
         <v>820.7465933818351</v>
@@ -9350,7 +9350,7 @@
         <v>12.54240013793387</v>
       </c>
       <c r="N7" t="n">
-        <v>440.9349012043079</v>
+        <v>12.54240013793387</v>
       </c>
       <c r="O7" t="n">
         <v>12.54234011726369</v>
@@ -9438,7 +9438,7 @@
         <v>21.82358147012943</v>
       </c>
       <c r="N8" t="n">
-        <v>440.9349012043079</v>
+        <v>16.57110441210643</v>
       </c>
       <c r="O8" t="n">
         <v>18.01453070894693</v>
@@ -9526,7 +9526,7 @@
         <v>37.32503494048741</v>
       </c>
       <c r="N9" t="n">
-        <v>440.9349012043079</v>
+        <v>37.32503494048741</v>
       </c>
       <c r="O9" t="n">
         <v>39.69007078716862</v>
@@ -10210,7 +10210,7 @@
         <v>4.9686735025296</v>
       </c>
       <c r="N5" t="n">
-        <v>293.057451144516</v>
+        <v>4.9686735025296</v>
       </c>
       <c r="O5" t="n">
         <v>4.9686735025296</v>
@@ -10298,7 +10298,7 @@
         <v>636.9962198776859</v>
       </c>
       <c r="N6" t="n">
-        <v>293.057451144516</v>
+        <v>637.0295910508607</v>
       </c>
       <c r="O6" t="n">
         <v>762.6513049924789</v>
@@ -10386,7 +10386,7 @@
         <v>10.16081329673456</v>
       </c>
       <c r="N7" t="n">
-        <v>293.057451144516</v>
+        <v>10.16081329673456</v>
       </c>
       <c r="O7" t="n">
         <v>10.16078544775103</v>
@@ -10474,7 +10474,7 @@
         <v>17.01189267746548</v>
       </c>
       <c r="N8" t="n">
-        <v>293.057451144516</v>
+        <v>12.99557752676147</v>
       </c>
       <c r="O8" t="n">
         <v>14.09929579937037</v>
@@ -10562,7 +10562,7 @@
         <v>27.81835647886587</v>
       </c>
       <c r="N9" t="n">
-        <v>293.057451144516</v>
+        <v>27.81835647886587</v>
       </c>
       <c r="O9" t="n">
         <v>29.55163598482603</v>

--- a/Results/Phase 2/Hydrogen/hydrogen resource use fossils results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen resource use fossils results.xlsx
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173.8145854905864</v>
+        <v>173.8145854905863</v>
       </c>
       <c r="C2" t="n">
-        <v>172.7420160708907</v>
+        <v>172.7420160708906</v>
       </c>
       <c r="D2" t="n">
         <v>173.3180902744197</v>
       </c>
       <c r="E2" t="n">
-        <v>159.700898777381</v>
+        <v>159.7008987773814</v>
       </c>
       <c r="F2" t="n">
         <v>173.3472175628494</v>
       </c>
       <c r="G2" t="n">
-        <v>174.0684880528504</v>
+        <v>174.0684880528503</v>
       </c>
       <c r="H2" t="n">
-        <v>174.0985486586491</v>
+        <v>174.0985486586492</v>
       </c>
       <c r="I2" t="n">
-        <v>173.1751026173185</v>
+        <v>173.1751026173184</v>
       </c>
       <c r="J2" t="n">
         <v>174.1385740319675</v>
@@ -616,22 +616,22 @@
         <v>173.9485971805979</v>
       </c>
       <c r="L2" t="n">
-        <v>174.4789231611575</v>
+        <v>174.4789231611573</v>
       </c>
       <c r="M2" t="n">
-        <v>175.3206705832821</v>
+        <v>175.320670583282</v>
       </c>
       <c r="N2" t="n">
-        <v>174.2895116942584</v>
+        <v>174.2895116942583</v>
       </c>
       <c r="O2" t="n">
-        <v>173.9712161625934</v>
+        <v>173.9712161625933</v>
       </c>
       <c r="P2" t="n">
         <v>174.5248542684616</v>
       </c>
       <c r="Q2" t="n">
-        <v>173.7649051733129</v>
+        <v>173.7649051733127</v>
       </c>
       <c r="R2" t="n">
         <v>173.4277778934625</v>
@@ -640,13 +640,13 @@
         <v>174.0121492630836</v>
       </c>
       <c r="T2" t="n">
-        <v>173.9587903912523</v>
+        <v>173.9587903912521</v>
       </c>
       <c r="U2" t="n">
         <v>174.8434913851698</v>
       </c>
       <c r="V2" t="n">
-        <v>178.8202422960795</v>
+        <v>178.8202422960794</v>
       </c>
       <c r="W2" t="n">
         <v>174.8768289137865</v>
@@ -655,13 +655,13 @@
         <v>173.689612786639</v>
       </c>
       <c r="Y2" t="n">
-        <v>175.0673438035884</v>
+        <v>175.0673438035885</v>
       </c>
       <c r="Z2" t="n">
-        <v>174.1443241952892</v>
+        <v>174.1443241952891</v>
       </c>
       <c r="AA2" t="n">
-        <v>173.8604689588245</v>
+        <v>173.8604689588244</v>
       </c>
       <c r="AB2" t="n">
         <v>175.3056050755021</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="C3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="D3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="E3" t="n">
-        <v>161.1664789020084</v>
+        <v>161.1664789020086</v>
       </c>
       <c r="F3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="G3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="H3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="I3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="J3" t="n">
-        <v>174.9461674590273</v>
+        <v>174.9461674590271</v>
       </c>
       <c r="K3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="L3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="M3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="N3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="O3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="P3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="Q3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="R3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="S3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="T3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="U3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="V3" t="n">
         <v>179.9793522035423</v>
       </c>
       <c r="W3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="X3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="Y3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="AA3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
       <c r="AB3" t="n">
-        <v>174.954746980573</v>
+        <v>174.9547469805728</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>425.2346822035043</v>
+        <v>425.2346822035046</v>
       </c>
       <c r="C4" t="n">
-        <v>151.314351366044</v>
+        <v>151.3143513660442</v>
       </c>
       <c r="D4" t="n">
-        <v>328.5446797351094</v>
+        <v>328.54467973511</v>
       </c>
       <c r="E4" t="n">
-        <v>299.6260352669206</v>
+        <v>299.6260352669203</v>
       </c>
       <c r="F4" t="n">
-        <v>344.3210843418898</v>
+        <v>344.3210843418895</v>
       </c>
       <c r="G4" t="n">
-        <v>508.1045914668832</v>
+        <v>508.1045914668826</v>
       </c>
       <c r="H4" t="n">
-        <v>587.8261856536863</v>
+        <v>587.8261856536858</v>
       </c>
       <c r="I4" t="n">
-        <v>288.0689684562194</v>
+        <v>288.0689684562191</v>
       </c>
       <c r="J4" t="n">
-        <v>543.3804345260969</v>
+        <v>543.3804345260965</v>
       </c>
       <c r="K4" t="n">
-        <v>516.5308676008013</v>
+        <v>516.5308676008</v>
       </c>
       <c r="L4" t="n">
-        <v>647.2668129524943</v>
+        <v>647.2668129524916</v>
       </c>
       <c r="M4" t="n">
-        <v>946.6114358286953</v>
+        <v>946.611435828695</v>
       </c>
       <c r="N4" t="n">
-        <v>606.9426783224385</v>
+        <v>606.9426783224393</v>
       </c>
       <c r="O4" t="n">
-        <v>456.2746303186615</v>
+        <v>456.2746303186611</v>
       </c>
       <c r="P4" t="n">
-        <v>628.5117218096593</v>
+        <v>628.511721809658</v>
       </c>
       <c r="Q4" t="n">
-        <v>455.0207636460457</v>
+        <v>455.0207636460451</v>
       </c>
       <c r="R4" t="n">
-        <v>370.1879348646798</v>
+        <v>370.1879348646793</v>
       </c>
       <c r="S4" t="n">
-        <v>492.9465738040095</v>
+        <v>492.9465738040096</v>
       </c>
       <c r="T4" t="n">
-        <v>525.4022047821289</v>
+        <v>525.4022047821312</v>
       </c>
       <c r="U4" t="n">
-        <v>737.7291167300993</v>
+        <v>737.7291167300998</v>
       </c>
       <c r="V4" t="n">
-        <v>444.8458635465482</v>
+        <v>444.8458635465466</v>
       </c>
       <c r="W4" t="n">
-        <v>767.7101791951623</v>
+        <v>767.710179195162</v>
       </c>
       <c r="X4" t="n">
         <v>435.7186488609846</v>
       </c>
       <c r="Y4" t="n">
-        <v>822.1445437181775</v>
+        <v>822.1445437181783</v>
       </c>
       <c r="Z4" t="n">
-        <v>528.7901547202509</v>
+        <v>528.7901547202511</v>
       </c>
       <c r="AA4" t="n">
-        <v>475.2229326370682</v>
+        <v>475.2229326370672</v>
       </c>
       <c r="AB4" t="n">
-        <v>977.1976751556085</v>
+        <v>977.1976751556084</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.75854761510653</v>
+        <v>17.75854761510655</v>
       </c>
       <c r="C5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="D5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="E5" t="n">
-        <v>21.61998957449338</v>
+        <v>21.61998957449352</v>
       </c>
       <c r="F5" t="n">
-        <v>19.04524188572617</v>
+        <v>19.04524188572611</v>
       </c>
       <c r="G5" t="n">
-        <v>27.73040419245611</v>
+        <v>27.73040419245602</v>
       </c>
       <c r="H5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="I5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="J5" t="n">
-        <v>26.02117275214841</v>
+        <v>26.02117275214828</v>
       </c>
       <c r="K5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="L5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="M5" t="n">
-        <v>26.01779536780447</v>
+        <v>26.01779536780423</v>
       </c>
       <c r="N5" t="n">
-        <v>606.9426783224385</v>
+        <v>19.61549661436677</v>
       </c>
       <c r="O5" t="n">
-        <v>21.37490389584131</v>
+        <v>21.37490389584126</v>
       </c>
       <c r="P5" t="n">
-        <v>20.94363065857268</v>
+        <v>20.94363065857275</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.13541692681555</v>
+        <v>16.13541692681538</v>
       </c>
       <c r="R5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="S5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="T5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780149</v>
       </c>
       <c r="U5" t="n">
-        <v>21.98973250969097</v>
+        <v>21.9897325096909</v>
       </c>
       <c r="V5" t="n">
-        <v>23.78566389108287</v>
+        <v>23.78566389108284</v>
       </c>
       <c r="W5" t="n">
-        <v>26.01941853468731</v>
+        <v>26.01941853468723</v>
       </c>
       <c r="X5" t="n">
-        <v>16.89239338737934</v>
+        <v>16.89239338737929</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.2351930761401</v>
+        <v>34.23519307613996</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.60512784884174</v>
+        <v>17.6051278488418</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.01779536780172</v>
+        <v>26.01779536780148</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.64527026138776</v>
+        <v>34.64527026138772</v>
       </c>
     </row>
     <row r="6">
@@ -941,82 +941,82 @@
         <v>38.05449447688449</v>
       </c>
       <c r="C6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="D6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="E6" t="n">
-        <v>45.13718264450337</v>
+        <v>45.13718264450316</v>
       </c>
       <c r="F6" t="n">
-        <v>26.03578401885596</v>
+        <v>26.03578401885583</v>
       </c>
       <c r="G6" t="n">
-        <v>47.26230858196617</v>
+        <v>47.26230858196603</v>
       </c>
       <c r="H6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="I6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="J6" t="n">
-        <v>47.26568431175534</v>
+        <v>47.26568431175516</v>
       </c>
       <c r="K6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="L6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="M6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="N6" t="n">
-        <v>606.9426783224385</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="O6" t="n">
-        <v>50.31376611978665</v>
+        <v>50.3137661197865</v>
       </c>
       <c r="P6" t="n">
-        <v>50.97740578006862</v>
+        <v>50.97740578006837</v>
       </c>
       <c r="Q6" t="n">
-        <v>47.26230858196617</v>
+        <v>47.26230858196603</v>
       </c>
       <c r="R6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="S6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="T6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="U6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="V6" t="n">
-        <v>57.90966915866273</v>
+        <v>57.90966915866264</v>
       </c>
       <c r="W6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="X6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="Y6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="Z6" t="n">
-        <v>41.71081546737931</v>
+        <v>41.71081546737916</v>
       </c>
       <c r="AA6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
       <c r="AB6" t="n">
-        <v>47.26230692740865</v>
+        <v>47.26230692740863</v>
       </c>
     </row>
     <row r="7">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165.7031749857646</v>
+        <v>165.7031749857645</v>
       </c>
       <c r="C7" t="n">
         <v>172.1250600331525</v>
@@ -1035,25 +1035,25 @@
         <v>168.753968191199</v>
       </c>
       <c r="E7" t="n">
-        <v>155.1682205989772</v>
+        <v>155.1682205989771</v>
       </c>
       <c r="F7" t="n">
-        <v>168.6144591536823</v>
+        <v>168.6144591536822</v>
       </c>
       <c r="G7" t="n">
-        <v>164.1986490455845</v>
+        <v>164.1986490455844</v>
       </c>
       <c r="H7" t="n">
-        <v>164.2550728020103</v>
+        <v>164.2550728020102</v>
       </c>
       <c r="I7" t="n">
-        <v>169.6015677933668</v>
+        <v>169.6015677933667</v>
       </c>
       <c r="J7" t="n">
         <v>163.7778837297635</v>
       </c>
       <c r="K7" t="n">
-        <v>165.0467230067081</v>
+        <v>165.046723006708</v>
       </c>
       <c r="L7" t="n">
         <v>161.833794302388</v>
@@ -1062,28 +1062,28 @@
         <v>157.0918486108896</v>
       </c>
       <c r="N7" t="n">
-        <v>163.013517868184</v>
+        <v>163.0135178681839</v>
       </c>
       <c r="O7" t="n">
         <v>164.7602599864261</v>
       </c>
       <c r="P7" t="n">
-        <v>161.450996356847</v>
+        <v>161.4509963568468</v>
       </c>
       <c r="Q7" t="n">
         <v>166.1141807717106</v>
       </c>
       <c r="R7" t="n">
-        <v>168.1384453401569</v>
+        <v>168.1384453401568</v>
       </c>
       <c r="S7" t="n">
-        <v>164.5600352700945</v>
+        <v>164.5600352700946</v>
       </c>
       <c r="T7" t="n">
-        <v>165.0073687444178</v>
+        <v>165.0073687444177</v>
       </c>
       <c r="U7" t="n">
-        <v>159.6632720277472</v>
+        <v>159.6632720277471</v>
       </c>
       <c r="V7" t="n">
         <v>170.3858456471519</v>
@@ -1092,19 +1092,19 @@
         <v>159.5072615164087</v>
       </c>
       <c r="X7" t="n">
-        <v>166.5697005245176</v>
+        <v>166.5697005245177</v>
       </c>
       <c r="Y7" t="n">
-        <v>158.4096129030125</v>
+        <v>158.4096129030124</v>
       </c>
       <c r="Z7" t="n">
         <v>163.7539269973718</v>
       </c>
       <c r="AA7" t="n">
-        <v>165.5134745862981</v>
+        <v>165.513474586298</v>
       </c>
       <c r="AB7" t="n">
-        <v>157.116115053566</v>
+        <v>157.1161150535659</v>
       </c>
     </row>
     <row r="8">
@@ -1120,34 +1120,34 @@
         <v>171.454499492137</v>
       </c>
       <c r="D8" t="n">
-        <v>170.496716164545</v>
+        <v>170.4967161645449</v>
       </c>
       <c r="E8" t="n">
-        <v>156.9716721341869</v>
+        <v>156.9716721341867</v>
       </c>
       <c r="F8" t="n">
-        <v>170.4623663963157</v>
+        <v>170.4623663963156</v>
       </c>
       <c r="G8" t="n">
-        <v>169.1744292147805</v>
+        <v>169.1744292147804</v>
       </c>
       <c r="H8" t="n">
-        <v>169.2301628095645</v>
+        <v>169.2301628095646</v>
       </c>
       <c r="I8" t="n">
-        <v>170.7393890275697</v>
+        <v>170.7393890275698</v>
       </c>
       <c r="J8" t="n">
-        <v>169.056969343944</v>
+        <v>169.0569693439439</v>
       </c>
       <c r="K8" t="n">
         <v>169.4404146974904</v>
       </c>
       <c r="L8" t="n">
-        <v>168.508847878588</v>
+        <v>168.5088478785881</v>
       </c>
       <c r="M8" t="n">
-        <v>167.1929948993966</v>
+        <v>167.1929948993964</v>
       </c>
       <c r="N8" t="n">
         <v>168.8562143936821</v>
@@ -1162,16 +1162,16 @@
         <v>169.7424193750676</v>
       </c>
       <c r="R8" t="n">
-        <v>170.3263389248087</v>
+        <v>170.3263389248086</v>
       </c>
       <c r="S8" t="n">
-        <v>169.2825223088351</v>
+        <v>169.282522308835</v>
       </c>
       <c r="T8" t="n">
-        <v>169.4327015933881</v>
+        <v>169.4327015933879</v>
       </c>
       <c r="U8" t="n">
-        <v>167.8858215505948</v>
+        <v>167.8858215505946</v>
       </c>
       <c r="V8" t="n">
         <v>174.4551662402305</v>
@@ -1183,16 +1183,16 @@
         <v>169.8743899275763</v>
       </c>
       <c r="Y8" t="n">
-        <v>167.5392550720845</v>
+        <v>167.5392550720844</v>
       </c>
       <c r="Z8" t="n">
-        <v>169.0479154080374</v>
+        <v>169.0479154080372</v>
       </c>
       <c r="AA8" t="n">
-        <v>169.5646599318795</v>
+        <v>169.5646599318794</v>
       </c>
       <c r="AB8" t="n">
-        <v>167.1889707003671</v>
+        <v>167.188970700367</v>
       </c>
     </row>
   </sheetData>
@@ -1358,25 +1358,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>169.9352015291462</v>
+        <v>169.9352015291464</v>
       </c>
       <c r="C2" t="n">
-        <v>170.1071156255261</v>
+        <v>170.107115625526</v>
       </c>
       <c r="D2" t="n">
-        <v>170.2496064057772</v>
+        <v>170.2496064057774</v>
       </c>
       <c r="E2" t="n">
-        <v>157.4618434098081</v>
+        <v>157.461843409808</v>
       </c>
       <c r="F2" t="n">
-        <v>170.5433330830309</v>
+        <v>170.5433330830311</v>
       </c>
       <c r="G2" t="n">
-        <v>170.7226895352258</v>
+        <v>170.7226895352259</v>
       </c>
       <c r="H2" t="n">
-        <v>170.6925337085</v>
+        <v>170.6925337085001</v>
       </c>
       <c r="I2" t="n">
         <v>170.2422455708761</v>
@@ -1385,58 +1385,58 @@
         <v>170.6228512447256</v>
       </c>
       <c r="K2" t="n">
-        <v>170.8750477161196</v>
+        <v>170.8750477161197</v>
       </c>
       <c r="L2" t="n">
-        <v>170.5037427297643</v>
+        <v>170.5037427297642</v>
       </c>
       <c r="M2" t="n">
-        <v>170.5291685719018</v>
+        <v>170.529168571902</v>
       </c>
       <c r="N2" t="n">
         <v>170.9121855925808</v>
       </c>
       <c r="O2" t="n">
-        <v>170.9767854546196</v>
+        <v>170.9767854546198</v>
       </c>
       <c r="P2" t="n">
         <v>171.5217797582277</v>
       </c>
       <c r="Q2" t="n">
-        <v>170.2341751976006</v>
+        <v>170.2341751976008</v>
       </c>
       <c r="R2" t="n">
-        <v>170.1857462447813</v>
+        <v>170.1857462447811</v>
       </c>
       <c r="S2" t="n">
-        <v>170.767195018202</v>
+        <v>170.7671950182021</v>
       </c>
       <c r="T2" t="n">
-        <v>170.7536351550308</v>
+        <v>170.7536351550309</v>
       </c>
       <c r="U2" t="n">
         <v>170.8483352405522</v>
       </c>
       <c r="V2" t="n">
-        <v>175.122485408619</v>
+        <v>175.1224854086191</v>
       </c>
       <c r="W2" t="n">
-        <v>171.5232032115394</v>
+        <v>171.5232032115395</v>
       </c>
       <c r="X2" t="n">
-        <v>171.5232426581169</v>
+        <v>171.523242658117</v>
       </c>
       <c r="Y2" t="n">
         <v>171.3277132222039</v>
       </c>
       <c r="Z2" t="n">
-        <v>170.2814199899798</v>
+        <v>170.28141998998</v>
       </c>
       <c r="AA2" t="n">
-        <v>171.1895950305103</v>
+        <v>171.1895950305104</v>
       </c>
       <c r="AB2" t="n">
-        <v>170.5549546249252</v>
+        <v>170.5549546249253</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="C3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="D3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="E3" t="n">
         <v>159.7585175817831</v>
       </c>
       <c r="F3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="G3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="H3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="I3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="J3" t="n">
-        <v>172.5379980721032</v>
+        <v>172.5379980721034</v>
       </c>
       <c r="K3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="L3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="M3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="N3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="O3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="P3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="Q3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="R3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="S3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="T3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="U3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="V3" t="n">
-        <v>177.3570437876159</v>
+        <v>177.357043787616</v>
       </c>
       <c r="W3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="X3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="Y3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="Z3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="AA3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
       <c r="AB3" t="n">
-        <v>172.5485007813302</v>
+        <v>172.5485007813303</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.4075572140034</v>
+        <v>18.40755721400335</v>
       </c>
       <c r="C4" t="n">
-        <v>61.58407852807839</v>
+        <v>61.58407852807834</v>
       </c>
       <c r="D4" t="n">
-        <v>97.7023188063566</v>
+        <v>97.70231880635676</v>
       </c>
       <c r="E4" t="n">
-        <v>46.24809042161971</v>
+        <v>46.24809042161961</v>
       </c>
       <c r="F4" t="n">
         <v>174.5930145827681</v>
       </c>
       <c r="G4" t="n">
-        <v>192.8955688657702</v>
+        <v>192.8955688657697</v>
       </c>
       <c r="H4" t="n">
-        <v>223.9865577297691</v>
+        <v>223.9865577297692</v>
       </c>
       <c r="I4" t="n">
-        <v>99.48345789420108</v>
+        <v>99.48345789420146</v>
       </c>
       <c r="J4" t="n">
-        <v>184.0310132102603</v>
+        <v>184.0310132102602</v>
       </c>
       <c r="K4" t="n">
         <v>232.8245575783912</v>
       </c>
       <c r="L4" t="n">
-        <v>148.0908550176233</v>
+        <v>148.0908550176234</v>
       </c>
       <c r="M4" t="n">
-        <v>169.1667529130712</v>
+        <v>169.166752913071</v>
       </c>
       <c r="N4" t="n">
-        <v>272.485265450497</v>
+        <v>272.4852654504971</v>
       </c>
       <c r="O4" t="n">
         <v>249.9310241323684</v>
       </c>
       <c r="P4" t="n">
-        <v>375.4293450603952</v>
+        <v>375.4293450603953</v>
       </c>
       <c r="Q4" t="n">
-        <v>90.88633491712739</v>
+        <v>90.88633491712733</v>
       </c>
       <c r="R4" t="n">
-        <v>87.16117793269613</v>
+        <v>87.16117793269603</v>
       </c>
       <c r="S4" t="n">
-        <v>205.7065842606161</v>
+        <v>205.7065842606162</v>
       </c>
       <c r="T4" t="n">
-        <v>234.4845742555568</v>
+        <v>234.484574255557</v>
       </c>
       <c r="U4" t="n">
-        <v>221.8534803108624</v>
+        <v>221.8534803108619</v>
       </c>
       <c r="V4" t="n">
         <v>120.5587104354032</v>
       </c>
       <c r="W4" t="n">
-        <v>418.6826809870629</v>
+        <v>418.6826809870627</v>
       </c>
       <c r="X4" t="n">
-        <v>406.6379555945519</v>
+        <v>406.6379555945526</v>
       </c>
       <c r="Y4" t="n">
-        <v>376.4466613828509</v>
+        <v>376.4466613828507</v>
       </c>
       <c r="Z4" t="n">
-        <v>92.51302787270961</v>
+        <v>92.51302787270983</v>
       </c>
       <c r="AA4" t="n">
-        <v>339.5406548246001</v>
+        <v>339.5406548246003</v>
       </c>
       <c r="AB4" t="n">
-        <v>188.2081087398592</v>
+        <v>188.2081087398591</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.2959207071441</v>
+        <v>10.29592070714406</v>
       </c>
       <c r="C5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="D5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4153081866734</v>
+        <v>12.41530818667339</v>
       </c>
       <c r="F5" t="n">
-        <v>11.00213454018572</v>
+        <v>11.00213454018568</v>
       </c>
       <c r="G5" t="n">
-        <v>15.76906472954689</v>
+        <v>15.76906472954681</v>
       </c>
       <c r="H5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="I5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="J5" t="n">
-        <v>14.83224806444523</v>
+        <v>14.83224806444518</v>
       </c>
       <c r="K5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="L5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="M5" t="n">
-        <v>14.8290838264531</v>
+        <v>14.829083826453</v>
       </c>
       <c r="N5" t="n">
-        <v>272.485265450497</v>
+        <v>11.31512402564989</v>
       </c>
       <c r="O5" t="n">
-        <v>12.28079068675189</v>
+        <v>12.28079068675183</v>
       </c>
       <c r="P5" t="n">
-        <v>12.04408245468829</v>
+        <v>12.04408245468823</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.405050691558239</v>
+        <v>9.405050691558202</v>
       </c>
       <c r="R5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="S5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="T5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="U5" t="n">
-        <v>12.5863036397345</v>
+        <v>12.58630363973442</v>
       </c>
       <c r="V5" t="n">
-        <v>13.57690306608901</v>
+        <v>13.57690306608897</v>
       </c>
       <c r="W5" t="n">
-        <v>14.82997471640305</v>
+        <v>14.82997471640295</v>
       </c>
       <c r="X5" t="n">
-        <v>9.820524094986411</v>
+        <v>9.820524094986377</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.28463487375303</v>
+        <v>19.28463487375294</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.21171487543769</v>
+        <v>10.21171487543765</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.82908382644329</v>
+        <v>14.82908382644319</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.56435175545547</v>
+        <v>19.56435175545536</v>
       </c>
     </row>
     <row r="6">
@@ -1713,82 +1713,82 @@
         <v>18.26418435754218</v>
       </c>
       <c r="C6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="D6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="E6" t="n">
-        <v>21.47694913903422</v>
+        <v>21.4769491390342</v>
       </c>
       <c r="F6" t="n">
         <v>12.81239984230144</v>
       </c>
       <c r="G6" t="n">
-        <v>22.44092349545605</v>
+        <v>22.440923495456</v>
       </c>
       <c r="H6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="I6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="J6" t="n">
-        <v>22.4440855116404</v>
+        <v>22.44408551164036</v>
       </c>
       <c r="K6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="L6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="M6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="N6" t="n">
-        <v>272.485265450497</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="O6" t="n">
-        <v>23.82508937678734</v>
+        <v>23.8250893767873</v>
       </c>
       <c r="P6" t="n">
         <v>24.12612170768998</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.44092349545605</v>
+        <v>22.440923495456</v>
       </c>
       <c r="R6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="S6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="T6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="U6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="V6" t="n">
         <v>27.28090155305149</v>
       </c>
       <c r="W6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="X6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.9227212054295</v>
+        <v>19.92272120542949</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
       <c r="AB6" t="n">
-        <v>22.44092127363838</v>
+        <v>22.44092127363836</v>
       </c>
     </row>
     <row r="7">
@@ -1801,43 +1801,43 @@
         <v>172.1947832825733</v>
       </c>
       <c r="C7" t="n">
-        <v>171.1916965940129</v>
+        <v>171.1916965940131</v>
       </c>
       <c r="D7" t="n">
-        <v>170.3586261905516</v>
+        <v>170.3586261905517</v>
       </c>
       <c r="E7" t="n">
-        <v>158.7152418080911</v>
+        <v>158.715241808091</v>
       </c>
       <c r="F7" t="n">
-        <v>168.6572044434161</v>
+        <v>168.6572044434163</v>
       </c>
       <c r="G7" t="n">
-        <v>167.5126828298716</v>
+        <v>167.5126828298717</v>
       </c>
       <c r="H7" t="n">
-        <v>167.7964430711489</v>
+        <v>167.796443071149</v>
       </c>
       <c r="I7" t="n">
-        <v>170.4057647872004</v>
+        <v>170.4057647872005</v>
       </c>
       <c r="J7" t="n">
         <v>168.0627457670131</v>
       </c>
       <c r="K7" t="n">
-        <v>166.6867826328128</v>
+        <v>166.6867826328131</v>
       </c>
       <c r="L7" t="n">
         <v>168.8358914456028</v>
       </c>
       <c r="M7" t="n">
-        <v>168.7356143229408</v>
+        <v>168.7356143229409</v>
       </c>
       <c r="N7" t="n">
-        <v>166.45185511794</v>
+        <v>166.4518551179402</v>
       </c>
       <c r="O7" t="n">
-        <v>165.9910850907428</v>
+        <v>165.9910850907429</v>
       </c>
       <c r="P7" t="n">
         <v>162.736578473453</v>
@@ -1852,22 +1852,22 @@
         <v>167.2614898641506</v>
       </c>
       <c r="T7" t="n">
-        <v>167.4095281222071</v>
+        <v>167.4095281222073</v>
       </c>
       <c r="U7" t="n">
-        <v>166.7929738284562</v>
+        <v>166.7929738284564</v>
       </c>
       <c r="V7" t="n">
         <v>174.3043212190804</v>
       </c>
       <c r="W7" t="n">
-        <v>162.8252587975566</v>
+        <v>162.8252587975567</v>
       </c>
       <c r="X7" t="n">
-        <v>162.8889747897271</v>
+        <v>162.8889747897274</v>
       </c>
       <c r="Y7" t="n">
-        <v>163.992877324076</v>
+        <v>163.9928773240761</v>
       </c>
       <c r="Z7" t="n">
         <v>170.1377454137857</v>
@@ -1876,7 +1876,7 @@
         <v>164.8005097937927</v>
       </c>
       <c r="AB7" t="n">
-        <v>168.5709481280789</v>
+        <v>168.570948128079</v>
       </c>
     </row>
     <row r="8">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.774258939981</v>
+        <v>169.7742589399811</v>
       </c>
       <c r="C8" t="n">
         <v>169.4897653964183</v>
@@ -1901,58 +1901,58 @@
         <v>168.7727808484543</v>
       </c>
       <c r="G8" t="n">
-        <v>168.4313763191125</v>
+        <v>168.4313763191127</v>
       </c>
       <c r="H8" t="n">
         <v>168.5303323064581</v>
       </c>
       <c r="I8" t="n">
-        <v>169.2672938650527</v>
+        <v>169.2672938650529</v>
       </c>
       <c r="J8" t="n">
-        <v>168.5865971841268</v>
+        <v>168.586597184127</v>
       </c>
       <c r="K8" t="n">
-        <v>168.2079472783569</v>
+        <v>168.2079472783568</v>
       </c>
       <c r="L8" t="n">
         <v>168.8144936506244</v>
       </c>
       <c r="M8" t="n">
-        <v>168.7942930823865</v>
+        <v>168.7942930823866</v>
       </c>
       <c r="N8" t="n">
-        <v>168.1381923868813</v>
+        <v>168.1381923868815</v>
       </c>
       <c r="O8" t="n">
-        <v>167.9931404181584</v>
+        <v>167.9931404181586</v>
       </c>
       <c r="P8" t="n">
-        <v>167.0573238394024</v>
+        <v>167.0573238394028</v>
       </c>
       <c r="Q8" t="n">
-        <v>169.2764574850233</v>
+        <v>169.2764574850236</v>
       </c>
       <c r="R8" t="n">
-        <v>169.3628051945693</v>
+        <v>169.3628051945692</v>
       </c>
       <c r="S8" t="n">
-        <v>168.3615882021811</v>
+        <v>168.3615882021812</v>
       </c>
       <c r="T8" t="n">
-        <v>168.4153862181958</v>
+        <v>168.4153862181959</v>
       </c>
       <c r="U8" t="n">
-        <v>168.2295521352183</v>
+        <v>168.2295521352185</v>
       </c>
       <c r="V8" t="n">
-        <v>173.7334869114857</v>
+        <v>173.7334869114858</v>
       </c>
       <c r="W8" t="n">
-        <v>167.0990971227887</v>
+        <v>167.0990971227888</v>
       </c>
       <c r="X8" t="n">
-        <v>167.1281275488547</v>
+        <v>167.1281275488548</v>
       </c>
       <c r="Y8" t="n">
         <v>167.4348772839991</v>
@@ -1964,7 +1964,7 @@
         <v>167.6642344397985</v>
       </c>
       <c r="AB8" t="n">
-        <v>168.7451554919877</v>
+        <v>168.7451554919879</v>
       </c>
     </row>
   </sheetData>
@@ -2139,13 +2139,13 @@
         <v>173.0882924877085</v>
       </c>
       <c r="E2" t="n">
-        <v>159.5000164666416</v>
+        <v>159.5000164666419</v>
       </c>
       <c r="F2" t="n">
-        <v>172.8243779009266</v>
+        <v>172.8243779009267</v>
       </c>
       <c r="G2" t="n">
-        <v>173.6213931276135</v>
+        <v>173.6213931276134</v>
       </c>
       <c r="H2" t="n">
         <v>173.4911489448452</v>
@@ -2154,13 +2154,13 @@
         <v>172.7785606296549</v>
       </c>
       <c r="J2" t="n">
-        <v>173.6744644561283</v>
+        <v>173.6744644561284</v>
       </c>
       <c r="K2" t="n">
         <v>173.3217104531139</v>
       </c>
       <c r="L2" t="n">
-        <v>173.8505322129966</v>
+        <v>173.8505322129967</v>
       </c>
       <c r="M2" t="n">
         <v>174.6925651625411</v>
@@ -2172,34 +2172,34 @@
         <v>173.6787661656469</v>
       </c>
       <c r="P2" t="n">
-        <v>174.2093505554909</v>
+        <v>174.2093505554908</v>
       </c>
       <c r="Q2" t="n">
-        <v>173.2713248942166</v>
+        <v>173.2713248942167</v>
       </c>
       <c r="R2" t="n">
         <v>173.17993357942</v>
       </c>
       <c r="S2" t="n">
-        <v>173.5175225564769</v>
+        <v>173.517522556477</v>
       </c>
       <c r="T2" t="n">
-        <v>173.2966676981922</v>
+        <v>173.2966676981921</v>
       </c>
       <c r="U2" t="n">
-        <v>174.1839178596024</v>
+        <v>174.1839178596023</v>
       </c>
       <c r="V2" t="n">
-        <v>178.2885343995059</v>
+        <v>178.2885343995058</v>
       </c>
       <c r="W2" t="n">
-        <v>174.6007348225918</v>
+        <v>174.6007348225919</v>
       </c>
       <c r="X2" t="n">
-        <v>173.4160214270266</v>
+        <v>173.4160214270267</v>
       </c>
       <c r="Y2" t="n">
-        <v>174.6832098484814</v>
+        <v>174.6832098484813</v>
       </c>
       <c r="Z2" t="n">
         <v>173.5623317227046</v>
@@ -2227,7 +2227,7 @@
         <v>174.60442659009</v>
       </c>
       <c r="E3" t="n">
-        <v>160.9945294730511</v>
+        <v>160.9945294730513</v>
       </c>
       <c r="F3" t="n">
         <v>174.60442659009</v>
@@ -2278,7 +2278,7 @@
         <v>174.60442659009</v>
       </c>
       <c r="V3" t="n">
-        <v>179.5891213065387</v>
+        <v>179.5891213065386</v>
       </c>
       <c r="W3" t="n">
         <v>174.60442659009</v>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>317.4917309889053</v>
+        <v>317.4917309889096</v>
       </c>
       <c r="C4" t="n">
         <v>126.3595836331666</v>
       </c>
       <c r="D4" t="n">
-        <v>340.7402869050067</v>
+        <v>340.740286905007</v>
       </c>
       <c r="E4" t="n">
-        <v>271.4555563909357</v>
+        <v>271.4555563909365</v>
       </c>
       <c r="F4" t="n">
-        <v>265.1723387202996</v>
+        <v>265.1723387203008</v>
       </c>
       <c r="G4" t="n">
-        <v>445.0684405326475</v>
+        <v>445.0684405326482</v>
       </c>
       <c r="H4" t="n">
-        <v>470.9136468375427</v>
+        <v>470.9136468375428</v>
       </c>
       <c r="I4" t="n">
-        <v>255.2373991963794</v>
+        <v>255.2373991963796</v>
       </c>
       <c r="J4" t="n">
-        <v>475.1689679524052</v>
+        <v>475.1689679524045</v>
       </c>
       <c r="K4" t="n">
-        <v>377.1652903054509</v>
+        <v>377.1652903054514</v>
       </c>
       <c r="L4" t="n">
-        <v>529.5830532380928</v>
+        <v>529.5830532380911</v>
       </c>
       <c r="M4" t="n">
-        <v>800.4747198625057</v>
+        <v>800.4747198625016</v>
       </c>
       <c r="N4" t="n">
-        <v>520.4558486234428</v>
+        <v>520.455848623443</v>
       </c>
       <c r="O4" t="n">
-        <v>435.9724407765632</v>
+        <v>435.9724407765634</v>
       </c>
       <c r="P4" t="n">
-        <v>594.4740540747395</v>
+        <v>594.4740540747437</v>
       </c>
       <c r="Q4" t="n">
-        <v>382.6807188397792</v>
+        <v>382.6807188397799</v>
       </c>
       <c r="R4" t="n">
-        <v>375.2213538678799</v>
+        <v>375.2213538678801</v>
       </c>
       <c r="S4" t="n">
-        <v>418.6758814161692</v>
+        <v>418.6758814161687</v>
       </c>
       <c r="T4" t="n">
-        <v>399.2746777177337</v>
+        <v>399.2746777177347</v>
       </c>
       <c r="U4" t="n">
-        <v>606.0617797659553</v>
+        <v>606.0617797659551</v>
       </c>
       <c r="V4" t="n">
-        <v>365.1487297672757</v>
+        <v>365.1487297672755</v>
       </c>
       <c r="W4" t="n">
-        <v>737.6669207442401</v>
+        <v>737.6669207442409</v>
       </c>
       <c r="X4" t="n">
-        <v>426.0710819977585</v>
+        <v>426.0710819977597</v>
       </c>
       <c r="Y4" t="n">
-        <v>750.4283784087004</v>
+        <v>750.4283784086997</v>
       </c>
       <c r="Z4" t="n">
-        <v>430.4154673374558</v>
+        <v>430.4154673374551</v>
       </c>
       <c r="AA4" t="n">
-        <v>374.6084292295008</v>
+        <v>374.6084292295025</v>
       </c>
       <c r="AB4" t="n">
-        <v>887.3943034159204</v>
+        <v>887.3943034159283</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.97552498520209</v>
+        <v>15.9755249852021</v>
       </c>
       <c r="C5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="D5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="E5" t="n">
-        <v>19.37700088930159</v>
+        <v>19.37700088930167</v>
       </c>
       <c r="F5" t="n">
-        <v>17.10895120359338</v>
+        <v>17.10895120359339</v>
       </c>
       <c r="G5" t="n">
-        <v>24.75955701884504</v>
+        <v>24.75955701884506</v>
       </c>
       <c r="H5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="I5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="J5" t="n">
-        <v>23.25432146358512</v>
+        <v>23.25432146358514</v>
       </c>
       <c r="K5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="L5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="M5" t="n">
-        <v>23.25095020527774</v>
+        <v>23.25095020527779</v>
       </c>
       <c r="N5" t="n">
-        <v>520.4558486234428</v>
+        <v>17.61127850491958</v>
       </c>
       <c r="O5" t="n">
-        <v>19.16110925124381</v>
+        <v>19.16110925124384</v>
       </c>
       <c r="P5" t="n">
-        <v>18.78120828673037</v>
+        <v>18.78120828673045</v>
       </c>
       <c r="Q5" t="n">
         <v>14.54573787880134</v>
       </c>
       <c r="R5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="S5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="T5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527118</v>
       </c>
       <c r="U5" t="n">
-        <v>19.70619656222446</v>
+        <v>19.70619656222452</v>
       </c>
       <c r="V5" t="n">
-        <v>21.29105452728725</v>
+        <v>21.29105452728724</v>
       </c>
       <c r="W5" t="n">
-        <v>23.25238002439242</v>
+        <v>23.25238002439246</v>
       </c>
       <c r="X5" t="n">
-        <v>15.21254505031443</v>
+        <v>15.21254505031438</v>
       </c>
       <c r="Y5" t="n">
-        <v>30.49549052374206</v>
+        <v>30.49549052374214</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.84038022743768</v>
+        <v>15.84038022743775</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.25095020527111</v>
+        <v>23.25095020527117</v>
       </c>
       <c r="AB5" t="n">
-        <v>30.85074019909538</v>
+        <v>30.85074019909553</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.44884456538934</v>
+        <v>31.44884456538925</v>
       </c>
       <c r="C6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="D6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="E6" t="n">
         <v>37.17624567130078</v>
       </c>
       <c r="F6" t="n">
-        <v>21.72993926561183</v>
+        <v>21.7299392656118</v>
       </c>
       <c r="G6" t="n">
-        <v>38.89472435571772</v>
+        <v>38.89472435571774</v>
       </c>
       <c r="H6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="I6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="J6" t="n">
-        <v>38.89809424600567</v>
+        <v>38.89809424600565</v>
       </c>
       <c r="K6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="L6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="M6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="N6" t="n">
-        <v>520.4558486234428</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="O6" t="n">
-        <v>41.36227916868524</v>
+        <v>41.36227916868529</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89893000439512</v>
+        <v>41.8989300043951</v>
       </c>
       <c r="Q6" t="n">
-        <v>38.89472435571772</v>
+        <v>38.89472435571774</v>
       </c>
       <c r="R6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="S6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="T6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="U6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="V6" t="n">
         <v>47.50875502322853</v>
       </c>
       <c r="W6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="X6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="Z6" t="n">
-        <v>34.40552095561473</v>
+        <v>34.40552095561475</v>
       </c>
       <c r="AA6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
       <c r="AB6" t="n">
-        <v>38.8947229876917</v>
+        <v>38.89472298769171</v>
       </c>
     </row>
     <row r="7">
@@ -2570,79 +2570,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>167.2045370410842</v>
+        <v>167.2045370410844</v>
       </c>
       <c r="C7" t="n">
-        <v>172.0373057513226</v>
+        <v>172.0373057513225</v>
       </c>
       <c r="D7" t="n">
         <v>167.718090261327</v>
       </c>
       <c r="E7" t="n">
-        <v>155.1716495788937</v>
+        <v>155.1716495788938</v>
       </c>
       <c r="F7" t="n">
         <v>169.2900518540627</v>
       </c>
       <c r="G7" t="n">
-        <v>164.4444542762327</v>
+        <v>164.4444542762328</v>
       </c>
       <c r="H7" t="n">
-        <v>165.4207167207364</v>
+        <v>165.4207167207365</v>
       </c>
       <c r="I7" t="n">
-        <v>169.5418540091574</v>
+        <v>169.5418540091576</v>
       </c>
       <c r="J7" t="n">
         <v>164.1272787705059</v>
       </c>
       <c r="K7" t="n">
-        <v>166.3391319219752</v>
+        <v>166.3391319219753</v>
       </c>
       <c r="L7" t="n">
-        <v>163.1479801560286</v>
+        <v>163.1479801560293</v>
       </c>
       <c r="M7" t="n">
-        <v>158.382817375426</v>
+        <v>158.3828173754262</v>
       </c>
       <c r="N7" t="n">
-        <v>163.6689234508434</v>
+        <v>163.6689234508435</v>
       </c>
       <c r="O7" t="n">
         <v>164.0860352235505</v>
       </c>
       <c r="P7" t="n">
-        <v>160.9139058268202</v>
+        <v>160.9139058268204</v>
       </c>
       <c r="Q7" t="n">
-        <v>166.6256153284915</v>
+        <v>166.6256153284916</v>
       </c>
       <c r="R7" t="n">
-        <v>167.2105597413857</v>
+        <v>167.2105597413858</v>
       </c>
       <c r="S7" t="n">
-        <v>165.0862319646427</v>
+        <v>165.0862319646428</v>
       </c>
       <c r="T7" t="n">
-        <v>166.502674920829</v>
+        <v>166.5026749208291</v>
       </c>
       <c r="U7" t="n">
-        <v>161.1636501677088</v>
+        <v>161.1636501677089</v>
       </c>
       <c r="V7" t="n">
-        <v>170.8602532285416</v>
+        <v>170.8602532285414</v>
       </c>
       <c r="W7" t="n">
         <v>158.7394226357652</v>
       </c>
       <c r="X7" t="n">
-        <v>165.789932182638</v>
+        <v>165.7899321826383</v>
       </c>
       <c r="Y7" t="n">
-        <v>158.2790669173993</v>
+        <v>158.2790669173994</v>
       </c>
       <c r="Z7" t="n">
-        <v>164.8010429025797</v>
+        <v>164.8010429025799</v>
       </c>
       <c r="AA7" t="n">
         <v>166.6022944046354</v>
@@ -2664,13 +2664,13 @@
         <v>171.1823580423461</v>
       </c>
       <c r="D8" t="n">
-        <v>169.9549875126695</v>
+        <v>169.9549875126694</v>
       </c>
       <c r="E8" t="n">
         <v>156.8505875583828</v>
       </c>
       <c r="F8" t="n">
-        <v>170.4063204601268</v>
+        <v>170.4063204601269</v>
       </c>
       <c r="G8" t="n">
         <v>168.9985733468978</v>
@@ -2679,22 +2679,22 @@
         <v>169.3125316875424</v>
       </c>
       <c r="I8" t="n">
-        <v>170.475073971869</v>
+        <v>170.4750739718691</v>
       </c>
       <c r="J8" t="n">
-        <v>168.9113007963191</v>
+        <v>168.9113007963193</v>
       </c>
       <c r="K8" t="n">
-        <v>169.5609750391904</v>
+        <v>169.5609750391905</v>
       </c>
       <c r="L8" t="n">
         <v>168.6378125759701</v>
       </c>
       <c r="M8" t="n">
-        <v>167.3116812746679</v>
+        <v>167.3116812746678</v>
       </c>
       <c r="N8" t="n">
-        <v>168.7960120022821</v>
+        <v>168.7960120022822</v>
       </c>
       <c r="O8" t="n">
         <v>168.8928645737471</v>
@@ -2706,19 +2706,19 @@
         <v>169.6409403432267</v>
       </c>
       <c r="R8" t="n">
-        <v>169.8157006004041</v>
+        <v>169.8157006004042</v>
       </c>
       <c r="S8" t="n">
         <v>169.1867136692121</v>
       </c>
       <c r="T8" t="n">
-        <v>169.6103448699278</v>
+        <v>169.6103448699279</v>
       </c>
       <c r="U8" t="n">
         <v>168.068321754206</v>
       </c>
       <c r="V8" t="n">
-        <v>174.3168716067651</v>
+        <v>174.316871606765</v>
       </c>
       <c r="W8" t="n">
         <v>167.3821074646062</v>
@@ -2730,7 +2730,7 @@
         <v>167.2551191715727</v>
       </c>
       <c r="Z8" t="n">
-        <v>169.1017609033572</v>
+        <v>169.1017609033574</v>
       </c>
       <c r="AA8" t="n">
         <v>169.628598265349</v>
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172.465105722525</v>
+        <v>172.4651057225251</v>
       </c>
       <c r="C2" t="n">
-        <v>172.094945387378</v>
+        <v>172.0949453873781</v>
       </c>
       <c r="D2" t="n">
-        <v>172.8187854264849</v>
+        <v>172.818785426485</v>
       </c>
       <c r="E2" t="n">
-        <v>159.0940065871</v>
+        <v>159.0940065871001</v>
       </c>
       <c r="F2" t="n">
-        <v>172.4055022203879</v>
+        <v>172.405502220388</v>
       </c>
       <c r="G2" t="n">
-        <v>173.0743746884391</v>
+        <v>173.0743746884392</v>
       </c>
       <c r="H2" t="n">
         <v>172.898175366471</v>
       </c>
       <c r="I2" t="n">
-        <v>172.4574786662371</v>
+        <v>172.4574786662372</v>
       </c>
       <c r="J2" t="n">
-        <v>173.0903890701647</v>
+        <v>173.090389070165</v>
       </c>
       <c r="K2" t="n">
         <v>172.5065236542096</v>
       </c>
       <c r="L2" t="n">
-        <v>173.1434741807572</v>
+        <v>173.1434741807573</v>
       </c>
       <c r="M2" t="n">
         <v>173.9521342361808</v>
@@ -2941,28 +2941,28 @@
         <v>172.9352460255228</v>
       </c>
       <c r="O2" t="n">
-        <v>173.1549108902275</v>
+        <v>173.1549108902274</v>
       </c>
       <c r="P2" t="n">
         <v>173.6665677070455</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.6245769340386</v>
+        <v>172.6245769340387</v>
       </c>
       <c r="R2" t="n">
-        <v>172.5703118626021</v>
+        <v>172.5703118626022</v>
       </c>
       <c r="S2" t="n">
         <v>172.9493650691848</v>
       </c>
       <c r="T2" t="n">
-        <v>172.8347020900326</v>
+        <v>172.8347020900327</v>
       </c>
       <c r="U2" t="n">
-        <v>173.3152448060345</v>
+        <v>173.3152448060346</v>
       </c>
       <c r="V2" t="n">
-        <v>177.7731881524465</v>
+        <v>177.7731881524466</v>
       </c>
       <c r="W2" t="n">
         <v>173.927060751296</v>
@@ -2974,10 +2974,10 @@
         <v>174.1667867649372</v>
       </c>
       <c r="Z2" t="n">
-        <v>172.883462787896</v>
+        <v>172.8834627878959</v>
       </c>
       <c r="AA2" t="n">
-        <v>172.7856200079182</v>
+        <v>172.7856200079183</v>
       </c>
       <c r="AB2" t="n">
         <v>174.2143344853467</v>
@@ -2999,7 +2999,7 @@
         <v>174.1476607935166</v>
       </c>
       <c r="E3" t="n">
-        <v>160.7310709430199</v>
+        <v>160.7310709430198</v>
       </c>
       <c r="F3" t="n">
         <v>174.1476607935166</v>
@@ -3014,7 +3014,7 @@
         <v>174.1476607935166</v>
       </c>
       <c r="J3" t="n">
-        <v>174.1412328646675</v>
+        <v>174.1412328646676</v>
       </c>
       <c r="K3" t="n">
         <v>174.1476607935166</v>
@@ -3050,7 +3050,7 @@
         <v>174.1476607935166</v>
       </c>
       <c r="V3" t="n">
-        <v>179.1241978528532</v>
+        <v>179.1241978528531</v>
       </c>
       <c r="W3" t="n">
         <v>174.1476607935166</v>
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>244.2074018352822</v>
+        <v>244.2074018352833</v>
       </c>
       <c r="C4" t="n">
-        <v>162.8652456331733</v>
+        <v>162.8652456331735</v>
       </c>
       <c r="D4" t="n">
-        <v>362.4114622176994</v>
+        <v>362.4114622177005</v>
       </c>
       <c r="E4" t="n">
-        <v>217.4911826478095</v>
+        <v>217.4911826478091</v>
       </c>
       <c r="F4" t="n">
-        <v>252.0662158477786</v>
+        <v>252.066215847779</v>
       </c>
       <c r="G4" t="n">
-        <v>385.5881116566435</v>
+        <v>385.5881116566445</v>
       </c>
       <c r="H4" t="n">
-        <v>402.9427065371376</v>
+        <v>402.9427065371382</v>
       </c>
       <c r="I4" t="n">
-        <v>271.886773388537</v>
+        <v>271.8867733885367</v>
       </c>
       <c r="J4" t="n">
-        <v>406.960645638435</v>
+        <v>406.9606456384356</v>
       </c>
       <c r="K4" t="n">
-        <v>251.0502039016467</v>
+        <v>251.0502039016466</v>
       </c>
       <c r="L4" t="n">
-        <v>427.0689523679242</v>
+        <v>427.0689523679239</v>
       </c>
       <c r="M4" t="n">
-        <v>670.3620754968287</v>
+        <v>670.362075496829</v>
       </c>
       <c r="N4" t="n">
-        <v>386.6570478049056</v>
+        <v>386.6570478049063</v>
       </c>
       <c r="O4" t="n">
-        <v>385.9766245294457</v>
+        <v>385.976624529446</v>
       </c>
       <c r="P4" t="n">
-        <v>525.4568763176881</v>
+        <v>525.4568763176892</v>
       </c>
       <c r="Q4" t="n">
-        <v>299.7935559262646</v>
+        <v>299.7935559262649</v>
       </c>
       <c r="R4" t="n">
-        <v>306.9021845139008</v>
+        <v>306.9021845139005</v>
       </c>
       <c r="S4" t="n">
-        <v>359.0774448842635</v>
+        <v>359.0774448842639</v>
       </c>
       <c r="T4" t="n">
-        <v>370.3203814387247</v>
+        <v>370.3203814387259</v>
       </c>
       <c r="U4" t="n">
-        <v>456.5559196911683</v>
+        <v>456.5559196911684</v>
       </c>
       <c r="V4" t="n">
-        <v>323.0055529789329</v>
+        <v>323.0055529789339</v>
       </c>
       <c r="W4" t="n">
-        <v>631.4372012290496</v>
+        <v>631.4372012290471</v>
       </c>
       <c r="X4" t="n">
-        <v>461.6209483230402</v>
+        <v>461.6209483230406</v>
       </c>
       <c r="Y4" t="n">
-        <v>685.2460624615039</v>
+        <v>685.2460624615069</v>
       </c>
       <c r="Z4" t="n">
-        <v>325.3196430875378</v>
+        <v>325.3196430875379</v>
       </c>
       <c r="AA4" t="n">
-        <v>341.9560359110079</v>
+        <v>341.9560359110084</v>
       </c>
       <c r="AB4" t="n">
-        <v>774.4054522284263</v>
+        <v>774.4054522284267</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.07155949496527</v>
+        <v>14.07155949496537</v>
       </c>
       <c r="C5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="D5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="E5" t="n">
-        <v>16.98502554714453</v>
+        <v>16.98502554714457</v>
       </c>
       <c r="F5" t="n">
-        <v>15.04237301927208</v>
+        <v>15.0423730192721</v>
       </c>
       <c r="G5" t="n">
-        <v>21.5953461845987</v>
+        <v>21.59534618459887</v>
       </c>
       <c r="H5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="I5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="J5" t="n">
-        <v>20.30695523614187</v>
+        <v>20.30695523614188</v>
       </c>
       <c r="K5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="L5" t="n">
-        <v>20.30317923658077</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="M5" t="n">
-        <v>20.30317923659394</v>
+        <v>20.30317923659406</v>
       </c>
       <c r="N5" t="n">
-        <v>386.6570478049056</v>
+        <v>15.47263140741633</v>
       </c>
       <c r="O5" t="n">
-        <v>16.80010788949161</v>
+        <v>16.80010788949174</v>
       </c>
       <c r="P5" t="n">
-        <v>16.47471132785973</v>
+        <v>16.47471132785974</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.84690398822774</v>
+        <v>12.84690398822797</v>
       </c>
       <c r="R5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="S5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="T5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="U5" t="n">
-        <v>17.24989247496298</v>
+        <v>17.24989247496309</v>
       </c>
       <c r="V5" t="n">
-        <v>18.61124258919153</v>
+        <v>18.61124258919158</v>
       </c>
       <c r="W5" t="n">
-        <v>20.30440392007004</v>
+        <v>20.3044039200701</v>
       </c>
       <c r="X5" t="n">
-        <v>13.4180443148309</v>
+        <v>13.41804431483086</v>
       </c>
       <c r="Y5" t="n">
-        <v>26.47909366515242</v>
+        <v>26.47909366515265</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.95580395968648</v>
+        <v>13.95580395968658</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.30317923658076</v>
+        <v>20.3031792365809</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.8126271284751</v>
+        <v>26.81262712847516</v>
       </c>
     </row>
     <row r="6">
@@ -3257,82 +3257,82 @@
         <v>26.35924359963409</v>
       </c>
       <c r="C6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="D6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="E6" t="n">
-        <v>31.0595082605573</v>
+        <v>31.05950826055733</v>
       </c>
       <c r="F6" t="n">
-        <v>18.3833001867911</v>
+        <v>18.38330018679115</v>
       </c>
       <c r="G6" t="n">
-        <v>32.46979967922152</v>
+        <v>32.46979967922149</v>
       </c>
       <c r="H6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="I6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="J6" t="n">
-        <v>32.47357469630106</v>
+        <v>32.47357469630109</v>
       </c>
       <c r="K6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="L6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674013</v>
       </c>
       <c r="M6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="N6" t="n">
-        <v>386.6570478049056</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="O6" t="n">
-        <v>34.49482996290672</v>
+        <v>34.4948299629067</v>
       </c>
       <c r="P6" t="n">
-        <v>34.93523930593973</v>
+        <v>34.93523930593986</v>
       </c>
       <c r="Q6" t="n">
-        <v>32.46979967922152</v>
+        <v>32.46979967922149</v>
       </c>
       <c r="R6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="S6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="T6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="U6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="V6" t="n">
-        <v>39.5454228444363</v>
+        <v>39.54542284443635</v>
       </c>
       <c r="W6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="X6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674013</v>
       </c>
       <c r="Y6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="Z6" t="n">
-        <v>28.78567773507785</v>
+        <v>28.78567773507797</v>
       </c>
       <c r="AA6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
       <c r="AB6" t="n">
-        <v>32.46979869674004</v>
+        <v>32.46979869674011</v>
       </c>
     </row>
     <row r="7">
@@ -3345,13 +3345,13 @@
         <v>168.1697779855662</v>
       </c>
       <c r="C7" t="n">
-        <v>170.4258137347866</v>
+        <v>170.4258137347867</v>
       </c>
       <c r="D7" t="n">
-        <v>166.190212012857</v>
+        <v>166.1902120128571</v>
       </c>
       <c r="E7" t="n">
-        <v>155.759206270792</v>
+        <v>155.7592062707919</v>
       </c>
       <c r="F7" t="n">
         <v>168.6380615280794</v>
@@ -3363,52 +3363,52 @@
         <v>165.7819986832376</v>
       </c>
       <c r="I7" t="n">
-        <v>168.3175166077737</v>
+        <v>168.3175166077735</v>
       </c>
       <c r="J7" t="n">
-        <v>164.4735162506577</v>
+        <v>164.4735162506578</v>
       </c>
       <c r="K7" t="n">
-        <v>168.0106031748397</v>
+        <v>168.0106031748396</v>
       </c>
       <c r="L7" t="n">
         <v>164.1969035474396</v>
       </c>
       <c r="M7" t="n">
-        <v>159.6069865773328</v>
+        <v>159.6069865773329</v>
       </c>
       <c r="N7" t="n">
-        <v>165.4714780274921</v>
+        <v>165.4714780274922</v>
       </c>
       <c r="O7" t="n">
-        <v>164.0550266070536</v>
+        <v>164.0550266070537</v>
       </c>
       <c r="P7" t="n">
         <v>160.9961017381816</v>
       </c>
       <c r="Q7" t="n">
-        <v>167.310349291101</v>
+        <v>167.3103492911011</v>
       </c>
       <c r="R7" t="n">
         <v>167.67128372139</v>
       </c>
       <c r="S7" t="n">
-        <v>165.3161943240864</v>
+        <v>165.3161943240865</v>
       </c>
       <c r="T7" t="n">
-        <v>166.1020928755239</v>
+        <v>166.102092875524</v>
       </c>
       <c r="U7" t="n">
         <v>163.1704727399611</v>
       </c>
       <c r="V7" t="n">
-        <v>170.7223784317925</v>
+        <v>170.7223784317924</v>
       </c>
       <c r="W7" t="n">
         <v>159.5888022169206</v>
       </c>
       <c r="X7" t="n">
-        <v>163.8236187171358</v>
+        <v>163.8236187171356</v>
       </c>
       <c r="Y7" t="n">
         <v>158.1997443397382</v>
@@ -3417,10 +3417,10 @@
         <v>165.6902812781019</v>
       </c>
       <c r="AA7" t="n">
-        <v>166.3319165670777</v>
+        <v>166.3319165670776</v>
       </c>
       <c r="AB7" t="n">
-        <v>158.0194259115066</v>
+        <v>158.0194259115065</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.7451499945254</v>
+        <v>169.7451499945255</v>
       </c>
       <c r="C8" t="n">
-        <v>170.4014931148331</v>
+        <v>170.4014931148332</v>
       </c>
       <c r="D8" t="n">
         <v>169.1981208724001</v>
       </c>
       <c r="E8" t="n">
-        <v>156.8317923168438</v>
+        <v>156.831792316844</v>
       </c>
       <c r="F8" t="n">
-        <v>169.8986169965629</v>
+        <v>169.898616996563</v>
       </c>
       <c r="G8" t="n">
         <v>168.7076227188801</v>
       </c>
       <c r="H8" t="n">
-        <v>169.0917724465107</v>
+        <v>169.0917724465108</v>
       </c>
       <c r="I8" t="n">
-        <v>169.8047444821568</v>
+        <v>169.8047444821569</v>
       </c>
       <c r="J8" t="n">
-        <v>168.6915472016055</v>
+        <v>168.6915472016056</v>
       </c>
       <c r="K8" t="n">
-        <v>169.7141428800693</v>
+        <v>169.7141428800694</v>
       </c>
       <c r="L8" t="n">
-        <v>168.6158479226104</v>
+        <v>168.6158479226105</v>
       </c>
       <c r="M8" t="n">
-        <v>167.3360811294378</v>
+        <v>167.3360811294379</v>
       </c>
       <c r="N8" t="n">
-        <v>168.9875552176277</v>
+        <v>168.9875552176278</v>
       </c>
       <c r="O8" t="n">
         <v>168.56273017207</v>
       </c>
       <c r="P8" t="n">
-        <v>167.6825664253361</v>
+        <v>167.682566425336</v>
       </c>
       <c r="Q8" t="n">
-        <v>169.5135784112207</v>
+        <v>169.5135784112208</v>
       </c>
       <c r="R8" t="n">
-        <v>169.6235396557954</v>
+        <v>169.6235396557956</v>
       </c>
       <c r="S8" t="n">
-        <v>168.9310196813804</v>
+        <v>168.9310196813803</v>
       </c>
       <c r="T8" t="n">
-        <v>169.1739430476421</v>
+        <v>169.1739430476422</v>
       </c>
       <c r="U8" t="n">
-        <v>168.320589259444</v>
+        <v>168.3205892594439</v>
       </c>
       <c r="V8" t="n">
-        <v>173.9503335408542</v>
+        <v>173.9503335408541</v>
       </c>
       <c r="W8" t="n">
-        <v>167.3027337026153</v>
+        <v>167.3027337026154</v>
       </c>
       <c r="X8" t="n">
-        <v>168.5236444619239</v>
+        <v>168.523644461924</v>
       </c>
       <c r="Y8" t="n">
-        <v>166.9104339554737</v>
+        <v>166.9104339554738</v>
       </c>
       <c r="Z8" t="n">
-        <v>169.0353281563128</v>
+        <v>169.0353281563129</v>
       </c>
       <c r="AA8" t="n">
         <v>169.2294314775895</v>
       </c>
       <c r="AB8" t="n">
-        <v>166.8759362163972</v>
+        <v>166.8759362163973</v>
       </c>
     </row>
   </sheetData>
@@ -3680,13 +3680,13 @@
         <v>171.7163770740889</v>
       </c>
       <c r="D2" t="n">
-        <v>172.0942646533536</v>
+        <v>172.0942646533537</v>
       </c>
       <c r="E2" t="n">
-        <v>158.3802240093391</v>
+        <v>158.3802240093392</v>
       </c>
       <c r="F2" t="n">
-        <v>172.2686493829424</v>
+        <v>172.2686493829425</v>
       </c>
       <c r="G2" t="n">
         <v>172.5392774741984</v>
@@ -3695,61 +3695,61 @@
         <v>172.3824859527534</v>
       </c>
       <c r="I2" t="n">
-        <v>172.2539311418146</v>
+        <v>172.2539311418145</v>
       </c>
       <c r="J2" t="n">
-        <v>172.5717551883198</v>
+        <v>172.5717551883197</v>
       </c>
       <c r="K2" t="n">
-        <v>172.495526709555</v>
+        <v>172.4955267095552</v>
       </c>
       <c r="L2" t="n">
         <v>172.7590298237418</v>
       </c>
       <c r="M2" t="n">
-        <v>173.3296070903947</v>
+        <v>173.3296070903945</v>
       </c>
       <c r="N2" t="n">
-        <v>172.3518096668424</v>
+        <v>172.3518096668425</v>
       </c>
       <c r="O2" t="n">
-        <v>172.4283818679337</v>
+        <v>172.428381867934</v>
       </c>
       <c r="P2" t="n">
-        <v>173.0151590768774</v>
+        <v>173.0151590768775</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.3412347502885</v>
+        <v>172.3412347502886</v>
       </c>
       <c r="R2" t="n">
-        <v>172.2326607460867</v>
+        <v>172.2326607460868</v>
       </c>
       <c r="S2" t="n">
-        <v>172.631315113609</v>
+        <v>172.6313151136092</v>
       </c>
       <c r="T2" t="n">
-        <v>172.5020976722987</v>
+        <v>172.5020976722988</v>
       </c>
       <c r="U2" t="n">
         <v>172.8010664797432</v>
       </c>
       <c r="V2" t="n">
-        <v>177.2748906782128</v>
+        <v>177.2748906782129</v>
       </c>
       <c r="W2" t="n">
         <v>173.3757771544427</v>
       </c>
       <c r="X2" t="n">
-        <v>172.9003687853475</v>
+        <v>172.9003687853476</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.5070333257529</v>
+        <v>173.5070333257528</v>
       </c>
       <c r="Z2" t="n">
-        <v>172.1022323613249</v>
+        <v>172.1022323613248</v>
       </c>
       <c r="AA2" t="n">
-        <v>172.4956178669105</v>
+        <v>172.4956178669107</v>
       </c>
       <c r="AB2" t="n">
         <v>173.5547516543367</v>
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="C3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="D3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="E3" t="n">
         <v>160.388280781829</v>
       </c>
       <c r="F3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="G3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="H3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="I3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="J3" t="n">
         <v>173.7252128295004</v>
       </c>
       <c r="K3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="L3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="M3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="N3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="O3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="P3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="R3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="S3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="T3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="U3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="V3" t="n">
-        <v>178.7285996224578</v>
+        <v>178.7285996224579</v>
       </c>
       <c r="W3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="X3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="Y3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="Z3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="AA3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
       <c r="AB3" t="n">
-        <v>173.7296170517014</v>
+        <v>173.7296170517015</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>219.4039977178024</v>
+        <v>219.4039977178021</v>
       </c>
       <c r="C4" t="n">
-        <v>169.9763590282178</v>
+        <v>169.9763590282179</v>
       </c>
       <c r="D4" t="n">
-        <v>269.2813455589124</v>
+        <v>269.2813455589131</v>
       </c>
       <c r="E4" t="n">
         <v>116.5441119451868</v>
       </c>
       <c r="F4" t="n">
-        <v>321.0361598297612</v>
+        <v>321.0361598297615</v>
       </c>
       <c r="G4" t="n">
-        <v>344.707432636074</v>
+        <v>344.7074326360737</v>
       </c>
       <c r="H4" t="n">
-        <v>375.8790869680278</v>
+        <v>375.8790869680282</v>
       </c>
       <c r="I4" t="n">
         <v>321.8861440005463</v>
       </c>
       <c r="J4" t="n">
-        <v>373.8730165629324</v>
+        <v>373.8730165629325</v>
       </c>
       <c r="K4" t="n">
-        <v>344.5225273787116</v>
+        <v>344.5225273787123</v>
       </c>
       <c r="L4" t="n">
-        <v>417.0028050486816</v>
+        <v>417.0028050486824</v>
       </c>
       <c r="M4" t="n">
-        <v>587.973336767721</v>
+        <v>587.9733367677217</v>
       </c>
       <c r="N4" t="n">
-        <v>343.710933756993</v>
+        <v>343.7109337569929</v>
       </c>
       <c r="O4" t="n">
-        <v>316.4581255681866</v>
+        <v>316.4581255681869</v>
       </c>
       <c r="P4" t="n">
-        <v>452.5809687786403</v>
+        <v>452.5809687786398</v>
       </c>
       <c r="Q4" t="n">
-        <v>323.9046889922303</v>
+        <v>323.9046889922304</v>
       </c>
       <c r="R4" t="n">
-        <v>327.4000075328517</v>
+        <v>327.4000075328518</v>
       </c>
       <c r="S4" t="n">
-        <v>376.1890760574997</v>
+        <v>376.1890760575001</v>
       </c>
       <c r="T4" t="n">
         <v>392.1854930090842</v>
       </c>
       <c r="U4" t="n">
-        <v>416.2845087022956</v>
+        <v>416.2845087022955</v>
       </c>
       <c r="V4" t="n">
-        <v>296.033826435512</v>
+        <v>296.0338264355126</v>
       </c>
       <c r="W4" t="n">
-        <v>597.436392714323</v>
+        <v>597.4363927143235</v>
       </c>
       <c r="X4" t="n">
-        <v>470.1207319466225</v>
+        <v>470.1207319466221</v>
       </c>
       <c r="Y4" t="n">
-        <v>636.3781589362243</v>
+        <v>636.3781589362235</v>
       </c>
       <c r="Z4" t="n">
         <v>229.7478315380905</v>
       </c>
       <c r="AA4" t="n">
-        <v>375.3568853311312</v>
+        <v>375.3568853311316</v>
       </c>
       <c r="AB4" t="n">
-        <v>695.1201085975812</v>
+        <v>695.1201085975806</v>
       </c>
     </row>
     <row r="5">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.25219775224646</v>
+        <v>13.2521977522462</v>
       </c>
       <c r="C5" t="n">
         <v>19.12061407062051</v>
@@ -3947,13 +3947,13 @@
         <v>19.12061407062051</v>
       </c>
       <c r="E5" t="n">
-        <v>15.99585549005302</v>
+        <v>15.99585549005316</v>
       </c>
       <c r="F5" t="n">
-        <v>14.16642842815664</v>
+        <v>14.16642842815672</v>
       </c>
       <c r="G5" t="n">
-        <v>20.33746842284437</v>
+        <v>20.33746842284447</v>
       </c>
       <c r="H5" t="n">
         <v>19.12061407062051</v>
@@ -3962,28 +3962,28 @@
         <v>19.12061407062051</v>
       </c>
       <c r="J5" t="n">
-        <v>19.12481144030766</v>
+        <v>19.12481144030793</v>
       </c>
       <c r="K5" t="n">
         <v>19.12061407062051</v>
       </c>
       <c r="L5" t="n">
-        <v>19.12061407062049</v>
+        <v>19.12061407062052</v>
       </c>
       <c r="M5" t="n">
-        <v>19.1206140706364</v>
+        <v>19.12061407063632</v>
       </c>
       <c r="N5" t="n">
-        <v>343.710933756993</v>
+        <v>14.57160965729711</v>
       </c>
       <c r="O5" t="n">
-        <v>15.82171556454276</v>
+        <v>15.82171556454288</v>
       </c>
       <c r="P5" t="n">
-        <v>15.51528440028518</v>
+        <v>15.5152844002852</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.098920007648</v>
+        <v>12.09892000764806</v>
       </c>
       <c r="R5" t="n">
         <v>19.12061407062051</v>
@@ -3995,28 +3995,28 @@
         <v>19.12061407062051</v>
       </c>
       <c r="U5" t="n">
-        <v>16.22105307552033</v>
+        <v>16.22105307552046</v>
       </c>
       <c r="V5" t="n">
-        <v>17.50466452573028</v>
+        <v>17.50466452573029</v>
       </c>
       <c r="W5" t="n">
-        <v>19.12176737508991</v>
+        <v>19.12176737509011</v>
       </c>
       <c r="X5" t="n">
-        <v>12.63677201934386</v>
+        <v>12.63677201934398</v>
       </c>
       <c r="Y5" t="n">
-        <v>24.89511815416404</v>
+        <v>24.89511815416402</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.14318890694128</v>
+        <v>13.14318890694121</v>
       </c>
       <c r="AA5" t="n">
         <v>19.12061407062051</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.25066561718376</v>
+        <v>25.25066561718353</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.59272016264925</v>
+        <v>23.5927201626493</v>
       </c>
       <c r="C6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="D6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="E6" t="n">
-        <v>27.75717031278856</v>
+        <v>27.75717031278859</v>
       </c>
       <c r="F6" t="n">
-        <v>16.52600772424956</v>
+        <v>16.52600772424962</v>
       </c>
       <c r="G6" t="n">
-        <v>29.00669320859992</v>
+        <v>29.00669320859983</v>
       </c>
       <c r="H6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="I6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="J6" t="n">
-        <v>29.01089057505226</v>
+        <v>29.01089057505233</v>
       </c>
       <c r="K6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="L6" t="n">
-        <v>29.00669320536484</v>
+        <v>29.00669320536487</v>
       </c>
       <c r="M6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="N6" t="n">
-        <v>343.710933756993</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="O6" t="n">
-        <v>30.80087678703537</v>
+        <v>30.80087678703538</v>
       </c>
       <c r="P6" t="n">
-        <v>31.19108093233922</v>
+        <v>31.19108093233917</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.00669320859992</v>
+        <v>29.00669320859983</v>
       </c>
       <c r="R6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="S6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="T6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="U6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="V6" t="n">
-        <v>35.28116813397068</v>
+        <v>35.28116813397079</v>
       </c>
       <c r="W6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="X6" t="n">
-        <v>29.00669320536484</v>
+        <v>29.00669320536487</v>
       </c>
       <c r="Y6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.74254889115925</v>
+        <v>25.74254889115913</v>
       </c>
       <c r="AA6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
       <c r="AB6" t="n">
-        <v>29.00669320536489</v>
+        <v>29.00669320536486</v>
       </c>
     </row>
     <row r="7">
@@ -4114,43 +4114,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168.1872633079682</v>
+        <v>168.1872633079683</v>
       </c>
       <c r="C7" t="n">
         <v>169.7981650636616</v>
       </c>
       <c r="D7" t="n">
-        <v>167.5892334648391</v>
+        <v>167.589233464839</v>
       </c>
       <c r="E7" t="n">
-        <v>157.624559201004</v>
+        <v>157.6245592010041</v>
       </c>
       <c r="F7" t="n">
         <v>166.602729611377</v>
       </c>
       <c r="G7" t="n">
-        <v>164.8506091264425</v>
+        <v>164.8506091264426</v>
       </c>
       <c r="H7" t="n">
         <v>165.9537786226347</v>
       </c>
       <c r="I7" t="n">
-        <v>166.6672316284902</v>
+        <v>166.6672316284903</v>
       </c>
       <c r="J7" t="n">
-        <v>164.6962871950576</v>
+        <v>164.6962871950575</v>
       </c>
       <c r="K7" t="n">
-        <v>165.2267871374087</v>
+        <v>165.2267871374086</v>
       </c>
       <c r="L7" t="n">
-        <v>163.6022956766482</v>
+        <v>163.6022956766483</v>
       </c>
       <c r="M7" t="n">
         <v>160.4039483228433</v>
       </c>
       <c r="N7" t="n">
-        <v>166.0482846785952</v>
+        <v>166.0482846785951</v>
       </c>
       <c r="O7" t="n">
         <v>165.4964480144519</v>
@@ -4159,7 +4159,7 @@
         <v>161.9913868100441</v>
       </c>
       <c r="Q7" t="n">
-        <v>166.1231919289614</v>
+        <v>166.1231919289615</v>
       </c>
       <c r="R7" t="n">
         <v>166.8059728844276</v>
@@ -4168,13 +4168,13 @@
         <v>164.3272480385498</v>
       </c>
       <c r="T7" t="n">
-        <v>165.205755730613</v>
+        <v>165.2057557306128</v>
       </c>
       <c r="U7" t="n">
         <v>163.3434207351213</v>
       </c>
       <c r="V7" t="n">
-        <v>170.9574167727564</v>
+        <v>170.9574167727565</v>
       </c>
       <c r="W7" t="n">
         <v>159.9791698156314</v>
@@ -4183,13 +4183,13 @@
         <v>162.8569996206385</v>
       </c>
       <c r="Y7" t="n">
-        <v>159.2279588342392</v>
+        <v>159.2279588342391</v>
       </c>
       <c r="Z7" t="n">
         <v>167.4526899595293</v>
       </c>
       <c r="AA7" t="n">
-        <v>165.1808036683826</v>
+        <v>165.1808036683825</v>
       </c>
       <c r="AB7" t="n">
         <v>159.037742971155</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.4557983329993</v>
+        <v>169.4557983329996</v>
       </c>
       <c r="C8" t="n">
         <v>169.9275538907366</v>
@@ -4211,37 +4211,37 @@
         <v>169.3003705530898</v>
       </c>
       <c r="E8" t="n">
-        <v>157.1227218826056</v>
+        <v>157.1227218826055</v>
       </c>
       <c r="F8" t="n">
-        <v>169.0258928855521</v>
+        <v>169.0258928855522</v>
       </c>
       <c r="G8" t="n">
         <v>168.4993005724863</v>
       </c>
       <c r="H8" t="n">
-        <v>168.8444546874013</v>
+        <v>168.8444546874011</v>
       </c>
       <c r="I8" t="n">
-        <v>169.0405232677666</v>
+        <v>169.0405232677665</v>
       </c>
       <c r="J8" t="n">
-        <v>168.4635652511697</v>
+        <v>168.4635652511694</v>
       </c>
       <c r="K8" t="n">
-        <v>168.6267120016407</v>
+        <v>168.6267120016406</v>
       </c>
       <c r="L8" t="n">
-        <v>168.1510663242344</v>
+        <v>168.1510663242342</v>
       </c>
       <c r="M8" t="n">
         <v>167.2663853523777</v>
       </c>
       <c r="N8" t="n">
-        <v>168.8567789581254</v>
+        <v>168.8567789581252</v>
       </c>
       <c r="O8" t="n">
-        <v>168.6822637184326</v>
+        <v>168.6822637184327</v>
       </c>
       <c r="P8" t="n">
         <v>167.6742269094032</v>
@@ -4250,28 +4250,28 @@
         <v>168.8802870792032</v>
       </c>
       <c r="R8" t="n">
-        <v>169.0823805856324</v>
+        <v>169.0823805856323</v>
       </c>
       <c r="S8" t="n">
-        <v>168.353207249053</v>
+        <v>168.3532072490529</v>
       </c>
       <c r="T8" t="n">
         <v>168.6237136072691</v>
       </c>
       <c r="U8" t="n">
-        <v>168.0753140568554</v>
+        <v>168.0753140568555</v>
       </c>
       <c r="V8" t="n">
-        <v>173.7389777163085</v>
+        <v>173.7389777163084</v>
       </c>
       <c r="W8" t="n">
-        <v>167.1192798419554</v>
+        <v>167.1192798419555</v>
       </c>
       <c r="X8" t="n">
         <v>167.9532932052382</v>
       </c>
       <c r="Y8" t="n">
-        <v>166.9087326227649</v>
+        <v>166.9087326227648</v>
       </c>
       <c r="Z8" t="n">
         <v>169.2462105310069</v>
@@ -4280,7 +4280,7 @@
         <v>168.6058805340489</v>
       </c>
       <c r="AB8" t="n">
-        <v>166.8699021274633</v>
+        <v>166.8699021274634</v>
       </c>
     </row>
   </sheetData>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>171.1725808846672</v>
+        <v>171.1725808846671</v>
       </c>
       <c r="C2" t="n">
         <v>171.0416960360959</v>
@@ -4458,10 +4458,10 @@
         <v>158.6245727964092</v>
       </c>
       <c r="F2" t="n">
-        <v>171.2335715979517</v>
+        <v>171.2335715979518</v>
       </c>
       <c r="G2" t="n">
-        <v>171.8622811820059</v>
+        <v>171.8622811820058</v>
       </c>
       <c r="H2" t="n">
         <v>171.8066089175577</v>
@@ -4488,10 +4488,10 @@
         <v>172.4979237435164</v>
       </c>
       <c r="P2" t="n">
-        <v>172.993374664141</v>
+        <v>172.9933746641411</v>
       </c>
       <c r="Q2" t="n">
-        <v>171.7688949444725</v>
+        <v>171.7688949444726</v>
       </c>
       <c r="R2" t="n">
         <v>171.4620093551566</v>
@@ -4509,13 +4509,13 @@
         <v>177.0880319500466</v>
       </c>
       <c r="W2" t="n">
-        <v>173.8585320641368</v>
+        <v>173.8585320641369</v>
       </c>
       <c r="X2" t="n">
         <v>171.8663252071859</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.2995003326868</v>
+        <v>173.2995003326869</v>
       </c>
       <c r="Z2" t="n">
         <v>172.0190636874692</v>
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="C3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="D3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="E3" t="n">
-        <v>160.3857723816954</v>
+        <v>160.3857723816955</v>
       </c>
       <c r="F3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="G3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="H3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="I3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="J3" t="n">
         <v>173.5833904629341</v>
       </c>
       <c r="K3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="L3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="M3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="N3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="O3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="P3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="R3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="S3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="T3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="U3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="V3" t="n">
         <v>178.6278846868298</v>
       </c>
       <c r="W3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="X3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="Y3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="Z3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="AA3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
       <c r="AB3" t="n">
-        <v>173.5741272859391</v>
+        <v>173.5741272859392</v>
       </c>
     </row>
     <row r="4">
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.45900014971501</v>
+        <v>75.45900014971511</v>
       </c>
       <c r="C4" t="n">
-        <v>46.89734842136318</v>
+        <v>46.89734842136313</v>
       </c>
       <c r="D4" t="n">
         <v>137.472335391421</v>
@@ -4637,13 +4637,13 @@
         <v>100.8033743255311</v>
       </c>
       <c r="G4" t="n">
-        <v>231.5688634719762</v>
+        <v>231.568863471976</v>
       </c>
       <c r="H4" t="n">
         <v>273.7733602385117</v>
       </c>
       <c r="I4" t="n">
-        <v>155.1497181445955</v>
+        <v>155.1497181445953</v>
       </c>
       <c r="J4" t="n">
         <v>292.9726428356607</v>
@@ -4652,55 +4652,55 @@
         <v>206.6779784471504</v>
       </c>
       <c r="L4" t="n">
-        <v>237.4409125595874</v>
+        <v>237.4409125595876</v>
       </c>
       <c r="M4" t="n">
-        <v>354.329736125048</v>
+        <v>354.3297361250482</v>
       </c>
       <c r="N4" t="n">
-        <v>416.8308364519179</v>
+        <v>416.8308364519181</v>
       </c>
       <c r="O4" t="n">
-        <v>389.1297953945867</v>
+        <v>389.1297953945868</v>
       </c>
       <c r="P4" t="n">
-        <v>537.7492163823389</v>
+        <v>537.7492163823395</v>
       </c>
       <c r="Q4" t="n">
-        <v>236.5844698923872</v>
+        <v>236.584469892387</v>
       </c>
       <c r="R4" t="n">
-        <v>171.4490911370177</v>
+        <v>171.4490911370176</v>
       </c>
       <c r="S4" t="n">
-        <v>182.3105583662581</v>
+        <v>182.3105583662579</v>
       </c>
       <c r="T4" t="n">
-        <v>291.1108550633024</v>
+        <v>291.1108550633021</v>
       </c>
       <c r="U4" t="n">
-        <v>422.425770474693</v>
+        <v>422.4257704746938</v>
       </c>
       <c r="V4" t="n">
-        <v>302.0662177828005</v>
+        <v>302.0662177828009</v>
       </c>
       <c r="W4" t="n">
-        <v>812.4037559467105</v>
+        <v>812.4037559467113</v>
       </c>
       <c r="X4" t="n">
-        <v>274.6885620449355</v>
+        <v>274.6885620449357</v>
       </c>
       <c r="Y4" t="n">
-        <v>650.4325214277408</v>
+        <v>650.432521427741</v>
       </c>
       <c r="Z4" t="n">
-        <v>276.5811891927048</v>
+        <v>276.581189192705</v>
       </c>
       <c r="AA4" t="n">
-        <v>272.0516636543776</v>
+        <v>272.0516636543771</v>
       </c>
       <c r="AB4" t="n">
-        <v>516.8334916032015</v>
+        <v>516.8334916032009</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.14249434590168</v>
+        <v>13.14249434590179</v>
       </c>
       <c r="C5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="D5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="E5" t="n">
-        <v>15.86135577366788</v>
+        <v>15.86135577366786</v>
       </c>
       <c r="F5" t="n">
-        <v>14.04846249412015</v>
+        <v>14.04846249412022</v>
       </c>
       <c r="G5" t="n">
-        <v>20.16373058246661</v>
+        <v>20.1637305824666</v>
       </c>
       <c r="H5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="I5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="J5" t="n">
-        <v>18.9651497100576</v>
+        <v>18.96514971005763</v>
       </c>
       <c r="K5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="L5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="M5" t="n">
-        <v>18.95787377488725</v>
+        <v>18.95787377488737</v>
       </c>
       <c r="N5" t="n">
-        <v>416.8308364519179</v>
+        <v>14.44998182334052</v>
       </c>
       <c r="O5" t="n">
-        <v>15.68878966842906</v>
+        <v>15.68878966842913</v>
       </c>
       <c r="P5" t="n">
-        <v>15.38512793229062</v>
+        <v>15.38512793229072</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.99963956090279</v>
+        <v>11.99963956090285</v>
       </c>
       <c r="R5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="S5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="T5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="U5" t="n">
-        <v>16.09887570274631</v>
+        <v>16.09887570274638</v>
       </c>
       <c r="V5" t="n">
-        <v>17.39230286579727</v>
+        <v>17.39230286579725</v>
       </c>
       <c r="W5" t="n">
-        <v>18.95901665472842</v>
+        <v>18.95901665472853</v>
       </c>
       <c r="X5" t="n">
-        <v>12.53263063548009</v>
+        <v>12.5326306354801</v>
       </c>
       <c r="Y5" t="n">
-        <v>24.70475140980642</v>
+        <v>24.70475140980651</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.03447068813039</v>
+        <v>13.03447068813035</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.9578737748789</v>
+        <v>18.95787377487902</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.03252385437309</v>
+        <v>25.03252385437305</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.84354834070315</v>
+        <v>25.84354834070313</v>
       </c>
       <c r="C6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="D6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="E6" t="n">
-        <v>30.4923912973475</v>
+        <v>30.49239129734754</v>
       </c>
       <c r="F6" t="n">
-        <v>17.95486312141051</v>
+        <v>17.95486312141054</v>
       </c>
       <c r="G6" t="n">
-        <v>31.88725388518869</v>
+        <v>31.88725388518872</v>
       </c>
       <c r="H6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="I6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="J6" t="n">
-        <v>31.89452745779755</v>
+        <v>31.8945274577976</v>
       </c>
       <c r="K6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="L6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="M6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="N6" t="n">
-        <v>416.8308364519179</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="O6" t="n">
-        <v>33.89012998907392</v>
+        <v>33.89012998907403</v>
       </c>
       <c r="P6" t="n">
-        <v>34.3257211781025</v>
+        <v>34.32572117810258</v>
       </c>
       <c r="Q6" t="n">
-        <v>31.88725388518869</v>
+        <v>31.88725388518872</v>
       </c>
       <c r="R6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="S6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="T6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="U6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="V6" t="n">
-        <v>38.90812347690147</v>
+        <v>38.90812347690148</v>
       </c>
       <c r="W6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="X6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="Y6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="Z6" t="n">
-        <v>28.24343686912981</v>
+        <v>28.2434368691299</v>
       </c>
       <c r="AA6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
       <c r="AB6" t="n">
-        <v>31.88725152261907</v>
+        <v>31.88725152261902</v>
       </c>
     </row>
     <row r="7">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171.900866656688</v>
+        <v>171.9008666566881</v>
       </c>
       <c r="C7" t="n">
         <v>172.6923151444396</v>
@@ -4895,7 +4895,7 @@
         <v>170.8127254551312</v>
       </c>
       <c r="E7" t="n">
-        <v>156.1542956398147</v>
+        <v>156.154295639815</v>
       </c>
       <c r="F7" t="n">
         <v>171.5792157094902</v>
@@ -4904,16 +4904,16 @@
         <v>167.8009325504447</v>
       </c>
       <c r="H7" t="n">
-        <v>168.2490080597383</v>
+        <v>168.2490080597384</v>
       </c>
       <c r="I7" t="n">
-        <v>170.4917871933949</v>
+        <v>170.491787193395</v>
       </c>
       <c r="J7" t="n">
-        <v>166.7624743376019</v>
+        <v>166.7624743376021</v>
       </c>
       <c r="K7" t="n">
-        <v>168.9467699490187</v>
+        <v>168.9467699490186</v>
       </c>
       <c r="L7" t="n">
         <v>167.8195090244443</v>
@@ -4925,19 +4925,19 @@
         <v>164.5248110843014</v>
       </c>
       <c r="O7" t="n">
-        <v>164.005761997053</v>
+        <v>164.0057619970531</v>
       </c>
       <c r="P7" t="n">
-        <v>161.0439055409642</v>
+        <v>161.0439055409644</v>
       </c>
       <c r="Q7" t="n">
-        <v>168.4205987092924</v>
+        <v>168.4205987092923</v>
       </c>
       <c r="R7" t="n">
-        <v>170.2445211160399</v>
+        <v>170.2445211160402</v>
       </c>
       <c r="S7" t="n">
-        <v>168.8857234958745</v>
+        <v>168.8857234958744</v>
       </c>
       <c r="T7" t="n">
         <v>167.3541859357907</v>
@@ -4955,7 +4955,7 @@
         <v>167.8575504630602</v>
       </c>
       <c r="Y7" t="n">
-        <v>159.384089243338</v>
+        <v>159.3840892433382</v>
       </c>
       <c r="Z7" t="n">
         <v>166.8724283661591</v>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>170.4112419659926</v>
+        <v>170.4112419659927</v>
       </c>
       <c r="C8" t="n">
-        <v>170.6404687015449</v>
+        <v>170.640468701545</v>
       </c>
       <c r="D8" t="n">
         <v>170.1063084714801</v>
@@ -4989,19 +4989,19 @@
         <v>170.3258804732614</v>
       </c>
       <c r="G8" t="n">
-        <v>169.2354591792759</v>
+        <v>169.2354591792758</v>
       </c>
       <c r="H8" t="n">
-        <v>169.3836626994883</v>
+        <v>169.3836626994884</v>
       </c>
       <c r="I8" t="n">
         <v>170.0160588552513</v>
       </c>
       <c r="J8" t="n">
-        <v>168.9499596490288</v>
+        <v>168.9499596490287</v>
       </c>
       <c r="K8" t="n">
-        <v>169.5747304601738</v>
+        <v>169.5747304601739</v>
       </c>
       <c r="L8" t="n">
         <v>169.2463600772514</v>
@@ -5010,34 +5010,34 @@
         <v>168.6449077856012</v>
       </c>
       <c r="N8" t="n">
-        <v>168.3122524371134</v>
+        <v>168.3122524371133</v>
       </c>
       <c r="O8" t="n">
-        <v>168.1442870445023</v>
+        <v>168.1442870445022</v>
       </c>
       <c r="P8" t="n">
         <v>167.2920838387301</v>
       </c>
       <c r="Q8" t="n">
-        <v>169.4240230187771</v>
+        <v>169.4240230187772</v>
       </c>
       <c r="R8" t="n">
-        <v>169.9470279370273</v>
+        <v>169.9470279370272</v>
       </c>
       <c r="S8" t="n">
         <v>169.5486012483164</v>
       </c>
       <c r="T8" t="n">
-        <v>169.1237800324255</v>
+        <v>169.1237800324253</v>
       </c>
       <c r="U8" t="n">
         <v>168.1395381063389</v>
       </c>
       <c r="V8" t="n">
-        <v>173.786624838027</v>
+        <v>173.7866248380269</v>
       </c>
       <c r="W8" t="n">
-        <v>165.8903412131661</v>
+        <v>165.8903412131662</v>
       </c>
       <c r="X8" t="n">
         <v>169.2652645351266</v>
@@ -5049,7 +5049,7 @@
         <v>168.969769321922</v>
       </c>
       <c r="AA8" t="n">
-        <v>169.2355394556619</v>
+        <v>169.2355394556617</v>
       </c>
       <c r="AB8" t="n">
         <v>167.9146939878939</v>
@@ -5224,43 +5224,43 @@
         <v>170.2162628828603</v>
       </c>
       <c r="D2" t="n">
-        <v>170.1627546003506</v>
+        <v>170.1627546003505</v>
       </c>
       <c r="E2" t="n">
-        <v>157.6185852245891</v>
+        <v>157.618585224589</v>
       </c>
       <c r="F2" t="n">
         <v>170.403647375656</v>
       </c>
       <c r="G2" t="n">
-        <v>170.814411123965</v>
+        <v>170.8144111239648</v>
       </c>
       <c r="H2" t="n">
-        <v>170.757101679151</v>
+        <v>170.7571016791509</v>
       </c>
       <c r="I2" t="n">
         <v>170.3827871893537</v>
       </c>
       <c r="J2" t="n">
-        <v>170.7863372211774</v>
+        <v>170.7863372211775</v>
       </c>
       <c r="K2" t="n">
         <v>170.3153046061537</v>
       </c>
       <c r="L2" t="n">
-        <v>170.1609896414296</v>
+        <v>170.1609896414295</v>
       </c>
       <c r="M2" t="n">
-        <v>170.5684626605841</v>
+        <v>170.568462660584</v>
       </c>
       <c r="N2" t="n">
-        <v>171.1762159545151</v>
+        <v>171.176215954515</v>
       </c>
       <c r="O2" t="n">
-        <v>171.3922408237457</v>
+        <v>171.3922408237456</v>
       </c>
       <c r="P2" t="n">
-        <v>171.8187092438094</v>
+        <v>171.8187092438093</v>
       </c>
       <c r="Q2" t="n">
         <v>170.4017804332119</v>
@@ -5272,25 +5272,25 @@
         <v>170.534761770376</v>
       </c>
       <c r="T2" t="n">
-        <v>170.7298784605984</v>
+        <v>170.7298784605982</v>
       </c>
       <c r="U2" t="n">
-        <v>170.8399181054017</v>
+        <v>170.8399181054018</v>
       </c>
       <c r="V2" t="n">
-        <v>175.837782476819</v>
+        <v>175.8377824768189</v>
       </c>
       <c r="W2" t="n">
-        <v>171.8957065898614</v>
+        <v>171.8957065898613</v>
       </c>
       <c r="X2" t="n">
-        <v>171.4730086386719</v>
+        <v>171.473008638672</v>
       </c>
       <c r="Y2" t="n">
-        <v>171.9300067360998</v>
+        <v>171.9300067360997</v>
       </c>
       <c r="Z2" t="n">
-        <v>170.518984001568</v>
+        <v>170.5189840015679</v>
       </c>
       <c r="AA2" t="n">
         <v>171.1478556686039</v>
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="C3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="D3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="E3" t="n">
-        <v>159.8214320322936</v>
+        <v>159.8214320322935</v>
       </c>
       <c r="F3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="G3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="H3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="I3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="J3" t="n">
-        <v>172.6874327342538</v>
+        <v>172.6874327342539</v>
       </c>
       <c r="K3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="L3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="M3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="N3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="O3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="P3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="Q3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="R3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="S3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="T3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="U3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="V3" t="n">
-        <v>177.6926146331318</v>
+        <v>177.6926146331317</v>
       </c>
       <c r="W3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="X3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="Y3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="Z3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="AA3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
       <c r="AB3" t="n">
-        <v>172.6800232200028</v>
+        <v>172.6800232200027</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.24849507723145</v>
+        <v>23.24849507723149</v>
       </c>
       <c r="C4" t="n">
-        <v>56.77815285342918</v>
+        <v>56.77815285342916</v>
       </c>
       <c r="D4" t="n">
-        <v>43.8805648353422</v>
+        <v>43.88056483534216</v>
       </c>
       <c r="E4" t="n">
         <v>72.08630797463368</v>
       </c>
       <c r="F4" t="n">
-        <v>104.898143718488</v>
+        <v>104.8981437184879</v>
       </c>
       <c r="G4" t="n">
-        <v>174.474923015068</v>
+        <v>174.4749230150682</v>
       </c>
       <c r="H4" t="n">
-        <v>206.7655594422669</v>
+        <v>206.7655594422668</v>
       </c>
       <c r="I4" t="n">
-        <v>101.52167473429</v>
+        <v>101.5216747342898</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5328856133834</v>
+        <v>179.5328856133833</v>
       </c>
       <c r="K4" t="n">
-        <v>77.23033451078017</v>
+        <v>77.23033451078015</v>
       </c>
       <c r="L4" t="n">
-        <v>38.53793514145766</v>
+        <v>38.53793514145755</v>
       </c>
       <c r="M4" t="n">
-        <v>131.5248764654969</v>
+        <v>131.5248764654968</v>
       </c>
       <c r="N4" t="n">
-        <v>289.8036832645926</v>
+        <v>289.8036832645923</v>
       </c>
       <c r="O4" t="n">
-        <v>311.586512708952</v>
+        <v>311.5865127089521</v>
       </c>
       <c r="P4" t="n">
-        <v>424.4821661648392</v>
+        <v>424.4821661648396</v>
       </c>
       <c r="Q4" t="n">
-        <v>93.88349919188772</v>
+        <v>93.88349919188764</v>
       </c>
       <c r="R4" t="n">
-        <v>61.19490376786707</v>
+        <v>61.19490376786697</v>
       </c>
       <c r="S4" t="n">
-        <v>116.4149014238652</v>
+        <v>116.4149014238653</v>
       </c>
       <c r="T4" t="n">
-        <v>181.2189089038451</v>
+        <v>181.2189089038448</v>
       </c>
       <c r="U4" t="n">
-        <v>181.2592199622957</v>
+        <v>181.2592199622955</v>
       </c>
       <c r="V4" t="n">
-        <v>202.3169785898984</v>
+        <v>202.3169785898985</v>
       </c>
       <c r="W4" t="n">
-        <v>453.1437333715523</v>
+        <v>453.1437333715519</v>
       </c>
       <c r="X4" t="n">
-        <v>359.0370583688267</v>
+        <v>359.0370583688269</v>
       </c>
       <c r="Y4" t="n">
-        <v>490.8843830044029</v>
+        <v>490.8843830044034</v>
       </c>
       <c r="Z4" t="n">
-        <v>118.3043127003422</v>
+        <v>118.304312700342</v>
       </c>
       <c r="AA4" t="n">
-        <v>292.6733668207252</v>
+        <v>292.6733668207258</v>
       </c>
       <c r="AB4" t="n">
-        <v>296.2404415428572</v>
+        <v>296.2404415428574</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.59749078246276</v>
+        <v>10.59749078246275</v>
       </c>
       <c r="C5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="D5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="E5" t="n">
-        <v>12.7044341602696</v>
+        <v>12.70443416026959</v>
       </c>
       <c r="F5" t="n">
-        <v>11.29955804162262</v>
+        <v>11.29955804162265</v>
       </c>
       <c r="G5" t="n">
-        <v>16.03849893470231</v>
+        <v>16.03849893470226</v>
       </c>
       <c r="H5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="I5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="J5" t="n">
-        <v>15.11087084788199</v>
+        <v>15.1108708478819</v>
       </c>
       <c r="K5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="L5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="M5" t="n">
-        <v>15.10403718185552</v>
+        <v>15.10403718185545</v>
       </c>
       <c r="N5" t="n">
-        <v>289.8036832645926</v>
+        <v>11.61070979188589</v>
       </c>
       <c r="O5" t="n">
-        <v>12.57070648739146</v>
+        <v>12.57070648739138</v>
       </c>
       <c r="P5" t="n">
-        <v>12.33538810090483</v>
+        <v>12.3353881009048</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.711851559807888</v>
+        <v>9.71185155980795</v>
       </c>
       <c r="R5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="S5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="T5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="U5" t="n">
         <v>12.88181070480298</v>
       </c>
       <c r="V5" t="n">
-        <v>13.89090964225844</v>
+        <v>13.89090964225838</v>
       </c>
       <c r="W5" t="n">
-        <v>15.10492284094837</v>
+        <v>15.10492284094833</v>
       </c>
       <c r="X5" t="n">
-        <v>10.12488548801819</v>
+        <v>10.12488548801815</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.54606097163703</v>
+        <v>19.54606097163699</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5137793699784</v>
+        <v>10.51377936997838</v>
       </c>
       <c r="AA5" t="n">
-        <v>15.10403718185755</v>
+        <v>15.10403718185747</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.81150172136228</v>
+        <v>19.81150172136222</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.9537115368626</v>
+        <v>19.95371153686257</v>
       </c>
       <c r="C6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="D6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="E6" t="n">
-        <v>23.45282142978964</v>
+        <v>23.45282142978961</v>
       </c>
       <c r="F6" t="n">
-        <v>14.01602408421125</v>
+        <v>14.01602408421128</v>
       </c>
       <c r="G6" t="n">
         <v>24.50271223614899</v>
       </c>
       <c r="H6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="I6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="J6" t="n">
-        <v>24.50954389051182</v>
+        <v>24.50954389051174</v>
       </c>
       <c r="K6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="L6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="M6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="N6" t="n">
-        <v>289.8036832645926</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="O6" t="n">
-        <v>26.01024511148407</v>
+        <v>26.0102451114841</v>
       </c>
       <c r="P6" t="n">
-        <v>26.33810764696155</v>
+        <v>26.33810764696151</v>
       </c>
       <c r="Q6" t="n">
         <v>24.50271223614899</v>
       </c>
       <c r="R6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="S6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="T6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="U6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="V6" t="n">
-        <v>29.79571096124611</v>
+        <v>29.79571096124601</v>
       </c>
       <c r="W6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="X6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="Y6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.7600693274044</v>
+        <v>21.76006932740439</v>
       </c>
       <c r="AA6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
       <c r="AB6" t="n">
-        <v>24.50271022448729</v>
+        <v>24.50271022448734</v>
       </c>
     </row>
     <row r="7">
@@ -5658,19 +5658,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172.2135851033931</v>
+        <v>172.213585103393</v>
       </c>
       <c r="C7" t="n">
-        <v>171.4507356981183</v>
+        <v>171.4507356981182</v>
       </c>
       <c r="D7" t="n">
-        <v>171.7655882610224</v>
+        <v>171.7655882610222</v>
       </c>
       <c r="E7" t="n">
         <v>158.2261956286123</v>
       </c>
       <c r="F7" t="n">
-        <v>170.3659088093045</v>
+        <v>170.3659088093044</v>
       </c>
       <c r="G7" t="n">
         <v>167.8771057577668</v>
@@ -5682,13 +5682,13 @@
         <v>170.4808685168116</v>
       </c>
       <c r="J7" t="n">
-        <v>168.1196127486882</v>
+        <v>168.1196127486883</v>
       </c>
       <c r="K7" t="n">
-        <v>170.8694558145979</v>
+        <v>170.8694558145977</v>
       </c>
       <c r="L7" t="n">
-        <v>171.767525862451</v>
+        <v>171.7675258624509</v>
       </c>
       <c r="M7" t="n">
         <v>169.4016367138435</v>
@@ -5697,31 +5697,31 @@
         <v>165.8002144972922</v>
       </c>
       <c r="O7" t="n">
-        <v>164.4278457727888</v>
+        <v>164.4278457727889</v>
       </c>
       <c r="P7" t="n">
-        <v>161.8783595239587</v>
+        <v>161.8783595239589</v>
       </c>
       <c r="Q7" t="n">
-        <v>170.3595634951815</v>
+        <v>170.3595634951816</v>
       </c>
       <c r="R7" t="n">
         <v>171.4308162495645</v>
       </c>
       <c r="S7" t="n">
-        <v>169.5478221761042</v>
+        <v>169.5478221761041</v>
       </c>
       <c r="T7" t="n">
-        <v>168.4463334470825</v>
+        <v>168.4463334470824</v>
       </c>
       <c r="U7" t="n">
         <v>167.7488901086929</v>
       </c>
       <c r="V7" t="n">
-        <v>172.3668728448902</v>
+        <v>172.3668728448901</v>
       </c>
       <c r="W7" t="n">
-        <v>161.5307953475855</v>
+        <v>161.5307953475854</v>
       </c>
       <c r="X7" t="n">
         <v>164.0824678033168</v>
@@ -5733,7 +5733,7 @@
         <v>169.6353590118338</v>
       </c>
       <c r="AA7" t="n">
-        <v>165.950068647674</v>
+        <v>165.9500686476739</v>
       </c>
       <c r="AB7" t="n">
         <v>165.974660002363</v>
@@ -5752,7 +5752,7 @@
         <v>169.656933142896</v>
       </c>
       <c r="D8" t="n">
-        <v>169.7466837798833</v>
+        <v>169.7466837798831</v>
       </c>
       <c r="E8" t="n">
         <v>156.8927475771972</v>
@@ -5761,70 +5761,70 @@
         <v>169.3507179441434</v>
       </c>
       <c r="G8" t="n">
-        <v>168.6290683726578</v>
+        <v>168.6290683726577</v>
       </c>
       <c r="H8" t="n">
-        <v>168.7704740299841</v>
+        <v>168.770474029984</v>
       </c>
       <c r="I8" t="n">
-        <v>169.3821647911118</v>
+        <v>169.3821647911117</v>
       </c>
       <c r="J8" t="n">
         <v>168.7079645709665</v>
       </c>
       <c r="K8" t="n">
-        <v>169.4914906667587</v>
+        <v>169.4914906667586</v>
       </c>
       <c r="L8" t="n">
         <v>169.7458004357869</v>
       </c>
       <c r="M8" t="n">
-        <v>169.0767863526837</v>
+        <v>169.0767863526836</v>
       </c>
       <c r="N8" t="n">
-        <v>168.0458810610324</v>
+        <v>168.0458810610322</v>
       </c>
       <c r="O8" t="n">
-        <v>167.6374737871341</v>
+        <v>167.6374737871342</v>
       </c>
       <c r="P8" t="n">
-        <v>166.9039178392495</v>
+        <v>166.9039178392496</v>
       </c>
       <c r="Q8" t="n">
         <v>169.345963863552</v>
       </c>
       <c r="R8" t="n">
-        <v>169.652358853139</v>
+        <v>169.6523588531391</v>
       </c>
       <c r="S8" t="n">
-        <v>169.1096003136696</v>
+        <v>169.1096003136697</v>
       </c>
       <c r="T8" t="n">
         <v>168.8035361219509</v>
       </c>
       <c r="U8" t="n">
-        <v>168.596236825167</v>
+        <v>168.5962368251669</v>
       </c>
       <c r="V8" t="n">
         <v>173.4145529910369</v>
       </c>
       <c r="W8" t="n">
-        <v>166.8227723774305</v>
+        <v>166.8227723774304</v>
       </c>
       <c r="X8" t="n">
-        <v>167.5610935252964</v>
+        <v>167.5610935252963</v>
       </c>
       <c r="Y8" t="n">
-        <v>166.7733044605034</v>
+        <v>166.7733044605035</v>
       </c>
       <c r="Z8" t="n">
         <v>169.1336520840819</v>
       </c>
       <c r="AA8" t="n">
-        <v>168.0857048911016</v>
+        <v>168.0857048911015</v>
       </c>
       <c r="AB8" t="n">
-        <v>168.1006840465966</v>
+        <v>168.1006840465964</v>
       </c>
     </row>
   </sheetData>
@@ -5990,61 +5990,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>169.583253864868</v>
+        <v>169.5832538648679</v>
       </c>
       <c r="C2" t="n">
-        <v>169.6583629968544</v>
+        <v>169.6583629968542</v>
       </c>
       <c r="D2" t="n">
-        <v>169.7738210806061</v>
+        <v>169.7738210806059</v>
       </c>
       <c r="E2" t="n">
-        <v>157.1483772701753</v>
+        <v>157.148377270175</v>
       </c>
       <c r="F2" t="n">
-        <v>170.0769925067266</v>
+        <v>170.0769925067264</v>
       </c>
       <c r="G2" t="n">
-        <v>169.9796048258076</v>
+        <v>169.9796048258074</v>
       </c>
       <c r="H2" t="n">
-        <v>170.2323202143377</v>
+        <v>170.2323202143376</v>
       </c>
       <c r="I2" t="n">
-        <v>169.8494682091853</v>
+        <v>169.849468209185</v>
       </c>
       <c r="J2" t="n">
         <v>170.0764762032242</v>
       </c>
       <c r="K2" t="n">
-        <v>169.8508726575108</v>
+        <v>169.8508726575107</v>
       </c>
       <c r="L2" t="n">
-        <v>169.6925779399949</v>
+        <v>169.6925779399947</v>
       </c>
       <c r="M2" t="n">
-        <v>170.0590172098873</v>
+        <v>170.0590172098872</v>
       </c>
       <c r="N2" t="n">
-        <v>170.3166186213994</v>
+        <v>170.3166186213991</v>
       </c>
       <c r="O2" t="n">
-        <v>170.5473070931135</v>
+        <v>170.5473070931134</v>
       </c>
       <c r="P2" t="n">
-        <v>171.0958017583075</v>
+        <v>171.0958017583073</v>
       </c>
       <c r="Q2" t="n">
-        <v>169.7788083025277</v>
+        <v>169.7788083025276</v>
       </c>
       <c r="R2" t="n">
-        <v>169.6967823022835</v>
+        <v>169.6967823022833</v>
       </c>
       <c r="S2" t="n">
-        <v>170.2185609380894</v>
+        <v>170.2185609380892</v>
       </c>
       <c r="T2" t="n">
-        <v>170.1558782413661</v>
+        <v>170.1558782413659</v>
       </c>
       <c r="U2" t="n">
         <v>170.3381074604746</v>
@@ -6053,22 +6053,22 @@
         <v>174.9806302074844</v>
       </c>
       <c r="W2" t="n">
-        <v>170.6271174462154</v>
+        <v>170.6271174462153</v>
       </c>
       <c r="X2" t="n">
-        <v>171.1200310504953</v>
+        <v>171.1200310504952</v>
       </c>
       <c r="Y2" t="n">
-        <v>170.8566474795445</v>
+        <v>170.8566474795443</v>
       </c>
       <c r="Z2" t="n">
-        <v>169.7538137542519</v>
+        <v>169.7538137542517</v>
       </c>
       <c r="AA2" t="n">
-        <v>170.7222942063633</v>
+        <v>170.7222942063632</v>
       </c>
       <c r="AB2" t="n">
-        <v>170.4801965993067</v>
+        <v>170.4801965993065</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>172.1755887754483</v>
       </c>
       <c r="E3" t="n">
-        <v>159.5370523670328</v>
+        <v>159.5370523670327</v>
       </c>
       <c r="F3" t="n">
         <v>172.1755887754483</v>
@@ -6102,7 +6102,7 @@
         <v>172.1755887754483</v>
       </c>
       <c r="J3" t="n">
-        <v>172.1819641811524</v>
+        <v>172.1819641811523</v>
       </c>
       <c r="K3" t="n">
         <v>172.1755887754483</v>
@@ -6166,85 +6166,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.16216914091946</v>
+        <v>22.16216914091957</v>
       </c>
       <c r="C4" t="n">
-        <v>42.26916701708162</v>
+        <v>42.26916701708166</v>
       </c>
       <c r="D4" t="n">
-        <v>71.36409926520906</v>
+        <v>71.36409926520894</v>
       </c>
       <c r="E4" t="n">
-        <v>24.4674674947038</v>
+        <v>24.4674674947039</v>
       </c>
       <c r="F4" t="n">
-        <v>151.5567946057508</v>
+        <v>151.5567946057511</v>
       </c>
       <c r="G4" t="n">
-        <v>109.4450496410286</v>
+        <v>109.4450496410288</v>
       </c>
       <c r="H4" t="n">
-        <v>197.587719137482</v>
+        <v>197.5877191374819</v>
       </c>
       <c r="I4" t="n">
-        <v>93.35339627433832</v>
+        <v>93.35339627433822</v>
       </c>
       <c r="J4" t="n">
         <v>137.6545299565356</v>
       </c>
       <c r="K4" t="n">
-        <v>87.67439913999567</v>
+        <v>87.67439913999566</v>
       </c>
       <c r="L4" t="n">
         <v>45.65148597776255</v>
       </c>
       <c r="M4" t="n">
-        <v>140.17461430744</v>
+        <v>140.1746143074401</v>
       </c>
       <c r="N4" t="n">
-        <v>206.4866000748666</v>
+        <v>206.4866000748667</v>
       </c>
       <c r="O4" t="n">
-        <v>236.2884355131689</v>
+        <v>236.2884355131686</v>
       </c>
       <c r="P4" t="n">
-        <v>361.6304202643194</v>
+        <v>361.6304202643191</v>
       </c>
       <c r="Q4" t="n">
-        <v>69.40663353915707</v>
+        <v>69.40663353915717</v>
       </c>
       <c r="R4" t="n">
-        <v>54.76142394402919</v>
+        <v>54.76142394402886</v>
       </c>
       <c r="S4" t="n">
         <v>164.0291796787199</v>
       </c>
       <c r="T4" t="n">
-        <v>168.876187087127</v>
+        <v>168.8761870871271</v>
       </c>
       <c r="U4" t="n">
         <v>187.4519677555072</v>
       </c>
       <c r="V4" t="n">
-        <v>144.6426084494777</v>
+        <v>144.6426084494779</v>
       </c>
       <c r="W4" t="n">
-        <v>275.7910957193722</v>
+        <v>275.7910957193727</v>
       </c>
       <c r="X4" t="n">
-        <v>387.6876104495225</v>
+        <v>387.6876104495224</v>
       </c>
       <c r="Y4" t="n">
-        <v>350.125115915004</v>
+        <v>350.1251159150046</v>
       </c>
       <c r="Z4" t="n">
-        <v>58.2315141555214</v>
+        <v>58.23151415552127</v>
       </c>
       <c r="AA4" t="n">
         <v>312.175907693342</v>
       </c>
       <c r="AB4" t="n">
-        <v>263.2209152486886</v>
+        <v>263.2209152486881</v>
       </c>
     </row>
     <row r="5">
@@ -6254,85 +6254,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.551073080639306</v>
+        <v>9.551073080639354</v>
       </c>
       <c r="C5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="D5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="E5" t="n">
-        <v>11.44331612046141</v>
+        <v>11.44331612046142</v>
       </c>
       <c r="F5" t="n">
-        <v>10.18159875054095</v>
+        <v>10.18159875054093</v>
       </c>
       <c r="G5" t="n">
-        <v>14.43763525146732</v>
+        <v>14.43763525146733</v>
       </c>
       <c r="H5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="I5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="J5" t="n">
-        <v>13.60496712182199</v>
+        <v>13.60496712182201</v>
       </c>
       <c r="K5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="L5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="M5" t="n">
         <v>13.59839639647526</v>
       </c>
       <c r="N5" t="n">
-        <v>206.4866000748667</v>
+        <v>10.46104372285405</v>
       </c>
       <c r="O5" t="n">
-        <v>11.32321547592139</v>
+        <v>11.32321547592128</v>
       </c>
       <c r="P5" t="n">
-        <v>11.1118763465552</v>
+        <v>11.11187634655511</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.755681674898396</v>
+        <v>8.755681674898483</v>
       </c>
       <c r="R5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="S5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="T5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="U5" t="n">
-        <v>11.59878228745565</v>
+        <v>11.59878228745562</v>
       </c>
       <c r="V5" t="n">
-        <v>12.507350846413</v>
+        <v>12.50735084641301</v>
       </c>
       <c r="W5" t="n">
-        <v>13.59919180602781</v>
+        <v>13.59919180602776</v>
       </c>
       <c r="X5" t="n">
-        <v>9.126626895593894</v>
+        <v>9.126626895593814</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.58121066686975</v>
+        <v>17.58121066686979</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.475891972612411</v>
+        <v>9.475891972612432</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.59839639648246</v>
+        <v>13.59839639648244</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.8261640265025</v>
+        <v>17.82616402650245</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.93780067603036</v>
+        <v>16.93780067603049</v>
       </c>
       <c r="C6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="D6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="E6" t="n">
-        <v>19.86419827796885</v>
+        <v>19.86419827796876</v>
       </c>
       <c r="F6" t="n">
-        <v>11.97195654589254</v>
+        <v>11.97195654589253</v>
       </c>
       <c r="G6" t="n">
-        <v>20.74224956302219</v>
+        <v>20.74224956302218</v>
       </c>
       <c r="H6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="I6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7488195861401</v>
+        <v>20.74881958614004</v>
       </c>
       <c r="K6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="L6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="M6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="N6" t="n">
-        <v>206.4866000748666</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="O6" t="n">
-        <v>22.00303894267027</v>
+        <v>22.00303894267025</v>
       </c>
       <c r="P6" t="n">
-        <v>22.27723900124117</v>
+        <v>22.27723900124106</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.74224956302219</v>
+        <v>20.74224956302218</v>
       </c>
       <c r="R6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="S6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="T6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="U6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="V6" t="n">
-        <v>25.17430735071653</v>
+        <v>25.17430735071656</v>
       </c>
       <c r="W6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="X6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.4485051889608</v>
+        <v>18.44850518896081</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.74224886080056</v>
+        <v>20.74224886080052</v>
       </c>
     </row>
     <row r="7">
@@ -6433,34 +6433,34 @@
         <v>171.7221554003081</v>
       </c>
       <c r="C7" t="n">
-        <v>171.2881843748569</v>
+        <v>171.288184374857</v>
       </c>
       <c r="D7" t="n">
         <v>170.6129149287973</v>
       </c>
       <c r="E7" t="n">
-        <v>159.0487403582593</v>
+        <v>159.0487403582592</v>
       </c>
       <c r="F7" t="n">
         <v>168.8533788851605</v>
       </c>
       <c r="G7" t="n">
-        <v>169.3657588240187</v>
+        <v>169.3657588240188</v>
       </c>
       <c r="H7" t="n">
-        <v>167.9559037463282</v>
+        <v>167.9559037463281</v>
       </c>
       <c r="I7" t="n">
-        <v>170.1735675706406</v>
+        <v>170.1735675706405</v>
       </c>
       <c r="J7" t="n">
-        <v>168.8586706441936</v>
+        <v>168.8586706441934</v>
       </c>
       <c r="K7" t="n">
         <v>170.1587250515088</v>
       </c>
       <c r="L7" t="n">
-        <v>171.07870608507</v>
+        <v>171.0787060850701</v>
       </c>
       <c r="M7" t="n">
         <v>168.9546464043218</v>
@@ -6469,46 +6469,46 @@
         <v>167.4133911196666</v>
       </c>
       <c r="O7" t="n">
-        <v>165.9800946119673</v>
+        <v>165.9800946119672</v>
       </c>
       <c r="P7" t="n">
-        <v>162.7050441916019</v>
+        <v>162.7050441916018</v>
       </c>
       <c r="Q7" t="n">
         <v>170.5796269052402</v>
       </c>
       <c r="R7" t="n">
-        <v>171.0685585741373</v>
+        <v>171.0685585741372</v>
       </c>
       <c r="S7" t="n">
         <v>167.9556782617468</v>
       </c>
       <c r="T7" t="n">
-        <v>168.3774173419031</v>
+        <v>168.377417341903</v>
       </c>
       <c r="U7" t="n">
-        <v>167.2575327007471</v>
+        <v>167.257532700747</v>
       </c>
       <c r="V7" t="n">
-        <v>173.4260037472079</v>
+        <v>173.426003747208</v>
       </c>
       <c r="W7" t="n">
-        <v>165.5649103075471</v>
+        <v>165.564910307547</v>
       </c>
       <c r="X7" t="n">
-        <v>162.7183553040121</v>
+        <v>162.718355304012</v>
       </c>
       <c r="Y7" t="n">
         <v>164.2230954611847</v>
       </c>
       <c r="Z7" t="n">
-        <v>170.7090934840428</v>
+        <v>170.7090934840427</v>
       </c>
       <c r="AA7" t="n">
-        <v>165.0090102112047</v>
+        <v>165.0090102112046</v>
       </c>
       <c r="AB7" t="n">
-        <v>166.47660043134</v>
+        <v>166.4766004313401</v>
       </c>
     </row>
     <row r="8">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>169.3769402341728</v>
+        <v>169.3769402341726</v>
       </c>
       <c r="C8" t="n">
         <v>169.2545911665953</v>
@@ -6527,13 +6527,13 @@
         <v>169.0627995004338</v>
       </c>
       <c r="E8" t="n">
-        <v>156.926193750025</v>
+        <v>156.9261937500249</v>
       </c>
       <c r="F8" t="n">
-        <v>168.565376419391</v>
+        <v>168.5653764193908</v>
       </c>
       <c r="G8" t="n">
-        <v>168.7011232435105</v>
+        <v>168.7011232435104</v>
       </c>
       <c r="H8" t="n">
         <v>168.3123500787497</v>
@@ -6548,13 +6548,13 @@
         <v>168.9331932357549</v>
       </c>
       <c r="L8" t="n">
-        <v>169.193492820315</v>
+        <v>169.1934928203149</v>
       </c>
       <c r="M8" t="n">
-        <v>168.5934781664906</v>
+        <v>168.5934781664905</v>
       </c>
       <c r="N8" t="n">
-        <v>168.1498035117952</v>
+        <v>168.1498035117951</v>
       </c>
       <c r="O8" t="n">
         <v>167.7283375048612</v>
@@ -6566,10 +6566,10 @@
         <v>169.0526405655544</v>
       </c>
       <c r="R8" t="n">
-        <v>169.1930800327909</v>
+        <v>169.193080032791</v>
       </c>
       <c r="S8" t="n">
-        <v>168.2984882062983</v>
+        <v>168.2984882062982</v>
       </c>
       <c r="T8" t="n">
         <v>168.4276981350488</v>
@@ -6581,22 +6581,22 @@
         <v>173.3060313073766</v>
       </c>
       <c r="W8" t="n">
-        <v>167.6192376763379</v>
+        <v>167.6192376763378</v>
       </c>
       <c r="X8" t="n">
-        <v>166.816959682577</v>
+        <v>166.8169596825769</v>
       </c>
       <c r="Y8" t="n">
-        <v>167.2382376784622</v>
+        <v>167.2382376784621</v>
       </c>
       <c r="Z8" t="n">
-        <v>169.0865537232192</v>
+        <v>169.0865537232191</v>
       </c>
       <c r="AA8" t="n">
-        <v>167.4614781211017</v>
+        <v>167.4614781211014</v>
       </c>
       <c r="AB8" t="n">
-        <v>167.8871387411392</v>
+        <v>167.8871387411391</v>
       </c>
     </row>
   </sheetData>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172.4282661094636</v>
+        <v>172.4282661094637</v>
       </c>
       <c r="C2" t="n">
         <v>171.8259430332716</v>
@@ -6771,7 +6771,7 @@
         <v>172.4318660443406</v>
       </c>
       <c r="E2" t="n">
-        <v>159.154237352572</v>
+        <v>159.1542373525722</v>
       </c>
       <c r="F2" t="n">
         <v>172.1753511633857</v>
@@ -6780,13 +6780,13 @@
         <v>173.2472992534363</v>
       </c>
       <c r="H2" t="n">
-        <v>173.0022205070033</v>
+        <v>173.0022205070034</v>
       </c>
       <c r="I2" t="n">
-        <v>172.3678226681074</v>
+        <v>172.3678226681075</v>
       </c>
       <c r="J2" t="n">
-        <v>173.2053446380655</v>
+        <v>173.2053446380656</v>
       </c>
       <c r="K2" t="n">
         <v>172.6110743157378</v>
@@ -6795,22 +6795,22 @@
         <v>173.3110663738514</v>
       </c>
       <c r="M2" t="n">
-        <v>174.3072620855335</v>
+        <v>174.3072620855336</v>
       </c>
       <c r="N2" t="n">
         <v>173.1607543502024</v>
       </c>
       <c r="O2" t="n">
-        <v>173.1155185657555</v>
+        <v>173.1155185657556</v>
       </c>
       <c r="P2" t="n">
-        <v>173.6608331099284</v>
+        <v>173.6608331099283</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.6123509000727</v>
+        <v>172.6123509000728</v>
       </c>
       <c r="R2" t="n">
-        <v>172.5476302291682</v>
+        <v>172.5476302291684</v>
       </c>
       <c r="S2" t="n">
         <v>172.7990821002018</v>
@@ -6828,16 +6828,16 @@
         <v>174.3373619113482</v>
       </c>
       <c r="X2" t="n">
-        <v>173.0031499828832</v>
+        <v>173.0031499828833</v>
       </c>
       <c r="Y2" t="n">
         <v>174.3239447090627</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.0721237521156</v>
+        <v>173.0721237521157</v>
       </c>
       <c r="AA2" t="n">
-        <v>172.8210496408388</v>
+        <v>172.8210496408389</v>
       </c>
       <c r="AB2" t="n">
         <v>174.259892171819</v>
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="C3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="D3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="E3" t="n">
-        <v>160.7805051860955</v>
+        <v>160.7805051860958</v>
       </c>
       <c r="F3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="G3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="H3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="I3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="J3" t="n">
-        <v>174.2691253492711</v>
+        <v>174.269125349271</v>
       </c>
       <c r="K3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="L3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="M3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="N3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="O3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="P3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="Q3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="R3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="S3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="T3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="U3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="V3" t="n">
-        <v>179.2701638450761</v>
+        <v>179.270163845076</v>
       </c>
       <c r="W3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="X3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="Y3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="Z3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="AA3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
       <c r="AB3" t="n">
-        <v>174.2750441587981</v>
+        <v>174.275044158798</v>
       </c>
     </row>
     <row r="4">
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>215.4150272067138</v>
+        <v>215.4150272067147</v>
       </c>
       <c r="C4" t="n">
-        <v>71.91416740870723</v>
+        <v>71.91416740870724</v>
       </c>
       <c r="D4" t="n">
-        <v>246.4573954807734</v>
+        <v>246.4573954807736</v>
       </c>
       <c r="E4" t="n">
-        <v>235.3232459671693</v>
+        <v>235.3232459671695</v>
       </c>
       <c r="F4" t="n">
-        <v>171.2967136781756</v>
+        <v>171.2967136781755</v>
       </c>
       <c r="G4" t="n">
         <v>413.3038092484589</v>
       </c>
       <c r="H4" t="n">
-        <v>422.0468456481008</v>
+        <v>422.0468456481011</v>
       </c>
       <c r="I4" t="n">
-        <v>228.0415698914085</v>
+        <v>228.0415698914082</v>
       </c>
       <c r="J4" t="n">
-        <v>421.0119260393958</v>
+        <v>421.0119260393961</v>
       </c>
       <c r="K4" t="n">
         <v>266.3873125941257</v>
       </c>
       <c r="L4" t="n">
-        <v>454.4060421828201</v>
+        <v>454.4060421828229</v>
       </c>
       <c r="M4" t="n">
-        <v>719.1745865194579</v>
+        <v>719.1745865194599</v>
       </c>
       <c r="N4" t="n">
-        <v>440.9349012043086</v>
+        <v>440.9349012043085</v>
       </c>
       <c r="O4" t="n">
-        <v>375.143435537491</v>
+        <v>375.1434355374903</v>
       </c>
       <c r="P4" t="n">
-        <v>536.5921360229667</v>
+        <v>536.5921360229665</v>
       </c>
       <c r="Q4" t="n">
-        <v>283.0288117500752</v>
+        <v>283.028811750075</v>
       </c>
       <c r="R4" t="n">
-        <v>285.7838554585762</v>
+        <v>285.7838554585758</v>
       </c>
       <c r="S4" t="n">
         <v>297.3672995751255</v>
       </c>
       <c r="T4" t="n">
-        <v>315.0510417486688</v>
+        <v>315.0510417486685</v>
       </c>
       <c r="U4" t="n">
-        <v>534.0764135853713</v>
+        <v>534.0764135853724</v>
       </c>
       <c r="V4" t="n">
         <v>350.8686954858571</v>
       </c>
       <c r="W4" t="n">
-        <v>754.2124887664551</v>
+        <v>754.2124887664559</v>
       </c>
       <c r="X4" t="n">
-        <v>401.2086525674405</v>
+        <v>401.2086525674423</v>
       </c>
       <c r="Y4" t="n">
-        <v>738.7426148069659</v>
+        <v>738.7426148069665</v>
       </c>
       <c r="Z4" t="n">
-        <v>378.1352111919661</v>
+        <v>378.1352111919657</v>
       </c>
       <c r="AA4" t="n">
-        <v>340.6552588916862</v>
+        <v>340.6552588916863</v>
       </c>
       <c r="AB4" t="n">
-        <v>800.4075501250535</v>
+        <v>800.4075501250534</v>
       </c>
     </row>
     <row r="5">
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.04765441524794</v>
+        <v>15.04765441524796</v>
       </c>
       <c r="C5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="D5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="E5" t="n">
-        <v>18.21560019275743</v>
+        <v>18.21560019275744</v>
       </c>
       <c r="F5" t="n">
-        <v>16.1032646572982</v>
+        <v>16.10326465729822</v>
       </c>
       <c r="G5" t="n">
-        <v>23.22861408523776</v>
+        <v>23.22861408523779</v>
       </c>
       <c r="H5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="I5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="J5" t="n">
-        <v>21.82757151805724</v>
+        <v>21.82757151805725</v>
       </c>
       <c r="K5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="L5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="M5" t="n">
-        <v>21.82358147012933</v>
+        <v>21.82358147012936</v>
       </c>
       <c r="N5" t="n">
-        <v>440.9349012043086</v>
+        <v>16.57110441210656</v>
       </c>
       <c r="O5" t="n">
-        <v>18.01453070894695</v>
+        <v>18.01453070894697</v>
       </c>
       <c r="P5" t="n">
-        <v>17.66071204607412</v>
+        <v>17.66071204607414</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.71603009869403</v>
+        <v>13.71603009869406</v>
       </c>
       <c r="R5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.82358147012429</v>
       </c>
       <c r="S5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="T5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.8235814701243</v>
       </c>
       <c r="U5" t="n">
-        <v>18.51218101361938</v>
+        <v>18.5121810136194</v>
       </c>
       <c r="V5" t="n">
-        <v>19.99260389840562</v>
+        <v>19.99260389840561</v>
       </c>
       <c r="W5" t="n">
-        <v>21.82491312389911</v>
+        <v>21.82491312389913</v>
       </c>
       <c r="X5" t="n">
-        <v>14.3370572710656</v>
+        <v>14.33705727106561</v>
       </c>
       <c r="Y5" t="n">
-        <v>28.55361343180288</v>
+        <v>28.55361343180291</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.9217880923069</v>
+        <v>14.92178809230694</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.82358147012427</v>
+        <v>21.82358147012429</v>
       </c>
       <c r="AB5" t="n">
-        <v>28.90160386339181</v>
+        <v>28.9016038633918</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.1885087636303</v>
+        <v>30.18850876363031</v>
       </c>
       <c r="C6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="D6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="E6" t="n">
         <v>35.67795404865875</v>
       </c>
       <c r="F6" t="n">
-        <v>20.87339395205627</v>
+        <v>20.87339395205629</v>
       </c>
       <c r="G6" t="n">
-        <v>37.3250352530567</v>
+        <v>37.32503525305669</v>
       </c>
       <c r="H6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="I6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="J6" t="n">
-        <v>37.32902498842032</v>
+        <v>37.3290249884203</v>
       </c>
       <c r="K6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="L6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="M6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="N6" t="n">
-        <v>440.9349012043086</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="O6" t="n">
-        <v>39.69007078716876</v>
+        <v>39.69007078716875</v>
       </c>
       <c r="P6" t="n">
-        <v>40.2044254386622</v>
+        <v>40.20442543866216</v>
       </c>
       <c r="Q6" t="n">
-        <v>37.3250352530567</v>
+        <v>37.32503525305669</v>
       </c>
       <c r="R6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="S6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="T6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="U6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="V6" t="n">
-        <v>45.58599912462428</v>
+        <v>45.58599912462432</v>
       </c>
       <c r="W6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="X6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="Y6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.02234438462869</v>
+        <v>33.02234438462872</v>
       </c>
       <c r="AA6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
       <c r="AB6" t="n">
-        <v>37.32503494048736</v>
+        <v>37.32503494048738</v>
       </c>
     </row>
     <row r="7">
@@ -7211,7 +7211,7 @@
         <v>169.3234710324787</v>
       </c>
       <c r="E7" t="n">
-        <v>155.7453041826784</v>
+        <v>155.7453041826786</v>
       </c>
       <c r="F7" t="n">
         <v>170.8428583351991</v>
@@ -7223,37 +7223,37 @@
         <v>166.0385407547673</v>
       </c>
       <c r="I7" t="n">
-        <v>169.707178709483</v>
+        <v>169.7071787094831</v>
       </c>
       <c r="J7" t="n">
-        <v>164.6599082313837</v>
+        <v>164.6599082313836</v>
       </c>
       <c r="K7" t="n">
-        <v>168.265241072469</v>
+        <v>168.2652410724689</v>
       </c>
       <c r="L7" t="n">
-        <v>164.0798479357038</v>
+        <v>164.0798479357037</v>
       </c>
       <c r="M7" t="n">
-        <v>158.3987684459966</v>
+        <v>158.3987684459968</v>
       </c>
       <c r="N7" t="n">
-        <v>165.0149625148381</v>
+        <v>165.0149625148382</v>
       </c>
       <c r="O7" t="n">
-        <v>165.1688869873148</v>
+        <v>165.1688869873149</v>
       </c>
       <c r="P7" t="n">
-        <v>161.9102066959871</v>
+        <v>161.910206695987</v>
       </c>
       <c r="Q7" t="n">
-        <v>168.2509041505128</v>
+        <v>168.2509041505127</v>
       </c>
       <c r="R7" t="n">
         <v>168.6675714524316</v>
       </c>
       <c r="S7" t="n">
-        <v>167.0836102381047</v>
+        <v>167.0836102381045</v>
       </c>
       <c r="T7" t="n">
         <v>167.8973192645142</v>
@@ -7277,10 +7277,10 @@
         <v>165.4467514737604</v>
       </c>
       <c r="AA7" t="n">
-        <v>166.9948533841075</v>
+        <v>166.9948533841076</v>
       </c>
       <c r="AB7" t="n">
-        <v>158.61932884669</v>
+        <v>158.6193288466901</v>
       </c>
     </row>
     <row r="8">
@@ -7299,25 +7299,25 @@
         <v>170.1788844921381</v>
       </c>
       <c r="E8" t="n">
-        <v>156.8632048497838</v>
+        <v>156.8632048497839</v>
       </c>
       <c r="F8" t="n">
-        <v>170.6136956759209</v>
+        <v>170.613695675921</v>
       </c>
       <c r="G8" t="n">
         <v>168.7542604365515</v>
       </c>
       <c r="H8" t="n">
-        <v>169.2545852099903</v>
+        <v>169.2545852099904</v>
       </c>
       <c r="I8" t="n">
-        <v>170.2894293317457</v>
+        <v>170.2894293317456</v>
       </c>
       <c r="J8" t="n">
         <v>168.8331202266687</v>
       </c>
       <c r="K8" t="n">
-        <v>169.876594759352</v>
+        <v>169.8765947593521</v>
       </c>
       <c r="L8" t="n">
         <v>168.6722196021809</v>
@@ -7326,10 +7326,10 @@
         <v>167.0835060415203</v>
       </c>
       <c r="N8" t="n">
-        <v>168.9473876920715</v>
+        <v>168.9473876920717</v>
       </c>
       <c r="O8" t="n">
-        <v>168.9721880331296</v>
+        <v>168.9721880331297</v>
       </c>
       <c r="P8" t="n">
         <v>168.0347926599503</v>
@@ -7338,7 +7338,7 @@
         <v>169.8713479985079</v>
       </c>
       <c r="R8" t="n">
-        <v>169.9962122778162</v>
+        <v>169.9962122778163</v>
       </c>
       <c r="S8" t="n">
         <v>169.5269567485462</v>
@@ -7350,22 +7350,22 @@
         <v>168.1774731486713</v>
       </c>
       <c r="V8" t="n">
-        <v>174.0885113236972</v>
+        <v>174.0885113236973</v>
       </c>
       <c r="W8" t="n">
-        <v>166.9502250308028</v>
+        <v>166.9502250308029</v>
       </c>
       <c r="X8" t="n">
-        <v>169.2239511874425</v>
+        <v>169.2239511874426</v>
       </c>
       <c r="Y8" t="n">
-        <v>166.9847113498635</v>
+        <v>166.9847113498636</v>
       </c>
       <c r="Z8" t="n">
         <v>169.0552224463242</v>
       </c>
       <c r="AA8" t="n">
-        <v>169.5085396377633</v>
+        <v>169.5085396377632</v>
       </c>
       <c r="AB8" t="n">
         <v>167.1364918130054</v>
@@ -7534,46 +7534,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>170.6346320814247</v>
+        <v>170.6346320814246</v>
       </c>
       <c r="C2" t="n">
-        <v>170.7382862854172</v>
+        <v>170.738286285417</v>
       </c>
       <c r="D2" t="n">
-        <v>170.8715127093313</v>
+        <v>170.8715127093312</v>
       </c>
       <c r="E2" t="n">
-        <v>158.1900883872165</v>
+        <v>158.1900883872166</v>
       </c>
       <c r="F2" t="n">
         <v>170.9229597298659</v>
       </c>
       <c r="G2" t="n">
-        <v>171.9868049353931</v>
+        <v>171.9868049353929</v>
       </c>
       <c r="H2" t="n">
-        <v>171.7009164455629</v>
+        <v>171.7009164455627</v>
       </c>
       <c r="I2" t="n">
         <v>170.815247832913</v>
       </c>
       <c r="J2" t="n">
-        <v>171.5927691595151</v>
+        <v>171.5927691595152</v>
       </c>
       <c r="K2" t="n">
-        <v>171.1394749717065</v>
+        <v>171.1394749717066</v>
       </c>
       <c r="L2" t="n">
         <v>171.1450457102127</v>
       </c>
       <c r="M2" t="n">
-        <v>171.5695275647612</v>
+        <v>171.569527564761</v>
       </c>
       <c r="N2" t="n">
-        <v>171.6474321584872</v>
+        <v>171.6474321584871</v>
       </c>
       <c r="O2" t="n">
-        <v>171.8534097824493</v>
+        <v>171.8534097824492</v>
       </c>
       <c r="P2" t="n">
         <v>172.3629763673281</v>
@@ -7582,28 +7582,28 @@
         <v>171.0871424258702</v>
       </c>
       <c r="R2" t="n">
-        <v>170.8771999467346</v>
+        <v>170.8771999467345</v>
       </c>
       <c r="S2" t="n">
-        <v>171.097477836222</v>
+        <v>171.0974778362219</v>
       </c>
       <c r="T2" t="n">
-        <v>171.2636977767812</v>
+        <v>171.263697776781</v>
       </c>
       <c r="U2" t="n">
-        <v>171.660444868463</v>
+        <v>171.6604448684631</v>
       </c>
       <c r="V2" t="n">
         <v>176.3045983085045</v>
       </c>
       <c r="W2" t="n">
-        <v>172.677576952876</v>
+        <v>172.6775769528761</v>
       </c>
       <c r="X2" t="n">
-        <v>172.0152133457924</v>
+        <v>172.0152133457925</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.1083802879204</v>
+        <v>173.1083802879203</v>
       </c>
       <c r="Z2" t="n">
         <v>171.1816363669411</v>
@@ -7612,7 +7612,7 @@
         <v>171.3455982391742</v>
       </c>
       <c r="AB2" t="n">
-        <v>172.6127461593473</v>
+        <v>172.6127461593472</v>
       </c>
     </row>
     <row r="3">
@@ -7646,7 +7646,7 @@
         <v>173.2089756102585</v>
       </c>
       <c r="J3" t="n">
-        <v>173.198678387534</v>
+        <v>173.1986783875338</v>
       </c>
       <c r="K3" t="n">
         <v>173.2089756102585</v>
@@ -7682,7 +7682,7 @@
         <v>173.2089756102585</v>
       </c>
       <c r="V3" t="n">
-        <v>178.142237462619</v>
+        <v>178.1422374626189</v>
       </c>
       <c r="W3" t="n">
         <v>173.2089756102585</v>
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.60712773544176</v>
+        <v>29.60712773544169</v>
       </c>
       <c r="C4" t="n">
-        <v>56.86427005499232</v>
+        <v>56.86427005499245</v>
       </c>
       <c r="D4" t="n">
-        <v>92.45725757351222</v>
+        <v>92.45725757351254</v>
       </c>
       <c r="E4" t="n">
-        <v>125.9838164323147</v>
+        <v>125.9838164323149</v>
       </c>
       <c r="F4" t="n">
         <v>105.3293005302388</v>
       </c>
       <c r="G4" t="n">
-        <v>323.5104198059317</v>
+        <v>323.5104198059016</v>
       </c>
       <c r="H4" t="n">
         <v>327.8987694463775</v>
       </c>
       <c r="I4" t="n">
-        <v>80.47397924948341</v>
+        <v>80.47397924948356</v>
       </c>
       <c r="J4" t="n">
-        <v>253.9053140797343</v>
+        <v>253.9053140797383</v>
       </c>
       <c r="K4" t="n">
         <v>145.721160483435</v>
       </c>
       <c r="L4" t="n">
-        <v>145.627740942989</v>
+        <v>145.6277409429892</v>
       </c>
       <c r="M4" t="n">
-        <v>254.2087270504203</v>
+        <v>254.2087270504198</v>
       </c>
       <c r="N4" t="n">
-        <v>293.0574511445151</v>
+        <v>293.0574511445157</v>
       </c>
       <c r="O4" t="n">
-        <v>299.2059253995236</v>
+        <v>299.2059253995243</v>
       </c>
       <c r="P4" t="n">
-        <v>429.8743428483637</v>
+        <v>429.8743428483631</v>
       </c>
       <c r="Q4" t="n">
         <v>135.3060198073402</v>
       </c>
       <c r="R4" t="n">
-        <v>98.3982698544023</v>
+        <v>98.39826985440244</v>
       </c>
       <c r="S4" t="n">
-        <v>131.2686536529475</v>
+        <v>131.2686536529474</v>
       </c>
       <c r="T4" t="n">
-        <v>196.2156656344613</v>
+        <v>196.2156656344565</v>
       </c>
       <c r="U4" t="n">
-        <v>265.0567564088129</v>
+        <v>265.0567564088123</v>
       </c>
       <c r="V4" t="n">
-        <v>209.9476912900789</v>
+        <v>209.9476912900785</v>
       </c>
       <c r="W4" t="n">
-        <v>549.3462209801116</v>
+        <v>549.3462209801115</v>
       </c>
       <c r="X4" t="n">
-        <v>377.7402372686368</v>
+        <v>377.7402372686324</v>
       </c>
       <c r="Y4" t="n">
-        <v>649.5605114464809</v>
+        <v>649.5605114464799</v>
       </c>
       <c r="Z4" t="n">
-        <v>149.809716102642</v>
+        <v>149.8097161026423</v>
       </c>
       <c r="AA4" t="n">
-        <v>211.3717589640594</v>
+        <v>211.3717589640565</v>
       </c>
       <c r="AB4" t="n">
-        <v>567.4191831263059</v>
+        <v>567.4191831263065</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.8306690014179</v>
+        <v>11.83066900141787</v>
       </c>
       <c r="C5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="D5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="E5" t="n">
-        <v>14.25304390801876</v>
+        <v>14.25304390801874</v>
       </c>
       <c r="F5" t="n">
-        <v>12.63784309504382</v>
+        <v>12.6378430950438</v>
       </c>
       <c r="G5" t="n">
-        <v>18.08625315864656</v>
+        <v>18.08625315864645</v>
       </c>
       <c r="H5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="I5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="J5" t="n">
-        <v>17.01507188821912</v>
+        <v>17.01507188821894</v>
       </c>
       <c r="K5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="L5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745711</v>
       </c>
       <c r="M5" t="n">
-        <v>17.01189267746539</v>
+        <v>17.01189267746546</v>
       </c>
       <c r="N5" t="n">
-        <v>293.0574511445151</v>
+        <v>12.99557752676152</v>
       </c>
       <c r="O5" t="n">
-        <v>14.09929579937037</v>
+        <v>14.09929579937035</v>
       </c>
       <c r="P5" t="n">
-        <v>13.82874778159021</v>
+        <v>13.82874778159023</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.81244029545072</v>
+        <v>10.81244029545082</v>
       </c>
       <c r="R5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="S5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="T5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="U5" t="n">
-        <v>14.46614296446596</v>
+        <v>14.46614296446567</v>
       </c>
       <c r="V5" t="n">
-        <v>15.59743984860199</v>
+        <v>15.5974398486019</v>
       </c>
       <c r="W5" t="n">
-        <v>17.01291092887035</v>
+        <v>17.01291092887042</v>
       </c>
       <c r="X5" t="n">
-        <v>11.2873097359975</v>
+        <v>11.28730973599747</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.13461675622034</v>
+        <v>22.13461675622037</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.73442511225037</v>
+        <v>11.73442511225048</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.01189267745699</v>
+        <v>17.01189267745718</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.42411404697179</v>
+        <v>22.42411404697172</v>
       </c>
     </row>
     <row r="6">
@@ -7886,85 +7886,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.58817082594167</v>
+        <v>22.5881708259421</v>
       </c>
       <c r="C6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="D6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="E6" t="n">
-        <v>26.61125259809676</v>
+        <v>26.61125259809658</v>
       </c>
       <c r="F6" t="n">
-        <v>15.76134832236701</v>
+        <v>15.76134832236681</v>
       </c>
       <c r="G6" t="n">
-        <v>27.81835860364248</v>
+        <v>27.81835860364263</v>
       </c>
       <c r="H6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="I6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="J6" t="n">
-        <v>27.82153568962787</v>
+        <v>27.82153568962738</v>
       </c>
       <c r="K6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="L6" t="n">
-        <v>27.81835647886594</v>
+        <v>27.81835647886603</v>
       </c>
       <c r="M6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="N6" t="n">
-        <v>293.0574511445151</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="O6" t="n">
-        <v>29.55163598482599</v>
+        <v>29.55163598482606</v>
       </c>
       <c r="P6" t="n">
-        <v>29.92859407720197</v>
+        <v>29.92859407720221</v>
       </c>
       <c r="Q6" t="n">
-        <v>27.81835860364248</v>
+        <v>27.81835860364263</v>
       </c>
       <c r="R6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="S6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="T6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="U6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="V6" t="n">
-        <v>33.87413188243357</v>
+        <v>33.87413188243229</v>
       </c>
       <c r="W6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="X6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="Y6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.66502046013255</v>
+        <v>24.66502046013187</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
       <c r="AB6" t="n">
-        <v>27.81835647886592</v>
+        <v>27.81835647886578</v>
       </c>
     </row>
     <row r="7">
@@ -7977,13 +7977,13 @@
         <v>172.5909722238257</v>
       </c>
       <c r="C7" t="n">
-        <v>171.9919561022694</v>
+        <v>171.9919561022693</v>
       </c>
       <c r="D7" t="n">
-        <v>171.2129902625611</v>
+        <v>171.2129902625612</v>
       </c>
       <c r="E7" t="n">
-        <v>157.3339696680903</v>
+        <v>157.3339696680901</v>
       </c>
       <c r="F7" t="n">
         <v>170.9228590925659</v>
@@ -7995,22 +7995,22 @@
         <v>166.4009692941183</v>
       </c>
       <c r="I7" t="n">
-        <v>171.5456870567848</v>
+        <v>171.5456870567846</v>
       </c>
       <c r="J7" t="n">
         <v>166.855565977855</v>
       </c>
       <c r="K7" t="n">
-        <v>169.6383347788976</v>
+        <v>169.6383347788977</v>
       </c>
       <c r="L7" t="n">
-        <v>169.5773811172461</v>
+        <v>169.577381117246</v>
       </c>
       <c r="M7" t="n">
-        <v>167.1474453581361</v>
+        <v>167.1474453581362</v>
       </c>
       <c r="N7" t="n">
-        <v>166.6403356926726</v>
+        <v>166.6403356926725</v>
       </c>
       <c r="O7" t="n">
         <v>165.331681650371</v>
@@ -8019,37 +8019,37 @@
         <v>162.287184898125</v>
       </c>
       <c r="Q7" t="n">
-        <v>169.941593321548</v>
+        <v>169.9415933215481</v>
       </c>
       <c r="R7" t="n">
-        <v>171.1876818451697</v>
+        <v>171.1876818451698</v>
       </c>
       <c r="S7" t="n">
         <v>169.8478388852823</v>
       </c>
       <c r="T7" t="n">
-        <v>168.9184811718285</v>
+        <v>168.9184811718284</v>
       </c>
       <c r="U7" t="n">
         <v>166.5237546623005</v>
       </c>
       <c r="V7" t="n">
-        <v>172.688023525087</v>
+        <v>172.6880235250871</v>
       </c>
       <c r="W7" t="n">
-        <v>160.5384827885235</v>
+        <v>160.5384827885233</v>
       </c>
       <c r="X7" t="n">
-        <v>164.5053594227977</v>
+        <v>164.5053594227976</v>
       </c>
       <c r="Y7" t="n">
-        <v>158.020462398158</v>
+        <v>158.0204623981581</v>
       </c>
       <c r="Z7" t="n">
-        <v>169.3410408967562</v>
+        <v>169.3410408967561</v>
       </c>
       <c r="AA7" t="n">
-        <v>168.403698529672</v>
+        <v>168.4036985296721</v>
       </c>
       <c r="AB7" t="n">
         <v>161.0164472833106</v>
@@ -8062,43 +8062,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>170.3534385711379</v>
+        <v>170.353438571138</v>
       </c>
       <c r="C8" t="n">
-        <v>170.1845385308711</v>
+        <v>170.184538530871</v>
       </c>
       <c r="D8" t="n">
         <v>169.9633330153011</v>
       </c>
       <c r="E8" t="n">
-        <v>156.8937270766407</v>
+        <v>156.8937270766409</v>
       </c>
       <c r="F8" t="n">
-        <v>169.8827694288946</v>
+        <v>169.8827694288947</v>
       </c>
       <c r="G8" t="n">
-        <v>168.0476160516669</v>
+        <v>168.047616051667</v>
       </c>
       <c r="H8" t="n">
-        <v>168.6032518758903</v>
+        <v>168.6032518758904</v>
       </c>
       <c r="I8" t="n">
-        <v>170.0584462404964</v>
+        <v>170.0584462404965</v>
       </c>
       <c r="J8" t="n">
         <v>168.7066327988112</v>
       </c>
       <c r="K8" t="n">
-        <v>169.5148220144802</v>
+        <v>169.5148220144801</v>
       </c>
       <c r="L8" t="n">
-        <v>169.492658642687</v>
+        <v>169.4926586426869</v>
       </c>
       <c r="M8" t="n">
         <v>168.8115119830947</v>
       </c>
       <c r="N8" t="n">
-        <v>168.6586800629721</v>
+        <v>168.658680062972</v>
       </c>
       <c r="O8" t="n">
         <v>168.2692159272542</v>
@@ -8107,19 +8107,19 @@
         <v>167.3935267876257</v>
       </c>
       <c r="Q8" t="n">
-        <v>169.6004730719773</v>
+        <v>169.6004730719775</v>
       </c>
       <c r="R8" t="n">
         <v>169.9575048421382</v>
       </c>
       <c r="S8" t="n">
-        <v>169.5681499150508</v>
+        <v>169.5681499150509</v>
       </c>
       <c r="T8" t="n">
-        <v>169.3115091343011</v>
+        <v>169.3115091343008</v>
       </c>
       <c r="U8" t="n">
-        <v>168.6186480326071</v>
+        <v>168.6186480326068</v>
       </c>
       <c r="V8" t="n">
         <v>173.8229135853789</v>
@@ -8128,16 +8128,16 @@
         <v>166.9124623405218</v>
       </c>
       <c r="X8" t="n">
-        <v>168.0550402437187</v>
+        <v>168.0550402437185</v>
       </c>
       <c r="Y8" t="n">
-        <v>166.1975583734951</v>
+        <v>166.197558373495</v>
       </c>
       <c r="Z8" t="n">
-        <v>169.421713745921</v>
+        <v>169.4217137459209</v>
       </c>
       <c r="AA8" t="n">
-        <v>169.159181853998</v>
+        <v>169.1591818539979</v>
       </c>
       <c r="AB8" t="n">
         <v>167.0651069153035</v>
